--- a/data/YACHT.MI.xlsx
+++ b/data/YACHT.MI.xlsx
@@ -19094,6 +19094,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="815">
+      <c r="A815" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B815" t="n">
+        <v>262903</v>
+      </c>
+      <c r="C815" t="n">
+        <v>2.98000001907349</v>
+      </c>
+      <c r="D815" t="n">
+        <v>2.85800004005432</v>
+      </c>
+      <c r="E815" t="n">
+        <v>2.93799996376038</v>
+      </c>
+      <c r="F815" t="n">
+        <v>2.9760000705719</v>
+      </c>
+      <c r="G815" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/YACHT.MI.xlsx
+++ b/data/YACHT.MI.xlsx
@@ -19117,6 +19117,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="816">
+      <c r="A816" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B816" t="n">
+        <v>188578</v>
+      </c>
+      <c r="C816" t="n">
+        <v>3.01200008392334</v>
+      </c>
+      <c r="D816" t="n">
+        <v>2.92000007629395</v>
+      </c>
+      <c r="E816" t="n">
+        <v>2.96399998664856</v>
+      </c>
+      <c r="F816" t="n">
+        <v>2.94000005722046</v>
+      </c>
+      <c r="G816" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/YACHT.MI.xlsx
+++ b/data/YACHT.MI.xlsx
@@ -19140,6 +19140,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="817">
+      <c r="A817" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B817" t="n">
+        <v>137307</v>
+      </c>
+      <c r="C817" t="n">
+        <v>2.97399997711182</v>
+      </c>
+      <c r="D817" t="n">
+        <v>2.9300000667572</v>
+      </c>
+      <c r="E817" t="n">
+        <v>2.96399998664856</v>
+      </c>
+      <c r="F817" t="n">
+        <v>2.92199993133545</v>
+      </c>
+      <c r="G817" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/YACHT.MI.xlsx
+++ b/data/YACHT.MI.xlsx
@@ -19151,7 +19151,7 @@
         <v>2.97399997711182</v>
       </c>
       <c r="D817" t="n">
-        <v>2.9300000667572</v>
+        <v>2.92199993133545</v>
       </c>
       <c r="E817" t="n">
         <v>2.96399998664856</v>
@@ -19160,6 +19160,29 @@
         <v>2.92199993133545</v>
       </c>
       <c r="G817" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B818" t="n">
+        <v>185983</v>
+      </c>
+      <c r="C818" t="n">
+        <v>2.98399996757507</v>
+      </c>
+      <c r="D818" t="n">
+        <v>2.87199997901917</v>
+      </c>
+      <c r="E818" t="n">
+        <v>2.93400001525879</v>
+      </c>
+      <c r="F818" t="n">
+        <v>2.85199999809265</v>
+      </c>
+      <c r="G818" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/YACHT.MI.xlsx
+++ b/data/YACHT.MI.xlsx
@@ -19004,10 +19004,10 @@
     </row>
     <row r="811">
       <c r="A811" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B811" t="n">
-        <v>104051</v>
+        <v>105606</v>
       </c>
       <c r="C811" t="n">
         <v>2.95600008964539</v>
@@ -19016,10 +19016,10 @@
         <v>2.92000007629395</v>
       </c>
       <c r="E811" t="n">
-        <v>2.94000005722046</v>
+        <v>2.95600008964539</v>
       </c>
       <c r="F811" t="n">
-        <v>2.93600010871887</v>
+        <v>2.92799997329712</v>
       </c>
       <c r="G811" t="s">
         <v>7</v>
@@ -19027,22 +19027,22 @@
     </row>
     <row r="812">
       <c r="A812" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B812" t="n">
-        <v>124066</v>
+        <v>104051</v>
       </c>
       <c r="C812" t="n">
-        <v>3.01999998092651</v>
+        <v>2.95600008964539</v>
       </c>
       <c r="D812" t="n">
-        <v>2.90799999237061</v>
+        <v>2.92000007629395</v>
       </c>
       <c r="E812" t="n">
-        <v>3.01999998092651</v>
+        <v>2.94000005722046</v>
       </c>
       <c r="F812" t="n">
-        <v>2.92600011825562</v>
+        <v>2.93600010871887</v>
       </c>
       <c r="G812" t="s">
         <v>7</v>
@@ -19050,22 +19050,22 @@
     </row>
     <row r="813">
       <c r="A813" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B813" t="n">
-        <v>99624</v>
+        <v>124066</v>
       </c>
       <c r="C813" t="n">
-        <v>2.94000005722046</v>
+        <v>3.01999998092651</v>
       </c>
       <c r="D813" t="n">
-        <v>2.88000011444092</v>
+        <v>2.90799999237061</v>
       </c>
       <c r="E813" t="n">
-        <v>2.94000005722046</v>
+        <v>3.01999998092651</v>
       </c>
       <c r="F813" t="n">
-        <v>2.89199995994568</v>
+        <v>2.92600011825562</v>
       </c>
       <c r="G813" t="s">
         <v>7</v>
@@ -19073,22 +19073,22 @@
     </row>
     <row r="814">
       <c r="A814" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B814" t="n">
-        <v>194877</v>
+        <v>99624</v>
       </c>
       <c r="C814" t="n">
-        <v>2.97000002861023</v>
+        <v>2.94000005722046</v>
       </c>
       <c r="D814" t="n">
-        <v>2.89000010490417</v>
+        <v>2.88000011444092</v>
       </c>
       <c r="E814" t="n">
-        <v>2.89000010490417</v>
+        <v>2.94000005722046</v>
       </c>
       <c r="F814" t="n">
-        <v>2.93600010871887</v>
+        <v>2.89199995994568</v>
       </c>
       <c r="G814" t="s">
         <v>7</v>
@@ -19096,22 +19096,22 @@
     </row>
     <row r="815">
       <c r="A815" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B815" t="n">
-        <v>262903</v>
+        <v>194877</v>
       </c>
       <c r="C815" t="n">
-        <v>2.98000001907349</v>
+        <v>2.97000002861023</v>
       </c>
       <c r="D815" t="n">
-        <v>2.85800004005432</v>
+        <v>2.89000010490417</v>
       </c>
       <c r="E815" t="n">
-        <v>2.93799996376038</v>
+        <v>2.89000010490417</v>
       </c>
       <c r="F815" t="n">
-        <v>2.9760000705719</v>
+        <v>2.93600010871887</v>
       </c>
       <c r="G815" t="s">
         <v>7</v>
@@ -19119,22 +19119,22 @@
     </row>
     <row r="816">
       <c r="A816" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B816" t="n">
-        <v>188578</v>
+        <v>262903</v>
       </c>
       <c r="C816" t="n">
-        <v>3.01200008392334</v>
+        <v>2.98000001907349</v>
       </c>
       <c r="D816" t="n">
-        <v>2.92000007629395</v>
+        <v>2.85800004005432</v>
       </c>
       <c r="E816" t="n">
-        <v>2.96399998664856</v>
+        <v>2.93799996376038</v>
       </c>
       <c r="F816" t="n">
-        <v>2.94000005722046</v>
+        <v>2.9760000705719</v>
       </c>
       <c r="G816" t="s">
         <v>7</v>
@@ -19142,22 +19142,22 @@
     </row>
     <row r="817">
       <c r="A817" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B817" t="n">
-        <v>137307</v>
+        <v>188578</v>
       </c>
       <c r="C817" t="n">
-        <v>2.97399997711182</v>
+        <v>3.01200008392334</v>
       </c>
       <c r="D817" t="n">
-        <v>2.92199993133545</v>
+        <v>2.92000007629395</v>
       </c>
       <c r="E817" t="n">
         <v>2.96399998664856</v>
       </c>
       <c r="F817" t="n">
-        <v>2.92199993133545</v>
+        <v>2.94000005722046</v>
       </c>
       <c r="G817" t="s">
         <v>7</v>
@@ -19165,24 +19165,47 @@
     </row>
     <row r="818">
       <c r="A818" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B818" t="n">
-        <v>185983</v>
+        <v>137307</v>
       </c>
       <c r="C818" t="n">
-        <v>2.98399996757507</v>
+        <v>2.97399997711182</v>
       </c>
       <c r="D818" t="n">
-        <v>2.87199997901917</v>
+        <v>2.92199993133545</v>
       </c>
       <c r="E818" t="n">
-        <v>2.93400001525879</v>
+        <v>2.96399998664856</v>
       </c>
       <c r="F818" t="n">
-        <v>2.85199999809265</v>
+        <v>2.92199993133545</v>
       </c>
       <c r="G818" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B819" t="n">
+        <v>353645</v>
+      </c>
+      <c r="C819" t="n">
+        <v>2.96000003814697</v>
+      </c>
+      <c r="D819" t="n">
+        <v>2.85800004005432</v>
+      </c>
+      <c r="E819" t="n">
+        <v>2.85800004005432</v>
+      </c>
+      <c r="F819" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="G819" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/YACHT.MI.xlsx
+++ b/data/YACHT.MI.xlsx
@@ -499,7 +499,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G5" t="n">
-        <v>2.59330797195435</v>
+        <v>2.59330821037292</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G6" t="n">
-        <v>2.61131715774536</v>
+        <v>2.61131739616394</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G7" t="n">
-        <v>2.62032175064087</v>
+        <v>2.62032198905945</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>2.88199996948242</v>
       </c>
       <c r="G11" t="n">
-        <v>2.59510898590088</v>
+        <v>2.5951087474823</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>2.89800000190735</v>
       </c>
       <c r="G12" t="n">
-        <v>2.60951614379883</v>
+        <v>2.60951638221741</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>2.89599990844727</v>
       </c>
       <c r="G14" t="n">
-        <v>2.60771536827087</v>
+        <v>2.60771512985229</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G18" t="n">
-        <v>2.84543538093567</v>
+        <v>2.84543561935425</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G21" t="n">
-        <v>2.82742619514465</v>
+        <v>2.82742643356323</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G22" t="n">
-        <v>2.79140782356262</v>
+        <v>2.7914080619812</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>3.08200001716614</v>
       </c>
       <c r="G24" t="n">
-        <v>2.77519965171814</v>
+        <v>2.77519989013672</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>3.16599988937378</v>
       </c>
       <c r="G28" t="n">
-        <v>2.85083794593811</v>
+        <v>2.85083770751953</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>3.12199997901917</v>
       </c>
       <c r="G29" t="n">
-        <v>2.81121778488159</v>
+        <v>2.81121802330017</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>3.17799997329712</v>
       </c>
       <c r="G30" t="n">
-        <v>2.86164355278015</v>
+        <v>2.86164331436157</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G33" t="n">
-        <v>2.7283763885498</v>
+        <v>2.72837615013123</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G35" t="n">
-        <v>2.69235825538635</v>
+        <v>2.69235801696777</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>2.96199989318848</v>
       </c>
       <c r="G36" t="n">
-        <v>2.66714525222778</v>
+        <v>2.66714549064636</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>2.96199989318848</v>
       </c>
       <c r="G37" t="n">
-        <v>2.66714525222778</v>
+        <v>2.66714549064636</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G39" t="n">
-        <v>2.6563401222229</v>
+        <v>2.65633988380432</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>2.93400001525879</v>
       </c>
       <c r="G40" t="n">
-        <v>2.64193248748779</v>
+        <v>2.64193272590637</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>2.89800000190735</v>
       </c>
       <c r="G41" t="n">
-        <v>2.60951614379883</v>
+        <v>2.60951638221741</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>2.91599988937378</v>
       </c>
       <c r="G42" t="n">
-        <v>2.62572455406189</v>
+        <v>2.62572431564331</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G44" t="n">
-        <v>2.61131715774536</v>
+        <v>2.61131739616394</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>2.89800000190735</v>
       </c>
       <c r="G45" t="n">
-        <v>2.60951614379883</v>
+        <v>2.60951638221741</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>2.91400003433228</v>
       </c>
       <c r="G47" t="n">
-        <v>2.62392354011536</v>
+        <v>2.62392377853394</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G49" t="n">
-        <v>2.6563401222229</v>
+        <v>2.65633988380432</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G50" t="n">
-        <v>2.63833093643188</v>
+        <v>2.63833069801331</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>2.89199995994568</v>
       </c>
       <c r="G51" t="n">
-        <v>2.60411357879639</v>
+        <v>2.60411334037781</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>2.81200003623962</v>
       </c>
       <c r="G53" t="n">
-        <v>2.5320770740509</v>
+        <v>2.53207731246948</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G54" t="n">
-        <v>2.62032175064087</v>
+        <v>2.62032198905945</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G55" t="n">
-        <v>2.59330797195435</v>
+        <v>2.59330821037292</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G57" t="n">
-        <v>2.59330797195435</v>
+        <v>2.59330821037292</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G58" t="n">
-        <v>2.61131715774536</v>
+        <v>2.61131739616394</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>2.93600010871887</v>
       </c>
       <c r="G59" t="n">
-        <v>2.64373373985291</v>
+        <v>2.64373350143433</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G60" t="n">
-        <v>2.61131715774536</v>
+        <v>2.61131739616394</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G61" t="n">
-        <v>2.6563401222229</v>
+        <v>2.65633988380432</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G64" t="n">
-        <v>2.67434906959534</v>
+        <v>2.67434883117676</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>2.88599991798401</v>
       </c>
       <c r="G65" t="n">
-        <v>2.59871053695679</v>
+        <v>2.59871077537537</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G66" t="n">
-        <v>2.61131715774536</v>
+        <v>2.61131739616394</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>2.84599995613098</v>
       </c>
       <c r="G67" t="n">
-        <v>2.56269240379333</v>
+        <v>2.56269264221191</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>2.80399990081787</v>
       </c>
       <c r="G68" t="n">
-        <v>2.52487325668335</v>
+        <v>2.52487373352051</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>2.85800004005432</v>
       </c>
       <c r="G69" t="n">
-        <v>2.57349824905396</v>
+        <v>2.57349801063538</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.81399989128113</v>
       </c>
       <c r="G75" t="n">
-        <v>2.53387808799744</v>
+        <v>2.53387832641602</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>2.81200003623962</v>
       </c>
       <c r="G79" t="n">
-        <v>2.5320770740509</v>
+        <v>2.53207731246948</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G83" t="n">
-        <v>2.52127194404602</v>
+        <v>2.52127170562744</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>2.73399996757507</v>
       </c>
       <c r="G85" t="n">
-        <v>2.46184182167053</v>
+        <v>2.46184158325195</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>2.76399993896484</v>
       </c>
       <c r="G86" t="n">
-        <v>2.4888551235199</v>
+        <v>2.48885536193848</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>2.77600002288818</v>
       </c>
       <c r="G91" t="n">
-        <v>2.49966096878052</v>
+        <v>2.49966073036194</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.84599995613098</v>
       </c>
       <c r="G94" t="n">
-        <v>2.56269240379333</v>
+        <v>2.56269264221191</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G100" t="n">
-        <v>2.62032175064087</v>
+        <v>2.62032198905945</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.93799996376038</v>
       </c>
       <c r="G101" t="n">
-        <v>2.64553427696228</v>
+        <v>2.64553451538086</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G103" t="n">
-        <v>2.7283763885498</v>
+        <v>2.72837615013123</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G106" t="n">
-        <v>2.61131715774536</v>
+        <v>2.61131739616394</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>2.90400004386902</v>
       </c>
       <c r="G108" t="n">
-        <v>2.61491894721985</v>
+        <v>2.61491918563843</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G109" t="n">
-        <v>2.69235825538635</v>
+        <v>2.69235801696777</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>3</v>
       </c>
       <c r="G112" t="n">
-        <v>2.7013623714447</v>
+        <v>2.70136260986328</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G113" t="n">
-        <v>2.62032175064087</v>
+        <v>2.62032198905945</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G116" t="n">
-        <v>2.6563401222229</v>
+        <v>2.65633988380432</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>2.98799991607666</v>
       </c>
       <c r="G118" t="n">
-        <v>2.69055724143982</v>
+        <v>2.69055700302124</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G125" t="n">
-        <v>2.6563401222229</v>
+        <v>2.65633988380432</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>2.99200010299683</v>
       </c>
       <c r="G126" t="n">
-        <v>2.69415903091431</v>
+        <v>2.69415926933289</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G131" t="n">
-        <v>2.62032175064087</v>
+        <v>2.62032198905945</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G132" t="n">
-        <v>2.59330797195435</v>
+        <v>2.59330821037292</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>2.80599999427795</v>
       </c>
       <c r="G136" t="n">
-        <v>2.52667427062988</v>
+        <v>2.52667450904846</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>2.85800004005432</v>
       </c>
       <c r="G141" t="n">
-        <v>2.57349824905396</v>
+        <v>2.57349801063538</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>2.8659999370575</v>
       </c>
       <c r="G142" t="n">
-        <v>2.58070158958435</v>
+        <v>2.58070182800293</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>2.84599995613098</v>
       </c>
       <c r="G146" t="n">
-        <v>2.56269240379333</v>
+        <v>2.56269264221191</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>2.86800003051758</v>
       </c>
       <c r="G148" t="n">
-        <v>2.58250284194946</v>
+        <v>2.58250260353088</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G149" t="n">
-        <v>2.61131715774536</v>
+        <v>2.61131739616394</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G151" t="n">
-        <v>2.63833093643188</v>
+        <v>2.63833069801331</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G152" t="n">
-        <v>2.6563401222229</v>
+        <v>2.65633988380432</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>3.00799989700317</v>
       </c>
       <c r="G159" t="n">
-        <v>2.70856595039368</v>
+        <v>2.70856618881226</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>3.12800002098083</v>
       </c>
       <c r="G161" t="n">
-        <v>2.81662082672119</v>
+        <v>2.81662058830261</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>3.07399988174438</v>
       </c>
       <c r="G164" t="n">
-        <v>2.76799583435059</v>
+        <v>2.76799607276917</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>3.2260000705719</v>
       </c>
       <c r="G168" t="n">
-        <v>2.90486550331116</v>
+        <v>2.90486526489258</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G169" t="n">
-        <v>2.94448494911194</v>
+        <v>2.94448518753052</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G170" t="n">
-        <v>2.98950791358948</v>
+        <v>2.9895076751709</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>3.50600004196167</v>
       </c>
       <c r="G175" t="n">
-        <v>3.15699219703674</v>
+        <v>3.15699243545532</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>3.31800007820129</v>
       </c>
       <c r="G178" t="n">
-        <v>2.98770689964294</v>
+        <v>2.98770713806152</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>3.29200005531311</v>
       </c>
       <c r="G179" t="n">
-        <v>2.96429538726807</v>
+        <v>2.96429514884949</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G185" t="n">
-        <v>2.89045786857605</v>
+        <v>2.89045810699463</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>3.19600009918213</v>
       </c>
       <c r="G186" t="n">
-        <v>2.87785148620605</v>
+        <v>2.87785172462463</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>3.16599988937378</v>
       </c>
       <c r="G190" t="n">
-        <v>2.85083794593811</v>
+        <v>2.85083770751953</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>3.16799998283386</v>
       </c>
       <c r="G192" t="n">
-        <v>2.85263895988464</v>
+        <v>2.85263872146606</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>3.16400003433228</v>
       </c>
       <c r="G195" t="n">
-        <v>2.84903717041016</v>
+        <v>2.84903693199158</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G197" t="n">
-        <v>2.84993767738342</v>
+        <v>2.84993743896484</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G202" t="n">
-        <v>2.77339887619019</v>
+        <v>2.77339863777161</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G203" t="n">
-        <v>2.76439452171326</v>
+        <v>2.7643940448761</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G205" t="n">
-        <v>2.67434906959534</v>
+        <v>2.67434883117676</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G207" t="n">
-        <v>2.63833093643188</v>
+        <v>2.63833069801331</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G208" t="n">
-        <v>2.66534423828125</v>
+        <v>2.66534447669983</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G209" t="n">
-        <v>2.63833093643188</v>
+        <v>2.63833069801331</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G213" t="n">
-        <v>2.52127194404602</v>
+        <v>2.52127170562744</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>2.875</v>
       </c>
       <c r="G218" t="n">
-        <v>2.58880591392517</v>
+        <v>2.58880567550659</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G219" t="n">
-        <v>2.61131715774536</v>
+        <v>2.61131739616394</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G220" t="n">
-        <v>2.66534423828125</v>
+        <v>2.66534447669983</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G222" t="n">
-        <v>2.70586490631104</v>
+        <v>2.70586514472961</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G225" t="n">
-        <v>2.73287844657898</v>
+        <v>2.73287868499756</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>3.04500007629395</v>
       </c>
       <c r="G226" t="n">
-        <v>2.74188303947449</v>
+        <v>2.74188327789307</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G230" t="n">
-        <v>2.79140782356262</v>
+        <v>2.7914080619812</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G233" t="n">
-        <v>2.76439452171326</v>
+        <v>2.7643940448761</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G234" t="n">
-        <v>2.79140782356262</v>
+        <v>2.7914080619812</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G235" t="n">
-        <v>2.78690552711487</v>
+        <v>2.78690576553345</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G241" t="n">
-        <v>2.73287844657898</v>
+        <v>2.73287868499756</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G245" t="n">
-        <v>2.77339887619019</v>
+        <v>2.77339863777161</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G246" t="n">
-        <v>2.78690552711487</v>
+        <v>2.78690576553345</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G249" t="n">
-        <v>2.669846534729</v>
+        <v>2.66984677314758</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G250" t="n">
-        <v>2.6563401222229</v>
+        <v>2.65633988380432</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G251" t="n">
-        <v>2.66534423828125</v>
+        <v>2.66534447669983</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G252" t="n">
-        <v>2.6563401222229</v>
+        <v>2.65633988380432</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -21718,6 +21718,32 @@
         <v>2.89800000190735</v>
       </c>
       <c r="H821" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B822" t="n">
+        <v>84780</v>
+      </c>
+      <c r="C822" t="n">
+        <v>2.92000007629395</v>
+      </c>
+      <c r="D822" t="n">
+        <v>2.87400007247925</v>
+      </c>
+      <c r="E822" t="n">
+        <v>2.91199994087219</v>
+      </c>
+      <c r="F822" t="n">
+        <v>2.8840000629425</v>
+      </c>
+      <c r="G822" t="n">
+        <v>2.8840000629425</v>
+      </c>
+      <c r="H822" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/YACHT.MI.xlsx
+++ b/data/YACHT.MI.xlsx
@@ -499,7 +499,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G5" t="n">
-        <v>2.59330821037292</v>
+        <v>2.59330797195435</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G6" t="n">
-        <v>2.61131739616394</v>
+        <v>2.61131715774536</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G7" t="n">
-        <v>2.62032198905945</v>
+        <v>2.62032175064087</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>2.88199996948242</v>
       </c>
       <c r="G11" t="n">
-        <v>2.5951087474823</v>
+        <v>2.59510898590088</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>2.89800000190735</v>
       </c>
       <c r="G12" t="n">
-        <v>2.60951638221741</v>
+        <v>2.60951614379883</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>2.89599990844727</v>
       </c>
       <c r="G14" t="n">
-        <v>2.60771512985229</v>
+        <v>2.60771536827087</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G18" t="n">
-        <v>2.84543561935425</v>
+        <v>2.84543538093567</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G21" t="n">
-        <v>2.82742643356323</v>
+        <v>2.82742619514465</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G22" t="n">
-        <v>2.7914080619812</v>
+        <v>2.79140782356262</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>3.08200001716614</v>
       </c>
       <c r="G24" t="n">
-        <v>2.77519989013672</v>
+        <v>2.77519965171814</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>3.16599988937378</v>
       </c>
       <c r="G28" t="n">
-        <v>2.85083770751953</v>
+        <v>2.85083794593811</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>3.12199997901917</v>
       </c>
       <c r="G29" t="n">
-        <v>2.81121802330017</v>
+        <v>2.81121778488159</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>3.17799997329712</v>
       </c>
       <c r="G30" t="n">
-        <v>2.86164331436157</v>
+        <v>2.86164355278015</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G33" t="n">
-        <v>2.72837615013123</v>
+        <v>2.7283763885498</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G35" t="n">
-        <v>2.69235801696777</v>
+        <v>2.69235825538635</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>2.96199989318848</v>
       </c>
       <c r="G36" t="n">
-        <v>2.66714549064636</v>
+        <v>2.66714525222778</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>2.96199989318848</v>
       </c>
       <c r="G37" t="n">
-        <v>2.66714549064636</v>
+        <v>2.66714525222778</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G39" t="n">
-        <v>2.65633988380432</v>
+        <v>2.6563401222229</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>2.93400001525879</v>
       </c>
       <c r="G40" t="n">
-        <v>2.64193272590637</v>
+        <v>2.64193248748779</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>2.89800000190735</v>
       </c>
       <c r="G41" t="n">
-        <v>2.60951638221741</v>
+        <v>2.60951614379883</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>2.91599988937378</v>
       </c>
       <c r="G42" t="n">
-        <v>2.62572431564331</v>
+        <v>2.62572455406189</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G44" t="n">
-        <v>2.61131739616394</v>
+        <v>2.61131715774536</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>2.89800000190735</v>
       </c>
       <c r="G45" t="n">
-        <v>2.60951638221741</v>
+        <v>2.60951614379883</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>2.91400003433228</v>
       </c>
       <c r="G47" t="n">
-        <v>2.62392377853394</v>
+        <v>2.62392354011536</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G49" t="n">
-        <v>2.65633988380432</v>
+        <v>2.6563401222229</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G50" t="n">
-        <v>2.63833069801331</v>
+        <v>2.63833093643188</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>2.89199995994568</v>
       </c>
       <c r="G51" t="n">
-        <v>2.60411334037781</v>
+        <v>2.60411357879639</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>2.81200003623962</v>
       </c>
       <c r="G53" t="n">
-        <v>2.53207731246948</v>
+        <v>2.5320770740509</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G54" t="n">
-        <v>2.62032198905945</v>
+        <v>2.62032175064087</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G55" t="n">
-        <v>2.59330821037292</v>
+        <v>2.59330797195435</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G57" t="n">
-        <v>2.59330821037292</v>
+        <v>2.59330797195435</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G58" t="n">
-        <v>2.61131739616394</v>
+        <v>2.61131715774536</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>2.93600010871887</v>
       </c>
       <c r="G59" t="n">
-        <v>2.64373350143433</v>
+        <v>2.64373373985291</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G60" t="n">
-        <v>2.61131739616394</v>
+        <v>2.61131715774536</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G61" t="n">
-        <v>2.65633988380432</v>
+        <v>2.6563401222229</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G64" t="n">
-        <v>2.67434883117676</v>
+        <v>2.67434906959534</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>2.88599991798401</v>
       </c>
       <c r="G65" t="n">
-        <v>2.59871077537537</v>
+        <v>2.59871053695679</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G66" t="n">
-        <v>2.61131739616394</v>
+        <v>2.61131715774536</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>2.84599995613098</v>
       </c>
       <c r="G67" t="n">
-        <v>2.56269264221191</v>
+        <v>2.56269240379333</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>2.80399990081787</v>
       </c>
       <c r="G68" t="n">
-        <v>2.52487373352051</v>
+        <v>2.52487325668335</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>2.85800004005432</v>
       </c>
       <c r="G69" t="n">
-        <v>2.57349801063538</v>
+        <v>2.57349824905396</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.81399989128113</v>
       </c>
       <c r="G75" t="n">
-        <v>2.53387832641602</v>
+        <v>2.53387808799744</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>2.81200003623962</v>
       </c>
       <c r="G79" t="n">
-        <v>2.53207731246948</v>
+        <v>2.5320770740509</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G83" t="n">
-        <v>2.52127170562744</v>
+        <v>2.52127194404602</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>2.73399996757507</v>
       </c>
       <c r="G85" t="n">
-        <v>2.46184158325195</v>
+        <v>2.46184182167053</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>2.76399993896484</v>
       </c>
       <c r="G86" t="n">
-        <v>2.48885536193848</v>
+        <v>2.4888551235199</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>2.77600002288818</v>
       </c>
       <c r="G91" t="n">
-        <v>2.49966073036194</v>
+        <v>2.49966096878052</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.84599995613098</v>
       </c>
       <c r="G94" t="n">
-        <v>2.56269264221191</v>
+        <v>2.56269240379333</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G100" t="n">
-        <v>2.62032198905945</v>
+        <v>2.62032175064087</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.93799996376038</v>
       </c>
       <c r="G101" t="n">
-        <v>2.64553451538086</v>
+        <v>2.64553427696228</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G103" t="n">
-        <v>2.72837615013123</v>
+        <v>2.7283763885498</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G106" t="n">
-        <v>2.61131739616394</v>
+        <v>2.61131715774536</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>2.90400004386902</v>
       </c>
       <c r="G108" t="n">
-        <v>2.61491918563843</v>
+        <v>2.61491894721985</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G109" t="n">
-        <v>2.69235801696777</v>
+        <v>2.69235825538635</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>3</v>
       </c>
       <c r="G112" t="n">
-        <v>2.70136260986328</v>
+        <v>2.7013623714447</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G113" t="n">
-        <v>2.62032198905945</v>
+        <v>2.62032175064087</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G116" t="n">
-        <v>2.65633988380432</v>
+        <v>2.6563401222229</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>2.98799991607666</v>
       </c>
       <c r="G118" t="n">
-        <v>2.69055700302124</v>
+        <v>2.69055724143982</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G125" t="n">
-        <v>2.65633988380432</v>
+        <v>2.6563401222229</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>2.99200010299683</v>
       </c>
       <c r="G126" t="n">
-        <v>2.69415926933289</v>
+        <v>2.69415903091431</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G131" t="n">
-        <v>2.62032198905945</v>
+        <v>2.62032175064087</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G132" t="n">
-        <v>2.59330821037292</v>
+        <v>2.59330797195435</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>2.80599999427795</v>
       </c>
       <c r="G136" t="n">
-        <v>2.52667450904846</v>
+        <v>2.52667427062988</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>2.85800004005432</v>
       </c>
       <c r="G141" t="n">
-        <v>2.57349801063538</v>
+        <v>2.57349824905396</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>2.8659999370575</v>
       </c>
       <c r="G142" t="n">
-        <v>2.58070182800293</v>
+        <v>2.58070158958435</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>2.84599995613098</v>
       </c>
       <c r="G146" t="n">
-        <v>2.56269264221191</v>
+        <v>2.56269240379333</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>2.86800003051758</v>
       </c>
       <c r="G148" t="n">
-        <v>2.58250260353088</v>
+        <v>2.58250284194946</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G149" t="n">
-        <v>2.61131739616394</v>
+        <v>2.61131715774536</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G151" t="n">
-        <v>2.63833069801331</v>
+        <v>2.63833093643188</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G152" t="n">
-        <v>2.65633988380432</v>
+        <v>2.6563401222229</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>3.00799989700317</v>
       </c>
       <c r="G159" t="n">
-        <v>2.70856618881226</v>
+        <v>2.70856595039368</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>3.12800002098083</v>
       </c>
       <c r="G161" t="n">
-        <v>2.81662058830261</v>
+        <v>2.81662082672119</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>3.07399988174438</v>
       </c>
       <c r="G164" t="n">
-        <v>2.76799607276917</v>
+        <v>2.76799583435059</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>3.2260000705719</v>
       </c>
       <c r="G168" t="n">
-        <v>2.90486526489258</v>
+        <v>2.90486550331116</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G169" t="n">
-        <v>2.94448518753052</v>
+        <v>2.94448494911194</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G170" t="n">
-        <v>2.9895076751709</v>
+        <v>2.98950791358948</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>3.50600004196167</v>
       </c>
       <c r="G175" t="n">
-        <v>3.15699243545532</v>
+        <v>3.15699219703674</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>3.31800007820129</v>
       </c>
       <c r="G178" t="n">
-        <v>2.98770713806152</v>
+        <v>2.98770689964294</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>3.29200005531311</v>
       </c>
       <c r="G179" t="n">
-        <v>2.96429514884949</v>
+        <v>2.96429538726807</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G185" t="n">
-        <v>2.89045810699463</v>
+        <v>2.89045786857605</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>3.19600009918213</v>
       </c>
       <c r="G186" t="n">
-        <v>2.87785172462463</v>
+        <v>2.87785148620605</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>3.16599988937378</v>
       </c>
       <c r="G190" t="n">
-        <v>2.85083770751953</v>
+        <v>2.85083794593811</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>3.16799998283386</v>
       </c>
       <c r="G192" t="n">
-        <v>2.85263872146606</v>
+        <v>2.85263895988464</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>3.16400003433228</v>
       </c>
       <c r="G195" t="n">
-        <v>2.84903693199158</v>
+        <v>2.84903717041016</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G197" t="n">
-        <v>2.84993743896484</v>
+        <v>2.84993767738342</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G202" t="n">
-        <v>2.77339863777161</v>
+        <v>2.77339887619019</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G203" t="n">
-        <v>2.7643940448761</v>
+        <v>2.76439452171326</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G205" t="n">
-        <v>2.67434883117676</v>
+        <v>2.67434906959534</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G207" t="n">
-        <v>2.63833069801331</v>
+        <v>2.63833093643188</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G208" t="n">
-        <v>2.66534447669983</v>
+        <v>2.66534423828125</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G209" t="n">
-        <v>2.63833069801331</v>
+        <v>2.63833093643188</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G213" t="n">
-        <v>2.52127170562744</v>
+        <v>2.52127194404602</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>2.875</v>
       </c>
       <c r="G218" t="n">
-        <v>2.58880567550659</v>
+        <v>2.58880591392517</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G219" t="n">
-        <v>2.61131739616394</v>
+        <v>2.61131715774536</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G220" t="n">
-        <v>2.66534447669983</v>
+        <v>2.66534423828125</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G222" t="n">
-        <v>2.70586514472961</v>
+        <v>2.70586490631104</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G225" t="n">
-        <v>2.73287868499756</v>
+        <v>2.73287844657898</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>3.04500007629395</v>
       </c>
       <c r="G226" t="n">
-        <v>2.74188327789307</v>
+        <v>2.74188303947449</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G230" t="n">
-        <v>2.7914080619812</v>
+        <v>2.79140782356262</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G233" t="n">
-        <v>2.7643940448761</v>
+        <v>2.76439452171326</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G234" t="n">
-        <v>2.7914080619812</v>
+        <v>2.79140782356262</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G235" t="n">
-        <v>2.78690576553345</v>
+        <v>2.78690552711487</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G241" t="n">
-        <v>2.73287868499756</v>
+        <v>2.73287844657898</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G245" t="n">
-        <v>2.77339863777161</v>
+        <v>2.77339887619019</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G246" t="n">
-        <v>2.78690576553345</v>
+        <v>2.78690552711487</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G249" t="n">
-        <v>2.66984677314758</v>
+        <v>2.669846534729</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G250" t="n">
-        <v>2.65633988380432</v>
+        <v>2.6563401222229</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G251" t="n">
-        <v>2.66534447669983</v>
+        <v>2.66534423828125</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G252" t="n">
-        <v>2.65633988380432</v>
+        <v>2.6563401222229</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -21744,6 +21744,32 @@
         <v>2.8840000629425</v>
       </c>
       <c r="H822" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B823" t="n">
+        <v>140996</v>
+      </c>
+      <c r="C823" t="n">
+        <v>2.92000007629395</v>
+      </c>
+      <c r="D823" t="n">
+        <v>2.88000011444092</v>
+      </c>
+      <c r="E823" t="n">
+        <v>2.89800000190735</v>
+      </c>
+      <c r="F823" t="n">
+        <v>2.8840000629425</v>
+      </c>
+      <c r="G823" t="n">
+        <v>2.8840000629425</v>
+      </c>
+      <c r="H823" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/YACHT.MI.xlsx
+++ b/data/YACHT.MI.xlsx
@@ -421,7 +421,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G2" t="n">
-        <v>2.68335342407227</v>
+        <v>2.68335366249084</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6293261051178</v>
+        <v>2.62932634353638</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G5" t="n">
-        <v>2.59330797195435</v>
+        <v>2.59330821037292</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G8" t="n">
-        <v>2.6293261051178</v>
+        <v>2.62932634353638</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G10" t="n">
-        <v>2.6293261051178</v>
+        <v>2.62932634353638</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>2.89800000190735</v>
       </c>
       <c r="G12" t="n">
-        <v>2.60951614379883</v>
+        <v>2.60951638221741</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>2.90199995040894</v>
       </c>
       <c r="G15" t="n">
-        <v>2.61311793327332</v>
+        <v>2.61311817169189</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G16" t="n">
-        <v>2.6293261051178</v>
+        <v>2.62932634353638</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G22" t="n">
-        <v>2.79140782356262</v>
+        <v>2.7914080619812</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>3.08200001716614</v>
       </c>
       <c r="G24" t="n">
-        <v>2.77519965171814</v>
+        <v>2.77519989013672</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>3.01600003242493</v>
       </c>
       <c r="G34" t="n">
-        <v>2.71576976776123</v>
+        <v>2.71577000617981</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G35" t="n">
-        <v>2.69235825538635</v>
+        <v>2.69235801696777</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>2.96199989318848</v>
       </c>
       <c r="G36" t="n">
-        <v>2.66714525222778</v>
+        <v>2.66714549064636</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>2.96199989318848</v>
       </c>
       <c r="G37" t="n">
-        <v>2.66714525222778</v>
+        <v>2.66714549064636</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G38" t="n">
-        <v>2.6293261051178</v>
+        <v>2.62932634353638</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>2.89800000190735</v>
       </c>
       <c r="G41" t="n">
-        <v>2.60951614379883</v>
+        <v>2.60951638221741</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>2.91599988937378</v>
       </c>
       <c r="G42" t="n">
-        <v>2.62572455406189</v>
+        <v>2.62572431564331</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>2.89800000190735</v>
       </c>
       <c r="G45" t="n">
-        <v>2.60951614379883</v>
+        <v>2.60951638221741</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>2.81200003623962</v>
       </c>
       <c r="G53" t="n">
-        <v>2.5320770740509</v>
+        <v>2.53207731246948</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G55" t="n">
-        <v>2.59330797195435</v>
+        <v>2.59330821037292</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G57" t="n">
-        <v>2.59330797195435</v>
+        <v>2.59330821037292</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>3.0239999294281</v>
       </c>
       <c r="G62" t="n">
-        <v>2.72297334671021</v>
+        <v>2.72297358512878</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>2.88599991798401</v>
       </c>
       <c r="G65" t="n">
-        <v>2.59871053695679</v>
+        <v>2.59871077537537</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>2.80399990081787</v>
       </c>
       <c r="G68" t="n">
-        <v>2.52487325668335</v>
+        <v>2.52487349510193</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>2.85800004005432</v>
       </c>
       <c r="G69" t="n">
-        <v>2.57349824905396</v>
+        <v>2.57349801063538</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G70" t="n">
-        <v>2.53928065299988</v>
+        <v>2.53928089141846</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>2.81599998474121</v>
       </c>
       <c r="G71" t="n">
-        <v>2.53567910194397</v>
+        <v>2.53567886352539</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>2.83599996566772</v>
       </c>
       <c r="G78" t="n">
-        <v>2.55368804931641</v>
+        <v>2.55368828773499</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>2.81200003623962</v>
       </c>
       <c r="G79" t="n">
-        <v>2.5320770740509</v>
+        <v>2.53207731246948</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>2.76399993896484</v>
       </c>
       <c r="G86" t="n">
-        <v>2.4888551235199</v>
+        <v>2.48885536193848</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G99" t="n">
-        <v>2.54828524589539</v>
+        <v>2.54828548431396</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.93799996376038</v>
       </c>
       <c r="G101" t="n">
-        <v>2.64553427696228</v>
+        <v>2.64553451538086</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>3.07599997520447</v>
       </c>
       <c r="G102" t="n">
-        <v>2.7697970867157</v>
+        <v>2.76979732513428</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>3.04800009727478</v>
       </c>
       <c r="G105" t="n">
-        <v>2.74458456039429</v>
+        <v>2.74458432197571</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.95600008964539</v>
       </c>
       <c r="G107" t="n">
-        <v>2.66174268722534</v>
+        <v>2.66174292564392</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G109" t="n">
-        <v>2.69235825538635</v>
+        <v>2.69235801696777</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>2.9760000705719</v>
       </c>
       <c r="G110" t="n">
-        <v>2.67975163459778</v>
+        <v>2.67975187301636</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>2.96799993515015</v>
       </c>
       <c r="G111" t="n">
-        <v>2.6725480556488</v>
+        <v>2.67254829406738</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>3</v>
       </c>
       <c r="G112" t="n">
-        <v>2.7013623714447</v>
+        <v>2.70136260986328</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>2.95600008964539</v>
       </c>
       <c r="G114" t="n">
-        <v>2.66174268722534</v>
+        <v>2.66174292564392</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>2.96799993515015</v>
       </c>
       <c r="G115" t="n">
-        <v>2.6725480556488</v>
+        <v>2.67254829406738</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>2.98600006103516</v>
       </c>
       <c r="G117" t="n">
-        <v>2.68875622749329</v>
+        <v>2.68875646591187</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>2.9760000705719</v>
       </c>
       <c r="G119" t="n">
-        <v>2.67975163459778</v>
+        <v>2.67975187301636</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2.95600008964539</v>
       </c>
       <c r="G120" t="n">
-        <v>2.66174268722534</v>
+        <v>2.66174292564392</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G121" t="n">
-        <v>2.68335342407227</v>
+        <v>2.68335366249084</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>2.9539999961853</v>
       </c>
       <c r="G123" t="n">
-        <v>2.65994167327881</v>
+        <v>2.65994143486023</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>2.96600008010864</v>
       </c>
       <c r="G124" t="n">
-        <v>2.67074728012085</v>
+        <v>2.67074704170227</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G128" t="n">
-        <v>2.68335342407227</v>
+        <v>2.68335366249084</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G132" t="n">
-        <v>2.59330797195435</v>
+        <v>2.59330821037292</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G134" t="n">
-        <v>2.54828524589539</v>
+        <v>2.54828548431396</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>2.80599999427795</v>
       </c>
       <c r="G136" t="n">
-        <v>2.52667427062988</v>
+        <v>2.52667450904846</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>2.85800004005432</v>
       </c>
       <c r="G141" t="n">
-        <v>2.57349824905396</v>
+        <v>2.57349801063538</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G144" t="n">
-        <v>2.53928065299988</v>
+        <v>2.53928089141846</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>2.92600011825562</v>
       </c>
       <c r="G155" t="n">
-        <v>2.63472890853882</v>
+        <v>2.6347291469574</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>2.81599998474121</v>
       </c>
       <c r="G157" t="n">
-        <v>2.53567910194397</v>
+        <v>2.53567886352539</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>3.12800002098083</v>
       </c>
       <c r="G161" t="n">
-        <v>2.81662082672119</v>
+        <v>2.81662058830261</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>3.07399988174438</v>
       </c>
       <c r="G164" t="n">
-        <v>2.76799583435059</v>
+        <v>2.76799607276917</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G169" t="n">
-        <v>2.94448494911194</v>
+        <v>2.94448518753052</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>3.13199996948242</v>
       </c>
       <c r="G181" t="n">
-        <v>2.8202223777771</v>
+        <v>2.82022261619568</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>3.13199996948242</v>
       </c>
       <c r="G183" t="n">
-        <v>2.8202223777771</v>
+        <v>2.82022261619568</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>3.19600009918213</v>
       </c>
       <c r="G186" t="n">
-        <v>2.87785148620605</v>
+        <v>2.87785172462463</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>3.13199996948242</v>
       </c>
       <c r="G187" t="n">
-        <v>2.8202223777771</v>
+        <v>2.82022261619568</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>3.14599990844727</v>
       </c>
       <c r="G188" t="n">
-        <v>2.83282899856567</v>
+        <v>2.83282876014709</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G197" t="n">
-        <v>2.84993767738342</v>
+        <v>2.84993743896484</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G200" t="n">
-        <v>2.79591035842896</v>
+        <v>2.79591012001038</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G212" t="n">
-        <v>2.54828524589539</v>
+        <v>2.54828548431396</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G217" t="n">
-        <v>2.54828524589539</v>
+        <v>2.54828548431396</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G221" t="n">
-        <v>2.68785572052002</v>
+        <v>2.68785548210144</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G222" t="n">
-        <v>2.70586490631104</v>
+        <v>2.70586514472961</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G223" t="n">
-        <v>2.68785572052002</v>
+        <v>2.68785548210144</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G230" t="n">
-        <v>2.79140782356262</v>
+        <v>2.7914080619812</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G234" t="n">
-        <v>2.79140782356262</v>
+        <v>2.7914080619812</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G235" t="n">
-        <v>2.78690552711487</v>
+        <v>2.78690576553345</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G244" t="n">
-        <v>2.80041265487671</v>
+        <v>2.80041241645813</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G246" t="n">
-        <v>2.78690552711487</v>
+        <v>2.78690576553345</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G253" t="n">
-        <v>2.68785572052002</v>
+        <v>2.68785548210144</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G256" t="n">
-        <v>2.63852882385254</v>
+        <v>2.63852858543396</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G257" t="n">
-        <v>2.63387513160706</v>
+        <v>2.63387537002563</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G264" t="n">
-        <v>2.63387513160706</v>
+        <v>2.63387537002563</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G265" t="n">
-        <v>2.61991500854492</v>
+        <v>2.61991477012634</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G266" t="n">
-        <v>2.61991500854492</v>
+        <v>2.61991477012634</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G269" t="n">
-        <v>2.62456798553467</v>
+        <v>2.62456822395325</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G270" t="n">
-        <v>2.62456798553467</v>
+        <v>2.62456822395325</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G275" t="n">
-        <v>2.62456798553467</v>
+        <v>2.62456822395325</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G276" t="n">
-        <v>2.61991500854492</v>
+        <v>2.61991477012634</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G285" t="n">
-        <v>2.49427080154419</v>
+        <v>2.49427056312561</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G287" t="n">
-        <v>2.52684497833252</v>
+        <v>2.52684473991394</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G288" t="n">
-        <v>2.54545879364014</v>
+        <v>2.54545903205872</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G289" t="n">
-        <v>2.54080533981323</v>
+        <v>2.54080557823181</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G290" t="n">
-        <v>2.531498670578</v>
+        <v>2.53149843215942</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G295" t="n">
-        <v>2.61991500854492</v>
+        <v>2.61991477012634</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G296" t="n">
-        <v>2.61991500854492</v>
+        <v>2.61991477012634</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G300" t="n">
-        <v>2.61991500854492</v>
+        <v>2.61991477012634</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G307" t="n">
-        <v>2.33605170249939</v>
+        <v>2.33605194091797</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G308" t="n">
-        <v>2.31743788719177</v>
+        <v>2.31743812561035</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G310" t="n">
-        <v>2.33605170249939</v>
+        <v>2.33605194091797</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>2.56500005722046</v>
       </c>
       <c r="G311" t="n">
-        <v>2.38724040985107</v>
+        <v>2.3872401714325</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>2.56500005722046</v>
       </c>
       <c r="G313" t="n">
-        <v>2.38724040985107</v>
+        <v>2.3872401714325</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G318" t="n">
-        <v>2.42912149429321</v>
+        <v>2.42912173271179</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G319" t="n">
-        <v>2.46169590950012</v>
+        <v>2.4616961479187</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G324" t="n">
-        <v>2.63387513160706</v>
+        <v>2.63387537002563</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G326" t="n">
-        <v>2.54080533981323</v>
+        <v>2.54080557823181</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G331" t="n">
-        <v>2.52684497833252</v>
+        <v>2.52684473991394</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G341" t="n">
-        <v>2.63852882385254</v>
+        <v>2.63852858543396</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G342" t="n">
-        <v>2.63387513160706</v>
+        <v>2.63387537002563</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G347" t="n">
-        <v>2.49427080154419</v>
+        <v>2.49427056312561</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G351" t="n">
-        <v>2.71763801574707</v>
+        <v>2.71763825416565</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G353" t="n">
-        <v>2.63387513160706</v>
+        <v>2.63387537002563</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G357" t="n">
-        <v>2.61991500854492</v>
+        <v>2.61991477012634</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G359" t="n">
-        <v>2.531498670578</v>
+        <v>2.53149843215942</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>2.70499992370605</v>
       </c>
       <c r="G360" t="n">
-        <v>2.51753783226013</v>
+        <v>2.51753807067871</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G364" t="n">
-        <v>2.63852882385254</v>
+        <v>2.63852858543396</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G373" t="n">
-        <v>2.61991500854492</v>
+        <v>2.61991477012634</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G376" t="n">
-        <v>2.68041014671326</v>
+        <v>2.68041038513184</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G384" t="n">
-        <v>2.62456798553467</v>
+        <v>2.62456822395325</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G385" t="n">
-        <v>2.61991500854492</v>
+        <v>2.61991477012634</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G386" t="n">
-        <v>2.62922167778015</v>
+        <v>2.62922191619873</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G388" t="n">
-        <v>2.63852882385254</v>
+        <v>2.63852858543396</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>2.89499998092651</v>
       </c>
       <c r="G397" t="n">
-        <v>2.69437074661255</v>
+        <v>2.69437050819397</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G399" t="n">
-        <v>2.71763801574707</v>
+        <v>2.71763825416565</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G406" t="n">
-        <v>2.78278708457947</v>
+        <v>2.78278684616089</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>2.93499994277954</v>
       </c>
       <c r="G408" t="n">
-        <v>2.73159861564636</v>
+        <v>2.73159837722778</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>2.93499994277954</v>
       </c>
       <c r="G416" t="n">
-        <v>2.73159861564636</v>
+        <v>2.73159837722778</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G423" t="n">
-        <v>2.63387513160706</v>
+        <v>2.63387537002563</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G425" t="n">
-        <v>2.71763801574707</v>
+        <v>2.71763825416565</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G428" t="n">
-        <v>2.63852882385254</v>
+        <v>2.63852858543396</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G433" t="n">
-        <v>2.54080533981323</v>
+        <v>2.54080557823181</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>2.70499992370605</v>
       </c>
       <c r="G434" t="n">
-        <v>2.51753783226013</v>
+        <v>2.51753807067871</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>2.70499992370605</v>
       </c>
       <c r="G436" t="n">
-        <v>2.51753783226013</v>
+        <v>2.51753807067871</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G437" t="n">
-        <v>2.54545879364014</v>
+        <v>2.54545903205872</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G440" t="n">
-        <v>2.54080533981323</v>
+        <v>2.54080557823181</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G445" t="n">
-        <v>2.42912149429321</v>
+        <v>2.42912173271179</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G446" t="n">
-        <v>2.4384286403656</v>
+        <v>2.43842840194702</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>2.5</v>
       </c>
       <c r="G459" t="n">
-        <v>2.32674503326416</v>
+        <v>2.32674479484558</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G461" t="n">
-        <v>2.33232927322388</v>
+        <v>2.3323290348053</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>2.4539999961853</v>
       </c>
       <c r="G462" t="n">
-        <v>2.28393268585205</v>
+        <v>2.28393292427063</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>2.59200000762939</v>
       </c>
       <c r="G464" t="n">
-        <v>2.41236901283264</v>
+        <v>2.41236925125122</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>2.61400008201599</v>
       </c>
       <c r="G470" t="n">
-        <v>2.43284463882446</v>
+        <v>2.43284440040588</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>2.58599996566772</v>
       </c>
       <c r="G472" t="n">
-        <v>2.40678477287292</v>
+        <v>2.4067850112915</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>2.72399997711182</v>
       </c>
       <c r="G482" t="n">
-        <v>2.53522109985352</v>
+        <v>2.53522133827209</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>2.81200003623962</v>
       </c>
       <c r="G487" t="n">
-        <v>2.61712265014648</v>
+        <v>2.61712288856506</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -21770,6 +21770,32 @@
         <v>2.8840000629425</v>
       </c>
       <c r="H823" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B824" t="n">
+        <v>133012</v>
+      </c>
+      <c r="C824" t="n">
+        <v>2.91599988937378</v>
+      </c>
+      <c r="D824" t="n">
+        <v>2.86999988555908</v>
+      </c>
+      <c r="E824" t="n">
+        <v>2.89800000190735</v>
+      </c>
+      <c r="F824" t="n">
+        <v>2.86999988555908</v>
+      </c>
+      <c r="G824" t="n">
+        <v>2.86999988555908</v>
+      </c>
+      <c r="H824" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/YACHT.MI.xlsx
+++ b/data/YACHT.MI.xlsx
@@ -21799,6 +21799,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="825">
+      <c r="A825" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B825" t="n">
+        <v>75442</v>
+      </c>
+      <c r="C825" t="n">
+        <v>2.89199995994568</v>
+      </c>
+      <c r="D825" t="n">
+        <v>2.85199999809265</v>
+      </c>
+      <c r="E825" t="n">
+        <v>2.89199995994568</v>
+      </c>
+      <c r="F825" t="n">
+        <v>2.85599994659424</v>
+      </c>
+      <c r="G825" t="n">
+        <v>2.85599994659424</v>
+      </c>
+      <c r="H825" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/YACHT.MI.xlsx
+++ b/data/YACHT.MI.xlsx
@@ -21877,6 +21877,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="828">
+      <c r="A828" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B828" t="n">
+        <v>176965</v>
+      </c>
+      <c r="C828" t="n">
+        <v>2.80599999427795</v>
+      </c>
+      <c r="D828" t="n">
+        <v>2.73000001907349</v>
+      </c>
+      <c r="E828" t="n">
+        <v>2.78399991989136</v>
+      </c>
+      <c r="F828" t="n">
+        <v>2.73000001907349</v>
+      </c>
+      <c r="G828" t="n">
+        <v>2.73000001907349</v>
+      </c>
+      <c r="H828" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/YACHT.MI.xlsx
+++ b/data/YACHT.MI.xlsx
@@ -19478,8 +19478,31 @@
       <c r="E831" t="n">
         <v>2.63000011444092</v>
       </c>
-      <c r="F831"/>
+      <c r="F831" t="n">
+        <v>2.66000008583069</v>
+      </c>
       <c r="G831" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B832" t="n">
+        <v>135089</v>
+      </c>
+      <c r="C832" t="n">
+        <v>2.74600005149841</v>
+      </c>
+      <c r="D832" t="n">
+        <v>2.65599989891052</v>
+      </c>
+      <c r="E832" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="F832"/>
+      <c r="G832" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/YACHT.MI.xlsx
+++ b/data/YACHT.MI.xlsx
@@ -19501,8 +19501,31 @@
       <c r="E832" t="n">
         <v>2.66000008583069</v>
       </c>
-      <c r="F832"/>
+      <c r="F832" t="n">
+        <v>2.71199989318848</v>
+      </c>
       <c r="G832" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B833" t="n">
+        <v>383969</v>
+      </c>
+      <c r="C833" t="n">
+        <v>2.71000003814697</v>
+      </c>
+      <c r="D833" t="n">
+        <v>2.60999989509583</v>
+      </c>
+      <c r="E833" t="n">
+        <v>2.71000003814697</v>
+      </c>
+      <c r="F833"/>
+      <c r="G833" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/YACHT.MI.xlsx
+++ b/data/YACHT.MI.xlsx
@@ -19524,8 +19524,31 @@
       <c r="E833" t="n">
         <v>2.71000003814697</v>
       </c>
-      <c r="F833"/>
+      <c r="F833" t="n">
+        <v>2.61400008201599</v>
+      </c>
       <c r="G833" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B834" t="n">
+        <v>371243</v>
+      </c>
+      <c r="C834" t="n">
+        <v>2.70000004768372</v>
+      </c>
+      <c r="D834" t="n">
+        <v>2.60999989509583</v>
+      </c>
+      <c r="E834" t="n">
+        <v>2.69000005722046</v>
+      </c>
+      <c r="F834"/>
+      <c r="G834" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/YACHT.MI.xlsx
+++ b/data/YACHT.MI.xlsx
@@ -19547,8 +19547,31 @@
       <c r="E834" t="n">
         <v>2.69000005722046</v>
       </c>
-      <c r="F834"/>
+      <c r="F834" t="n">
+        <v>2.65000009536743</v>
+      </c>
       <c r="G834" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B835" t="n">
+        <v>139481</v>
+      </c>
+      <c r="C835" t="n">
+        <v>2.73000001907349</v>
+      </c>
+      <c r="D835" t="n">
+        <v>2.64400005340576</v>
+      </c>
+      <c r="E835" t="n">
+        <v>2.73000001907349</v>
+      </c>
+      <c r="F835"/>
+      <c r="G835" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/YACHT.MI.xlsx
+++ b/data/YACHT.MI.xlsx
@@ -19577,6 +19577,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="836">
+      <c r="A836" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B836" t="n">
+        <v>252471</v>
+      </c>
+      <c r="C836" t="n">
+        <v>2.75999999046326</v>
+      </c>
+      <c r="D836" t="n">
+        <v>2.61999988555908</v>
+      </c>
+      <c r="E836" t="n">
+        <v>2.61999988555908</v>
+      </c>
+      <c r="F836" t="n">
+        <v>2.73000001907349</v>
+      </c>
+      <c r="G836" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/YACHT.MI.xlsx
+++ b/data/YACHT.MI.xlsx
@@ -447,7 +447,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G3" t="n">
-        <v>2.62932634353638</v>
+        <v>2.6293261051178</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G7" t="n">
-        <v>2.62032175064087</v>
+        <v>2.62032198905945</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G8" t="n">
-        <v>2.62932634353638</v>
+        <v>2.6293261051178</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G9" t="n">
-        <v>2.60231256484985</v>
+        <v>2.60231280326843</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G10" t="n">
-        <v>2.62932634353638</v>
+        <v>2.6293261051178</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>2.88199996948242</v>
       </c>
       <c r="G11" t="n">
-        <v>2.59510898590088</v>
+        <v>2.5951087474823</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G13" t="n">
-        <v>2.60231256484985</v>
+        <v>2.60231280326843</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G16" t="n">
-        <v>2.62932634353638</v>
+        <v>2.6293261051178</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G18" t="n">
-        <v>2.84543538093567</v>
+        <v>2.84543561935425</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G20" t="n">
-        <v>2.83643078804016</v>
+        <v>2.83643102645874</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>3.12199997901917</v>
       </c>
       <c r="G29" t="n">
-        <v>2.81121778488159</v>
+        <v>2.81121802330017</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>3.17799997329712</v>
       </c>
       <c r="G30" t="n">
-        <v>2.86164355278015</v>
+        <v>2.86164331436157</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G32" t="n">
-        <v>2.74638509750366</v>
+        <v>2.74638533592224</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>2.96199989318848</v>
       </c>
       <c r="G36" t="n">
-        <v>2.66714525222778</v>
+        <v>2.66714549064636</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>2.96199989318848</v>
       </c>
       <c r="G37" t="n">
-        <v>2.66714525222778</v>
+        <v>2.66714549064636</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G38" t="n">
-        <v>2.62932634353638</v>
+        <v>2.6293261051178</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>2.93400001525879</v>
       </c>
       <c r="G40" t="n">
-        <v>2.64193248748779</v>
+        <v>2.64193272590637</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>2.91400003433228</v>
       </c>
       <c r="G47" t="n">
-        <v>2.62392354011536</v>
+        <v>2.62392377853394</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>2.90799999237061</v>
       </c>
       <c r="G48" t="n">
-        <v>2.61852073669434</v>
+        <v>2.61852097511292</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G50" t="n">
-        <v>2.63833093643188</v>
+        <v>2.63833069801331</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G52" t="n">
-        <v>2.58430361747742</v>
+        <v>2.58430337905884</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G54" t="n">
-        <v>2.62032175064087</v>
+        <v>2.62032198905945</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G64" t="n">
-        <v>2.67434906959534</v>
+        <v>2.67434883117676</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>2.80399990081787</v>
       </c>
       <c r="G68" t="n">
-        <v>2.52487349510193</v>
+        <v>2.52487373352051</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G73" t="n">
-        <v>2.58430361747742</v>
+        <v>2.58430337905884</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.81399989128113</v>
       </c>
       <c r="G75" t="n">
-        <v>2.53387808799744</v>
+        <v>2.53387832641602</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G76" t="n">
-        <v>2.58430361747742</v>
+        <v>2.58430337905884</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G77" t="n">
-        <v>2.58430361747742</v>
+        <v>2.58430337905884</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>2.80800008773804</v>
       </c>
       <c r="G80" t="n">
-        <v>2.52847528457642</v>
+        <v>2.528475522995</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G83" t="n">
-        <v>2.52127194404602</v>
+        <v>2.52127170562744</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G84" t="n">
-        <v>2.48525357246399</v>
+        <v>2.48525381088257</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>2.76399993896484</v>
       </c>
       <c r="G86" t="n">
-        <v>2.4888551235199</v>
+        <v>2.48885536193848</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>2.74600005149841</v>
       </c>
       <c r="G88" t="n">
-        <v>2.47264719009399</v>
+        <v>2.47264742851257</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>2.74399995803833</v>
       </c>
       <c r="G89" t="n">
-        <v>2.47084641456604</v>
+        <v>2.47084617614746</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.84400010108948</v>
       </c>
       <c r="G97" t="n">
-        <v>2.56089210510254</v>
+        <v>2.56089186668396</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G99" t="n">
-        <v>2.54828548431396</v>
+        <v>2.54828524589539</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G100" t="n">
-        <v>2.62032175064087</v>
+        <v>2.62032198905945</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>3.07599997520447</v>
       </c>
       <c r="G102" t="n">
-        <v>2.76979732513428</v>
+        <v>2.7697970867157</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>2.90400004386902</v>
       </c>
       <c r="G108" t="n">
-        <v>2.61491894721985</v>
+        <v>2.61491918563843</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>2.9760000705719</v>
       </c>
       <c r="G110" t="n">
-        <v>2.67975187301636</v>
+        <v>2.67975163459778</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G113" t="n">
-        <v>2.62032175064087</v>
+        <v>2.62032198905945</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>2.98799991607666</v>
       </c>
       <c r="G118" t="n">
-        <v>2.69055724143982</v>
+        <v>2.69055700302124</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>2.9760000705719</v>
       </c>
       <c r="G119" t="n">
-        <v>2.67975187301636</v>
+        <v>2.67975163459778</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>2.96600008010864</v>
       </c>
       <c r="G124" t="n">
-        <v>2.67074704170227</v>
+        <v>2.67074728012085</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>2.99200010299683</v>
       </c>
       <c r="G126" t="n">
-        <v>2.69415903091431</v>
+        <v>2.69415926933289</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G127" t="n">
-        <v>2.7193717956543</v>
+        <v>2.71937155723572</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G131" t="n">
-        <v>2.62032175064087</v>
+        <v>2.62032198905945</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G134" t="n">
-        <v>2.54828548431396</v>
+        <v>2.54828524589539</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>2.8659999370575</v>
       </c>
       <c r="G142" t="n">
-        <v>2.58070158958435</v>
+        <v>2.58070182800293</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>2.84400010108948</v>
       </c>
       <c r="G143" t="n">
-        <v>2.56089210510254</v>
+        <v>2.56089186668396</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G147" t="n">
-        <v>2.58430361747742</v>
+        <v>2.58430337905884</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>2.90799999237061</v>
       </c>
       <c r="G150" t="n">
-        <v>2.61852073669434</v>
+        <v>2.61852097511292</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G151" t="n">
-        <v>2.63833093643188</v>
+        <v>2.63833069801331</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>2.92600011825562</v>
       </c>
       <c r="G155" t="n">
-        <v>2.6347291469574</v>
+        <v>2.63472890853882</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>2.88800001144409</v>
       </c>
       <c r="G156" t="n">
-        <v>2.60051202774048</v>
+        <v>2.6005117893219</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G160" t="n">
-        <v>2.73738050460815</v>
+        <v>2.73738074302673</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>3.11199998855591</v>
       </c>
       <c r="G162" t="n">
-        <v>2.80221343040466</v>
+        <v>2.80221366882324</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>3.07800006866455</v>
       </c>
       <c r="G163" t="n">
-        <v>2.77159786224365</v>
+        <v>2.77159810066223</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G166" t="n">
-        <v>2.87244915962219</v>
+        <v>2.87244892120361</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G170" t="n">
-        <v>2.98950791358948</v>
+        <v>2.9895076751709</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>3.50200009346008</v>
       </c>
       <c r="G172" t="n">
-        <v>3.15339064598083</v>
+        <v>3.15339088439941</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G177" t="n">
-        <v>3.06154417991638</v>
+        <v>3.06154441833496</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>3.25200009346008</v>
       </c>
       <c r="G180" t="n">
-        <v>2.92827701568604</v>
+        <v>2.92827725410461</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>3.13199996948242</v>
       </c>
       <c r="G181" t="n">
-        <v>2.82022261619568</v>
+        <v>2.8202223777771</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>3.13199996948242</v>
       </c>
       <c r="G183" t="n">
-        <v>2.82022261619568</v>
+        <v>2.8202223777771</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G185" t="n">
-        <v>2.89045786857605</v>
+        <v>2.89045810699463</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>3.13199996948242</v>
       </c>
       <c r="G187" t="n">
-        <v>2.82022261619568</v>
+        <v>2.8202223777771</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G189" t="n">
-        <v>2.80941724777222</v>
+        <v>2.80941700935364</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G193" t="n">
-        <v>2.83643078804016</v>
+        <v>2.83643102645874</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>3.16400003433228</v>
       </c>
       <c r="G195" t="n">
-        <v>2.84903717041016</v>
+        <v>2.84903693199158</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G196" t="n">
-        <v>2.80491495132446</v>
+        <v>2.80491471290588</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G198" t="n">
-        <v>2.83643078804016</v>
+        <v>2.83643102645874</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G199" t="n">
-        <v>2.80941724777222</v>
+        <v>2.80941700935364</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G203" t="n">
-        <v>2.76439428329468</v>
+        <v>2.7643940448761</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G204" t="n">
-        <v>2.74638509750366</v>
+        <v>2.74638533592224</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G205" t="n">
-        <v>2.67434906959534</v>
+        <v>2.67434883117676</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G207" t="n">
-        <v>2.63833093643188</v>
+        <v>2.63833069801331</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G209" t="n">
-        <v>2.63833093643188</v>
+        <v>2.63833069801331</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G212" t="n">
-        <v>2.54828548431396</v>
+        <v>2.54828524589539</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G213" t="n">
-        <v>2.52127194404602</v>
+        <v>2.52127170562744</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G216" t="n">
-        <v>2.58430361747742</v>
+        <v>2.58430337905884</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G217" t="n">
-        <v>2.54828548431396</v>
+        <v>2.54828524589539</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>2.875</v>
       </c>
       <c r="G218" t="n">
-        <v>2.58880591392517</v>
+        <v>2.58880567550659</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G225" t="n">
-        <v>2.73287844657898</v>
+        <v>2.73287868499756</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G227" t="n">
-        <v>2.80941724777222</v>
+        <v>2.80941700935364</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G229" t="n">
-        <v>2.80491495132446</v>
+        <v>2.80491471290588</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G233" t="n">
-        <v>2.76439428329468</v>
+        <v>2.7643940448761</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G240" t="n">
-        <v>2.71036696434021</v>
+        <v>2.71036720275879</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G241" t="n">
-        <v>2.73287844657898</v>
+        <v>2.73287868499756</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G244" t="n">
-        <v>2.80041241645813</v>
+        <v>2.80041265487671</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G247" t="n">
-        <v>2.7193717956543</v>
+        <v>2.71937155723572</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G249" t="n">
-        <v>2.669846534729</v>
+        <v>2.66984677314758</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G256" t="n">
-        <v>2.63852858543396</v>
+        <v>2.63852882385254</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G257" t="n">
-        <v>2.63387537002563</v>
+        <v>2.63387513160706</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G264" t="n">
-        <v>2.63387537002563</v>
+        <v>2.63387513160706</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G265" t="n">
-        <v>2.61991477012634</v>
+        <v>2.61991500854492</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G266" t="n">
-        <v>2.61991477012634</v>
+        <v>2.61991500854492</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G269" t="n">
-        <v>2.62456822395325</v>
+        <v>2.62456798553467</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G270" t="n">
-        <v>2.62456822395325</v>
+        <v>2.62456798553467</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G275" t="n">
-        <v>2.62456822395325</v>
+        <v>2.62456798553467</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G276" t="n">
-        <v>2.61991477012634</v>
+        <v>2.61991500854492</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G285" t="n">
-        <v>2.49427056312561</v>
+        <v>2.49427080154419</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G287" t="n">
-        <v>2.52684473991394</v>
+        <v>2.52684497833252</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G288" t="n">
-        <v>2.54545903205872</v>
+        <v>2.54545879364014</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G289" t="n">
-        <v>2.54080557823181</v>
+        <v>2.54080533981323</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G290" t="n">
-        <v>2.53149843215942</v>
+        <v>2.531498670578</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G295" t="n">
-        <v>2.61991477012634</v>
+        <v>2.61991500854492</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G296" t="n">
-        <v>2.61991477012634</v>
+        <v>2.61991500854492</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G300" t="n">
-        <v>2.61991477012634</v>
+        <v>2.61991500854492</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G307" t="n">
-        <v>2.33605194091797</v>
+        <v>2.33605170249939</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G308" t="n">
-        <v>2.31743812561035</v>
+        <v>2.31743788719177</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G310" t="n">
-        <v>2.33605194091797</v>
+        <v>2.33605170249939</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>2.56500005722046</v>
       </c>
       <c r="G311" t="n">
-        <v>2.3872401714325</v>
+        <v>2.38724040985107</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>2.56500005722046</v>
       </c>
       <c r="G313" t="n">
-        <v>2.3872401714325</v>
+        <v>2.38724040985107</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G318" t="n">
-        <v>2.42912173271179</v>
+        <v>2.42912149429321</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G319" t="n">
-        <v>2.4616961479187</v>
+        <v>2.46169590950012</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G324" t="n">
-        <v>2.63387537002563</v>
+        <v>2.63387513160706</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G326" t="n">
-        <v>2.54080557823181</v>
+        <v>2.54080533981323</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G331" t="n">
-        <v>2.52684473991394</v>
+        <v>2.52684497833252</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G341" t="n">
-        <v>2.63852858543396</v>
+        <v>2.63852882385254</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G342" t="n">
-        <v>2.63387537002563</v>
+        <v>2.63387513160706</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G347" t="n">
-        <v>2.49427056312561</v>
+        <v>2.49427080154419</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G351" t="n">
-        <v>2.71763825416565</v>
+        <v>2.71763801574707</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G353" t="n">
-        <v>2.63387537002563</v>
+        <v>2.63387513160706</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G357" t="n">
-        <v>2.61991477012634</v>
+        <v>2.61991500854492</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G359" t="n">
-        <v>2.53149843215942</v>
+        <v>2.531498670578</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>2.70499992370605</v>
       </c>
       <c r="G360" t="n">
-        <v>2.51753807067871</v>
+        <v>2.51753783226013</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G364" t="n">
-        <v>2.63852858543396</v>
+        <v>2.63852882385254</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G373" t="n">
-        <v>2.61991477012634</v>
+        <v>2.61991500854492</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G376" t="n">
-        <v>2.68041038513184</v>
+        <v>2.68041014671326</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G384" t="n">
-        <v>2.62456822395325</v>
+        <v>2.62456798553467</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G385" t="n">
-        <v>2.61991477012634</v>
+        <v>2.61991500854492</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G386" t="n">
-        <v>2.62922191619873</v>
+        <v>2.62922167778015</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G388" t="n">
-        <v>2.63852858543396</v>
+        <v>2.63852882385254</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>2.89499998092651</v>
       </c>
       <c r="G397" t="n">
-        <v>2.69437050819397</v>
+        <v>2.69437074661255</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G399" t="n">
-        <v>2.71763825416565</v>
+        <v>2.71763801574707</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G406" t="n">
-        <v>2.78278684616089</v>
+        <v>2.78278708457947</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>2.93499994277954</v>
       </c>
       <c r="G408" t="n">
-        <v>2.73159837722778</v>
+        <v>2.73159861564636</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>2.93499994277954</v>
       </c>
       <c r="G416" t="n">
-        <v>2.73159837722778</v>
+        <v>2.73159861564636</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G423" t="n">
-        <v>2.63387537002563</v>
+        <v>2.63387513160706</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G425" t="n">
-        <v>2.71763825416565</v>
+        <v>2.71763801574707</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G428" t="n">
-        <v>2.63852858543396</v>
+        <v>2.63852882385254</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G433" t="n">
-        <v>2.54080557823181</v>
+        <v>2.54080533981323</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>2.70499992370605</v>
       </c>
       <c r="G434" t="n">
-        <v>2.51753807067871</v>
+        <v>2.51753783226013</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>2.70499992370605</v>
       </c>
       <c r="G436" t="n">
-        <v>2.51753807067871</v>
+        <v>2.51753783226013</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G437" t="n">
-        <v>2.54545903205872</v>
+        <v>2.54545879364014</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G440" t="n">
-        <v>2.54080557823181</v>
+        <v>2.54080533981323</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G445" t="n">
-        <v>2.42912173271179</v>
+        <v>2.42912149429321</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G446" t="n">
-        <v>2.43842840194702</v>
+        <v>2.4384286403656</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>2.5</v>
       </c>
       <c r="G459" t="n">
-        <v>2.32674479484558</v>
+        <v>2.32674503326416</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G461" t="n">
-        <v>2.3323290348053</v>
+        <v>2.33232927322388</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>2.4539999961853</v>
       </c>
       <c r="G462" t="n">
-        <v>2.28393292427063</v>
+        <v>2.28393268585205</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>2.59200000762939</v>
       </c>
       <c r="G464" t="n">
-        <v>2.41236925125122</v>
+        <v>2.41236901283264</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>2.61400008201599</v>
       </c>
       <c r="G470" t="n">
-        <v>2.43284440040588</v>
+        <v>2.43284463882446</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>2.58599996566772</v>
       </c>
       <c r="G472" t="n">
-        <v>2.4067850112915</v>
+        <v>2.40678477287292</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>2.72399997711182</v>
       </c>
       <c r="G482" t="n">
-        <v>2.53522133827209</v>
+        <v>2.53522109985352</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>2.81200003623962</v>
       </c>
       <c r="G487" t="n">
-        <v>2.61712288856506</v>
+        <v>2.61712265014648</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -22142,7 +22142,7 @@
         <v>46309.2916666667</v>
       </c>
       <c r="B838" t="n">
-        <v>180137</v>
+        <v>187258</v>
       </c>
       <c r="C838" t="n">
         <v>2.74799990653992</v>
@@ -22160,6 +22160,32 @@
         <v>2.67199993133545</v>
       </c>
       <c r="H838" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B839" t="n">
+        <v>1759564</v>
+      </c>
+      <c r="C839" t="n">
+        <v>2.75999999046326</v>
+      </c>
+      <c r="D839" t="n">
+        <v>2.58400011062622</v>
+      </c>
+      <c r="E839" t="n">
+        <v>2.71799993515015</v>
+      </c>
+      <c r="F839" t="n">
+        <v>2.65000009536743</v>
+      </c>
+      <c r="G839" t="n">
+        <v>2.65000009536743</v>
+      </c>
+      <c r="H839" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/YACHT.MI.xlsx
+++ b/data/YACHT.MI.xlsx
@@ -421,7 +421,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G2" t="n">
-        <v>2.68335342407227</v>
+        <v>2.68335366249084</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6293261051178</v>
+        <v>2.62932634353638</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G4" t="n">
-        <v>2.57529902458191</v>
+        <v>2.57529878616333</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G7" t="n">
-        <v>2.62032198905945</v>
+        <v>2.62032175064087</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G8" t="n">
-        <v>2.6293261051178</v>
+        <v>2.62932634353638</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G9" t="n">
-        <v>2.60231280326843</v>
+        <v>2.60231256484985</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G10" t="n">
-        <v>2.6293261051178</v>
+        <v>2.62932634353638</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>2.88199996948242</v>
       </c>
       <c r="G11" t="n">
-        <v>2.5951087474823</v>
+        <v>2.59510898590088</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G13" t="n">
-        <v>2.60231280326843</v>
+        <v>2.60231256484985</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G16" t="n">
-        <v>2.6293261051178</v>
+        <v>2.62932634353638</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>2.99799990653992</v>
       </c>
       <c r="G17" t="n">
-        <v>2.69956159591675</v>
+        <v>2.69956135749817</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G18" t="n">
-        <v>2.84543561935425</v>
+        <v>2.84543514251709</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G19" t="n">
-        <v>2.81842184066772</v>
+        <v>2.81842160224915</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>3.2039999961853</v>
       </c>
       <c r="G27" t="n">
-        <v>2.88505530357361</v>
+        <v>2.88505506515503</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>3.12199997901917</v>
       </c>
       <c r="G29" t="n">
-        <v>2.81121802330017</v>
+        <v>2.81121778488159</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>3.17799997329712</v>
       </c>
       <c r="G30" t="n">
-        <v>2.86164331436157</v>
+        <v>2.86164355278015</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G33" t="n">
-        <v>2.72837615013123</v>
+        <v>2.7283763885498</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>2.96199989318848</v>
       </c>
       <c r="G36" t="n">
-        <v>2.66714549064636</v>
+        <v>2.66714525222778</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>2.96199989318848</v>
       </c>
       <c r="G37" t="n">
-        <v>2.66714549064636</v>
+        <v>2.66714525222778</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G38" t="n">
-        <v>2.6293261051178</v>
+        <v>2.62932634353638</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G39" t="n">
-        <v>2.65633988380432</v>
+        <v>2.6563401222229</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>2.93400001525879</v>
       </c>
       <c r="G40" t="n">
-        <v>2.64193272590637</v>
+        <v>2.64193248748779</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>2.90599989891052</v>
       </c>
       <c r="G43" t="n">
-        <v>2.6167197227478</v>
+        <v>2.61671996116638</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>2.91400003433228</v>
       </c>
       <c r="G47" t="n">
-        <v>2.62392377853394</v>
+        <v>2.62392354011536</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>2.90799999237061</v>
       </c>
       <c r="G48" t="n">
-        <v>2.61852097511292</v>
+        <v>2.61852073669434</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G49" t="n">
-        <v>2.65633988380432</v>
+        <v>2.6563401222229</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G50" t="n">
-        <v>2.63833069801331</v>
+        <v>2.63833093643188</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>2.89199995994568</v>
       </c>
       <c r="G51" t="n">
-        <v>2.60411334037781</v>
+        <v>2.60411357879639</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G52" t="n">
-        <v>2.58430337905884</v>
+        <v>2.58430361747742</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G54" t="n">
-        <v>2.62032198905945</v>
+        <v>2.62032175064087</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>2.8840000629425</v>
       </c>
       <c r="G56" t="n">
-        <v>2.59690999984741</v>
+        <v>2.59690976142883</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>2.93600010871887</v>
       </c>
       <c r="G59" t="n">
-        <v>2.64373350143433</v>
+        <v>2.64373373985291</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G61" t="n">
-        <v>2.65633988380432</v>
+        <v>2.6563401222229</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>3.0239999294281</v>
       </c>
       <c r="G62" t="n">
-        <v>2.72297334671021</v>
+        <v>2.72297358512878</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>2.99799990653992</v>
       </c>
       <c r="G63" t="n">
-        <v>2.69956159591675</v>
+        <v>2.69956135749817</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G64" t="n">
-        <v>2.67434883117676</v>
+        <v>2.67434906959534</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>2.84599995613098</v>
       </c>
       <c r="G67" t="n">
-        <v>2.56269264221191</v>
+        <v>2.56269240379333</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>2.80399990081787</v>
       </c>
       <c r="G68" t="n">
-        <v>2.52487373352051</v>
+        <v>2.52487349510193</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>2.81599998474121</v>
       </c>
       <c r="G71" t="n">
-        <v>2.53567910194397</v>
+        <v>2.53567886352539</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G72" t="n">
-        <v>2.4942581653595</v>
+        <v>2.49425792694092</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G73" t="n">
-        <v>2.58430337905884</v>
+        <v>2.58430361747742</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.81399989128113</v>
       </c>
       <c r="G75" t="n">
-        <v>2.53387832641602</v>
+        <v>2.53387784957886</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G76" t="n">
-        <v>2.58430337905884</v>
+        <v>2.58430361747742</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G77" t="n">
-        <v>2.58430337905884</v>
+        <v>2.58430361747742</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>2.83599996566772</v>
       </c>
       <c r="G78" t="n">
-        <v>2.55368804931641</v>
+        <v>2.55368828773499</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>2.80800008773804</v>
       </c>
       <c r="G80" t="n">
-        <v>2.528475522995</v>
+        <v>2.52847528457642</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>2.80200004577637</v>
       </c>
       <c r="G81" t="n">
-        <v>2.52307271957397</v>
+        <v>2.5230724811554</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G82" t="n">
-        <v>2.4942581653595</v>
+        <v>2.49425792694092</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G84" t="n">
-        <v>2.48525381088257</v>
+        <v>2.48525357246399</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>2.76399993896484</v>
       </c>
       <c r="G86" t="n">
-        <v>2.48885536193848</v>
+        <v>2.4888551235199</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>2.74600005149841</v>
       </c>
       <c r="G88" t="n">
-        <v>2.47264742851257</v>
+        <v>2.47264719009399</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>2.74399995803833</v>
       </c>
       <c r="G89" t="n">
-        <v>2.47084617614746</v>
+        <v>2.47084641456604</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G90" t="n">
-        <v>2.46724462509155</v>
+        <v>2.46724438667297</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.84599995613098</v>
       </c>
       <c r="G94" t="n">
-        <v>2.56269264221191</v>
+        <v>2.56269240379333</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G99" t="n">
-        <v>2.54828524589539</v>
+        <v>2.54828548431396</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G100" t="n">
-        <v>2.62032198905945</v>
+        <v>2.62032175064087</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G103" t="n">
-        <v>2.72837615013123</v>
+        <v>2.7283763885498</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>3.04800009727478</v>
       </c>
       <c r="G105" t="n">
-        <v>2.74458456039429</v>
+        <v>2.74458432197571</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>2.90400004386902</v>
       </c>
       <c r="G108" t="n">
-        <v>2.61491918563843</v>
+        <v>2.61491894721985</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>2.9760000705719</v>
       </c>
       <c r="G110" t="n">
-        <v>2.67975163459778</v>
+        <v>2.67975187301636</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G113" t="n">
-        <v>2.62032198905945</v>
+        <v>2.62032175064087</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G116" t="n">
-        <v>2.65633988380432</v>
+        <v>2.6563401222229</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>2.98600006103516</v>
       </c>
       <c r="G117" t="n">
-        <v>2.68875622749329</v>
+        <v>2.68875646591187</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>2.98799991607666</v>
       </c>
       <c r="G118" t="n">
-        <v>2.69055700302124</v>
+        <v>2.69055724143982</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>2.9760000705719</v>
       </c>
       <c r="G119" t="n">
-        <v>2.67975163459778</v>
+        <v>2.67975187301636</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G121" t="n">
-        <v>2.68335342407227</v>
+        <v>2.68335366249084</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>3.00200009346008</v>
       </c>
       <c r="G122" t="n">
-        <v>2.70316362380981</v>
+        <v>2.70316338539124</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>2.96600008010864</v>
       </c>
       <c r="G124" t="n">
-        <v>2.67074728012085</v>
+        <v>2.67074704170227</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G125" t="n">
-        <v>2.65633988380432</v>
+        <v>2.6563401222229</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>2.99200010299683</v>
       </c>
       <c r="G126" t="n">
-        <v>2.69415926933289</v>
+        <v>2.69415903091431</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G127" t="n">
-        <v>2.71937155723572</v>
+        <v>2.7193717956543</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G128" t="n">
-        <v>2.68335342407227</v>
+        <v>2.68335366249084</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>2.92799997329712</v>
       </c>
       <c r="G130" t="n">
-        <v>2.63652992248535</v>
+        <v>2.63652968406677</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G131" t="n">
-        <v>2.62032198905945</v>
+        <v>2.62032175064087</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G134" t="n">
-        <v>2.54828524589539</v>
+        <v>2.54828548431396</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G138" t="n">
-        <v>2.55728983879089</v>
+        <v>2.55728960037231</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>2.83200001716614</v>
       </c>
       <c r="G139" t="n">
-        <v>2.55008625984192</v>
+        <v>2.5500864982605</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>2.8659999370575</v>
       </c>
       <c r="G142" t="n">
-        <v>2.58070182800293</v>
+        <v>2.58070158958435</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>2.84599995613098</v>
       </c>
       <c r="G146" t="n">
-        <v>2.56269264221191</v>
+        <v>2.56269240379333</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G147" t="n">
-        <v>2.58430337905884</v>
+        <v>2.58430361747742</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>2.86800003051758</v>
       </c>
       <c r="G148" t="n">
-        <v>2.58250260353088</v>
+        <v>2.58250284194946</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>2.90799999237061</v>
       </c>
       <c r="G150" t="n">
-        <v>2.61852097511292</v>
+        <v>2.61852073669434</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G151" t="n">
-        <v>2.63833069801331</v>
+        <v>2.63833093643188</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G152" t="n">
-        <v>2.65633988380432</v>
+        <v>2.6563401222229</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>2.92600011825562</v>
       </c>
       <c r="G155" t="n">
-        <v>2.63472890853882</v>
+        <v>2.6347291469574</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>2.81599998474121</v>
       </c>
       <c r="G157" t="n">
-        <v>2.53567910194397</v>
+        <v>2.53567886352539</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G160" t="n">
-        <v>2.73738074302673</v>
+        <v>2.73738050460815</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>3.11199998855591</v>
       </c>
       <c r="G162" t="n">
-        <v>2.80221366882324</v>
+        <v>2.80221343040466</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>3.07800006866455</v>
       </c>
       <c r="G163" t="n">
-        <v>2.77159810066223</v>
+        <v>2.77159786224365</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G166" t="n">
-        <v>2.87244892120361</v>
+        <v>2.87244915962219</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>3.2260000705719</v>
       </c>
       <c r="G168" t="n">
-        <v>2.90486526489258</v>
+        <v>2.90486550331116</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G170" t="n">
-        <v>2.9895076751709</v>
+        <v>2.98950791358948</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>3.50600004196167</v>
       </c>
       <c r="G175" t="n">
-        <v>3.15699243545532</v>
+        <v>3.15699219703674</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G177" t="n">
-        <v>3.06154441833496</v>
+        <v>3.06154417991638</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>3.31800007820129</v>
       </c>
       <c r="G178" t="n">
-        <v>2.98770713806152</v>
+        <v>2.98770689964294</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>3.13199996948242</v>
       </c>
       <c r="G181" t="n">
-        <v>2.8202223777771</v>
+        <v>2.82022261619568</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>3.13199996948242</v>
       </c>
       <c r="G183" t="n">
-        <v>2.8202223777771</v>
+        <v>2.82022261619568</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G185" t="n">
-        <v>2.89045810699463</v>
+        <v>2.89045786857605</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>3.13199996948242</v>
       </c>
       <c r="G187" t="n">
-        <v>2.8202223777771</v>
+        <v>2.82022261619568</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>3.18199992179871</v>
       </c>
       <c r="G191" t="n">
-        <v>2.86524510383606</v>
+        <v>2.86524534225464</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>3.16799998283386</v>
       </c>
       <c r="G192" t="n">
-        <v>2.85263872146606</v>
+        <v>2.85263895988464</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>3.16400003433228</v>
       </c>
       <c r="G195" t="n">
-        <v>2.84903693199158</v>
+        <v>2.84903717041016</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G196" t="n">
-        <v>2.80491471290588</v>
+        <v>2.80491495132446</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G197" t="n">
-        <v>2.84993743896484</v>
+        <v>2.84993767738342</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G200" t="n">
-        <v>2.79591035842896</v>
+        <v>2.79591012001038</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G202" t="n">
-        <v>2.77339863777161</v>
+        <v>2.77339887619019</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G203" t="n">
-        <v>2.7643940448761</v>
+        <v>2.76439452171326</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G205" t="n">
-        <v>2.67434883117676</v>
+        <v>2.67434906959534</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G207" t="n">
-        <v>2.63833069801331</v>
+        <v>2.63833093643188</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G208" t="n">
-        <v>2.66534447669983</v>
+        <v>2.66534423828125</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G209" t="n">
-        <v>2.63833069801331</v>
+        <v>2.63833093643188</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G211" t="n">
-        <v>2.57529902458191</v>
+        <v>2.57529878616333</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G212" t="n">
-        <v>2.54828524589539</v>
+        <v>2.54828548431396</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G214" t="n">
-        <v>2.55728983879089</v>
+        <v>2.55728960037231</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G215" t="n">
-        <v>2.57529902458191</v>
+        <v>2.57529878616333</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G216" t="n">
-        <v>2.58430337905884</v>
+        <v>2.58430361747742</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G217" t="n">
-        <v>2.54828524589539</v>
+        <v>2.54828548431396</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>2.875</v>
       </c>
       <c r="G218" t="n">
-        <v>2.58880567550659</v>
+        <v>2.58880591392517</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G220" t="n">
-        <v>2.66534447669983</v>
+        <v>2.66534423828125</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G221" t="n">
-        <v>2.68785572052002</v>
+        <v>2.68785548210144</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G223" t="n">
-        <v>2.68785572052002</v>
+        <v>2.68785548210144</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G224" t="n">
-        <v>2.71486949920654</v>
+        <v>2.71486926078796</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G225" t="n">
-        <v>2.73287868499756</v>
+        <v>2.73287844657898</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G229" t="n">
-        <v>2.80491471290588</v>
+        <v>2.80491495132446</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G233" t="n">
-        <v>2.7643940448761</v>
+        <v>2.76439452171326</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G240" t="n">
-        <v>2.71036720275879</v>
+        <v>2.71036696434021</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G241" t="n">
-        <v>2.73287868499756</v>
+        <v>2.73287844657898</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G244" t="n">
-        <v>2.80041265487671</v>
+        <v>2.80041241645813</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G245" t="n">
-        <v>2.77339863777161</v>
+        <v>2.77339887619019</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G247" t="n">
-        <v>2.71937155723572</v>
+        <v>2.7193717956543</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G249" t="n">
-        <v>2.66984677314758</v>
+        <v>2.669846534729</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G250" t="n">
-        <v>2.65633988380432</v>
+        <v>2.6563401222229</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G251" t="n">
-        <v>2.66534447669983</v>
+        <v>2.66534423828125</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G252" t="n">
-        <v>2.65633988380432</v>
+        <v>2.6563401222229</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G253" t="n">
-        <v>2.68785572052002</v>
+        <v>2.68785548210144</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G256" t="n">
-        <v>2.63852882385254</v>
+        <v>2.63852858543396</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G257" t="n">
-        <v>2.63387513160706</v>
+        <v>2.63387537002563</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G264" t="n">
-        <v>2.63387513160706</v>
+        <v>2.63387537002563</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G265" t="n">
-        <v>2.61991500854492</v>
+        <v>2.61991477012634</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G266" t="n">
-        <v>2.61991500854492</v>
+        <v>2.61991477012634</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G269" t="n">
-        <v>2.62456798553467</v>
+        <v>2.62456822395325</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G270" t="n">
-        <v>2.62456798553467</v>
+        <v>2.62456822395325</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G275" t="n">
-        <v>2.62456798553467</v>
+        <v>2.62456822395325</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G276" t="n">
-        <v>2.61991500854492</v>
+        <v>2.61991477012634</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G285" t="n">
-        <v>2.49427080154419</v>
+        <v>2.49427056312561</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G287" t="n">
-        <v>2.52684497833252</v>
+        <v>2.52684473991394</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G288" t="n">
-        <v>2.54545879364014</v>
+        <v>2.54545903205872</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G289" t="n">
-        <v>2.54080533981323</v>
+        <v>2.54080557823181</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G290" t="n">
-        <v>2.531498670578</v>
+        <v>2.53149843215942</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G295" t="n">
-        <v>2.61991500854492</v>
+        <v>2.61991477012634</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G296" t="n">
-        <v>2.61991500854492</v>
+        <v>2.61991477012634</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G300" t="n">
-        <v>2.61991500854492</v>
+        <v>2.61991477012634</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G307" t="n">
-        <v>2.33605170249939</v>
+        <v>2.33605194091797</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G308" t="n">
-        <v>2.31743788719177</v>
+        <v>2.31743812561035</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G310" t="n">
-        <v>2.33605170249939</v>
+        <v>2.33605194091797</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>2.56500005722046</v>
       </c>
       <c r="G311" t="n">
-        <v>2.38724040985107</v>
+        <v>2.3872401714325</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>2.56500005722046</v>
       </c>
       <c r="G313" t="n">
-        <v>2.38724040985107</v>
+        <v>2.3872401714325</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G318" t="n">
-        <v>2.42912149429321</v>
+        <v>2.42912173271179</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G319" t="n">
-        <v>2.46169590950012</v>
+        <v>2.4616961479187</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G324" t="n">
-        <v>2.63387513160706</v>
+        <v>2.63387537002563</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G326" t="n">
-        <v>2.54080533981323</v>
+        <v>2.54080557823181</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G331" t="n">
-        <v>2.52684497833252</v>
+        <v>2.52684473991394</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G341" t="n">
-        <v>2.63852882385254</v>
+        <v>2.63852858543396</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G342" t="n">
-        <v>2.63387513160706</v>
+        <v>2.63387537002563</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G347" t="n">
-        <v>2.49427080154419</v>
+        <v>2.49427056312561</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G351" t="n">
-        <v>2.71763801574707</v>
+        <v>2.71763825416565</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G353" t="n">
-        <v>2.63387513160706</v>
+        <v>2.63387537002563</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G357" t="n">
-        <v>2.61991500854492</v>
+        <v>2.61991477012634</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G359" t="n">
-        <v>2.531498670578</v>
+        <v>2.53149843215942</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>2.70499992370605</v>
       </c>
       <c r="G360" t="n">
-        <v>2.51753783226013</v>
+        <v>2.51753807067871</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G364" t="n">
-        <v>2.63852882385254</v>
+        <v>2.63852858543396</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G373" t="n">
-        <v>2.61991500854492</v>
+        <v>2.61991477012634</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G376" t="n">
-        <v>2.68041014671326</v>
+        <v>2.68041038513184</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G384" t="n">
-        <v>2.62456798553467</v>
+        <v>2.62456822395325</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G385" t="n">
-        <v>2.61991500854492</v>
+        <v>2.61991477012634</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G386" t="n">
-        <v>2.62922167778015</v>
+        <v>2.62922191619873</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G388" t="n">
-        <v>2.63852882385254</v>
+        <v>2.63852858543396</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>2.89499998092651</v>
       </c>
       <c r="G397" t="n">
-        <v>2.69437074661255</v>
+        <v>2.69437050819397</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G399" t="n">
-        <v>2.71763801574707</v>
+        <v>2.71763825416565</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G406" t="n">
-        <v>2.78278708457947</v>
+        <v>2.78278684616089</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>2.93499994277954</v>
       </c>
       <c r="G408" t="n">
-        <v>2.73159861564636</v>
+        <v>2.73159837722778</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>2.93499994277954</v>
       </c>
       <c r="G416" t="n">
-        <v>2.73159861564636</v>
+        <v>2.73159837722778</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G423" t="n">
-        <v>2.63387513160706</v>
+        <v>2.63387537002563</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G425" t="n">
-        <v>2.71763801574707</v>
+        <v>2.71763825416565</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G428" t="n">
-        <v>2.63852882385254</v>
+        <v>2.63852858543396</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G433" t="n">
-        <v>2.54080533981323</v>
+        <v>2.54080557823181</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>2.70499992370605</v>
       </c>
       <c r="G434" t="n">
-        <v>2.51753783226013</v>
+        <v>2.51753807067871</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>2.70499992370605</v>
       </c>
       <c r="G436" t="n">
-        <v>2.51753783226013</v>
+        <v>2.51753807067871</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G437" t="n">
-        <v>2.54545879364014</v>
+        <v>2.54545903205872</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G440" t="n">
-        <v>2.54080533981323</v>
+        <v>2.54080557823181</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G445" t="n">
-        <v>2.42912149429321</v>
+        <v>2.42912173271179</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G446" t="n">
-        <v>2.4384286403656</v>
+        <v>2.43842840194702</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>2.5</v>
       </c>
       <c r="G459" t="n">
-        <v>2.32674503326416</v>
+        <v>2.32674479484558</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G461" t="n">
-        <v>2.33232927322388</v>
+        <v>2.3323290348053</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>2.4539999961853</v>
       </c>
       <c r="G462" t="n">
-        <v>2.28393268585205</v>
+        <v>2.28393292427063</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>2.59200000762939</v>
       </c>
       <c r="G464" t="n">
-        <v>2.41236901283264</v>
+        <v>2.41236925125122</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>2.61400008201599</v>
       </c>
       <c r="G470" t="n">
-        <v>2.43284463882446</v>
+        <v>2.43284440040588</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>2.58599996566772</v>
       </c>
       <c r="G472" t="n">
-        <v>2.40678477287292</v>
+        <v>2.4067850112915</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>2.72399997711182</v>
       </c>
       <c r="G482" t="n">
-        <v>2.53522109985352</v>
+        <v>2.53522133827209</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>2.81200003623962</v>
       </c>
       <c r="G487" t="n">
-        <v>2.61712265014648</v>
+        <v>2.61712288856506</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -22186,6 +22186,32 @@
         <v>2.65000009536743</v>
       </c>
       <c r="H839" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B840" t="n">
+        <v>160559</v>
+      </c>
+      <c r="C840" t="n">
+        <v>2.69000005722046</v>
+      </c>
+      <c r="D840" t="n">
+        <v>2.61199998855591</v>
+      </c>
+      <c r="E840" t="n">
+        <v>2.61199998855591</v>
+      </c>
+      <c r="F840" t="n">
+        <v>2.67199993133545</v>
+      </c>
+      <c r="G840" t="n">
+        <v>2.67199993133545</v>
+      </c>
+      <c r="H840" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/YACHT.MI.xlsx
+++ b/data/YACHT.MI.xlsx
@@ -427,7 +427,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G2" t="n">
-        <v>2.68335342407227</v>
+        <v>2.68335366249084</v>
       </c>
       <c r="H2" t="n">
         <v>9271589</v>
@@ -456,7 +456,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6293261051178</v>
+        <v>2.62932634353638</v>
       </c>
       <c r="H3" t="n">
         <v>5523202</v>
@@ -485,7 +485,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G4" t="n">
-        <v>2.57529902458191</v>
+        <v>2.57529878616333</v>
       </c>
       <c r="H4" t="n">
         <v>2742684</v>
@@ -572,7 +572,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G7" t="n">
-        <v>2.62032198905945</v>
+        <v>2.62032175064087</v>
       </c>
       <c r="H7" t="n">
         <v>462954</v>
@@ -601,7 +601,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G8" t="n">
-        <v>2.6293261051178</v>
+        <v>2.62932634353638</v>
       </c>
       <c r="H8" t="n">
         <v>470527</v>
@@ -630,7 +630,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G9" t="n">
-        <v>2.60231280326843</v>
+        <v>2.60231256484985</v>
       </c>
       <c r="H9" t="n">
         <v>370604</v>
@@ -659,7 +659,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G10" t="n">
-        <v>2.6293261051178</v>
+        <v>2.62932634353638</v>
       </c>
       <c r="H10" t="n">
         <v>167157</v>
@@ -688,7 +688,7 @@
         <v>2.88199996948242</v>
       </c>
       <c r="G11" t="n">
-        <v>2.5951087474823</v>
+        <v>2.59510898590088</v>
       </c>
       <c r="H11" t="n">
         <v>527158</v>
@@ -746,7 +746,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G13" t="n">
-        <v>2.60231280326843</v>
+        <v>2.60231256484985</v>
       </c>
       <c r="H13" t="n">
         <v>258873</v>
@@ -833,7 +833,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G16" t="n">
-        <v>2.6293261051178</v>
+        <v>2.62932634353638</v>
       </c>
       <c r="H16" t="n">
         <v>234246</v>
@@ -862,7 +862,7 @@
         <v>2.99799990653992</v>
       </c>
       <c r="G17" t="n">
-        <v>2.69956159591675</v>
+        <v>2.69956135749817</v>
       </c>
       <c r="H17" t="n">
         <v>721392</v>
@@ -891,7 +891,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G18" t="n">
-        <v>2.84543561935425</v>
+        <v>2.84543514251709</v>
       </c>
       <c r="H18" t="n">
         <v>1195492</v>
@@ -920,7 +920,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G19" t="n">
-        <v>2.81842184066772</v>
+        <v>2.81842160224915</v>
       </c>
       <c r="H19" t="n">
         <v>1196581</v>
@@ -1152,7 +1152,7 @@
         <v>3.2039999961853</v>
       </c>
       <c r="G27" t="n">
-        <v>2.88505530357361</v>
+        <v>2.88505506515503</v>
       </c>
       <c r="H27" t="n">
         <v>920776</v>
@@ -1210,7 +1210,7 @@
         <v>3.12199997901917</v>
       </c>
       <c r="G29" t="n">
-        <v>2.81121802330017</v>
+        <v>2.81121778488159</v>
       </c>
       <c r="H29" t="n">
         <v>544144</v>
@@ -1239,7 +1239,7 @@
         <v>3.17799997329712</v>
       </c>
       <c r="G30" t="n">
-        <v>2.86164331436157</v>
+        <v>2.86164355278015</v>
       </c>
       <c r="H30" t="n">
         <v>594226</v>
@@ -1326,7 +1326,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G33" t="n">
-        <v>2.72837615013123</v>
+        <v>2.7283763885498</v>
       </c>
       <c r="H33" t="n">
         <v>552267</v>
@@ -1413,7 +1413,7 @@
         <v>2.96199989318848</v>
       </c>
       <c r="G36" t="n">
-        <v>2.66714549064636</v>
+        <v>2.66714525222778</v>
       </c>
       <c r="H36" t="n">
         <v>99000</v>
@@ -1442,7 +1442,7 @@
         <v>2.96199989318848</v>
       </c>
       <c r="G37" t="n">
-        <v>2.66714549064636</v>
+        <v>2.66714525222778</v>
       </c>
       <c r="H37" t="n">
         <v>318498</v>
@@ -1471,7 +1471,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G38" t="n">
-        <v>2.6293261051178</v>
+        <v>2.62932634353638</v>
       </c>
       <c r="H38" t="n">
         <v>113466</v>
@@ -1500,7 +1500,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G39" t="n">
-        <v>2.65633988380432</v>
+        <v>2.6563401222229</v>
       </c>
       <c r="H39" t="n">
         <v>413206</v>
@@ -1529,7 +1529,7 @@
         <v>2.93400001525879</v>
       </c>
       <c r="G40" t="n">
-        <v>2.64193272590637</v>
+        <v>2.64193248748779</v>
       </c>
       <c r="H40" t="n">
         <v>560977</v>
@@ -1616,7 +1616,7 @@
         <v>2.90599989891052</v>
       </c>
       <c r="G43" t="n">
-        <v>2.6167197227478</v>
+        <v>2.61671996116638</v>
       </c>
       <c r="H43" t="n">
         <v>160349</v>
@@ -1732,7 +1732,7 @@
         <v>2.91400003433228</v>
       </c>
       <c r="G47" t="n">
-        <v>2.62392377853394</v>
+        <v>2.62392354011536</v>
       </c>
       <c r="H47" t="n">
         <v>681087</v>
@@ -1761,7 +1761,7 @@
         <v>2.90799999237061</v>
       </c>
       <c r="G48" t="n">
-        <v>2.61852097511292</v>
+        <v>2.61852073669434</v>
       </c>
       <c r="H48" t="n">
         <v>395238</v>
@@ -1790,7 +1790,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G49" t="n">
-        <v>2.65633988380432</v>
+        <v>2.6563401222229</v>
       </c>
       <c r="H49" t="n">
         <v>278184</v>
@@ -1819,7 +1819,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G50" t="n">
-        <v>2.63833069801331</v>
+        <v>2.63833093643188</v>
       </c>
       <c r="H50" t="n">
         <v>440815</v>
@@ -1848,7 +1848,7 @@
         <v>2.89199995994568</v>
       </c>
       <c r="G51" t="n">
-        <v>2.60411334037781</v>
+        <v>2.60411357879639</v>
       </c>
       <c r="H51" t="n">
         <v>301022</v>
@@ -1877,7 +1877,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G52" t="n">
-        <v>2.58430337905884</v>
+        <v>2.58430361747742</v>
       </c>
       <c r="H52" t="n">
         <v>406342</v>
@@ -1935,7 +1935,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G54" t="n">
-        <v>2.62032198905945</v>
+        <v>2.62032175064087</v>
       </c>
       <c r="H54" t="n">
         <v>470047</v>
@@ -1993,7 +1993,7 @@
         <v>2.8840000629425</v>
       </c>
       <c r="G56" t="n">
-        <v>2.59690999984741</v>
+        <v>2.59690976142883</v>
       </c>
       <c r="H56" t="n">
         <v>223974</v>
@@ -2080,7 +2080,7 @@
         <v>2.93600010871887</v>
       </c>
       <c r="G59" t="n">
-        <v>2.64373350143433</v>
+        <v>2.64373373985291</v>
       </c>
       <c r="H59" t="n">
         <v>1235755</v>
@@ -2138,7 +2138,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G61" t="n">
-        <v>2.65633988380432</v>
+        <v>2.6563401222229</v>
       </c>
       <c r="H61" t="n">
         <v>481432</v>
@@ -2167,7 +2167,7 @@
         <v>3.0239999294281</v>
       </c>
       <c r="G62" t="n">
-        <v>2.72297334671021</v>
+        <v>2.72297358512878</v>
       </c>
       <c r="H62" t="n">
         <v>610853</v>
@@ -2196,7 +2196,7 @@
         <v>2.99799990653992</v>
       </c>
       <c r="G63" t="n">
-        <v>2.69956159591675</v>
+        <v>2.69956135749817</v>
       </c>
       <c r="H63" t="n">
         <v>323387</v>
@@ -2225,7 +2225,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G64" t="n">
-        <v>2.67434883117676</v>
+        <v>2.67434906959534</v>
       </c>
       <c r="H64" t="n">
         <v>215337</v>
@@ -2312,7 +2312,7 @@
         <v>2.84599995613098</v>
       </c>
       <c r="G67" t="n">
-        <v>2.56269264221191</v>
+        <v>2.56269240379333</v>
       </c>
       <c r="H67" t="n">
         <v>325027</v>
@@ -2341,7 +2341,7 @@
         <v>2.80399990081787</v>
       </c>
       <c r="G68" t="n">
-        <v>2.52487373352051</v>
+        <v>2.52487349510193</v>
       </c>
       <c r="H68" t="n">
         <v>241271</v>
@@ -2428,7 +2428,7 @@
         <v>2.81599998474121</v>
       </c>
       <c r="G71" t="n">
-        <v>2.53567910194397</v>
+        <v>2.53567886352539</v>
       </c>
       <c r="H71" t="n">
         <v>188200</v>
@@ -2457,7 +2457,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G72" t="n">
-        <v>2.4942581653595</v>
+        <v>2.49425792694092</v>
       </c>
       <c r="H72" t="n">
         <v>268719</v>
@@ -2486,7 +2486,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G73" t="n">
-        <v>2.58430337905884</v>
+        <v>2.58430361747742</v>
       </c>
       <c r="H73" t="n">
         <v>296618</v>
@@ -2544,7 +2544,7 @@
         <v>2.81399989128113</v>
       </c>
       <c r="G75" t="n">
-        <v>2.53387832641602</v>
+        <v>2.53387784957886</v>
       </c>
       <c r="H75" t="n">
         <v>173870</v>
@@ -2573,7 +2573,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G76" t="n">
-        <v>2.58430337905884</v>
+        <v>2.58430361747742</v>
       </c>
       <c r="H76" t="n">
         <v>271694</v>
@@ -2602,7 +2602,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G77" t="n">
-        <v>2.58430337905884</v>
+        <v>2.58430361747742</v>
       </c>
       <c r="H77" t="n">
         <v>304675</v>
@@ -2631,7 +2631,7 @@
         <v>2.83599996566772</v>
       </c>
       <c r="G78" t="n">
-        <v>2.55368804931641</v>
+        <v>2.55368828773499</v>
       </c>
       <c r="H78" t="n">
         <v>311069</v>
@@ -2689,7 +2689,7 @@
         <v>2.80800008773804</v>
       </c>
       <c r="G80" t="n">
-        <v>2.528475522995</v>
+        <v>2.52847528457642</v>
       </c>
       <c r="H80" t="n">
         <v>109058</v>
@@ -2718,7 +2718,7 @@
         <v>2.80200004577637</v>
       </c>
       <c r="G81" t="n">
-        <v>2.52307271957397</v>
+        <v>2.5230724811554</v>
       </c>
       <c r="H81" t="n">
         <v>98753</v>
@@ -2747,7 +2747,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G82" t="n">
-        <v>2.4942581653595</v>
+        <v>2.49425792694092</v>
       </c>
       <c r="H82" t="n">
         <v>89415</v>
@@ -2805,7 +2805,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G84" t="n">
-        <v>2.48525381088257</v>
+        <v>2.48525357246399</v>
       </c>
       <c r="H84" t="n">
         <v>88572</v>
@@ -2863,7 +2863,7 @@
         <v>2.76399993896484</v>
       </c>
       <c r="G86" t="n">
-        <v>2.48885536193848</v>
+        <v>2.4888551235199</v>
       </c>
       <c r="H86" t="n">
         <v>72690</v>
@@ -2921,7 +2921,7 @@
         <v>2.74600005149841</v>
       </c>
       <c r="G88" t="n">
-        <v>2.47264742851257</v>
+        <v>2.47264719009399</v>
       </c>
       <c r="H88" t="n">
         <v>107336</v>
@@ -2950,7 +2950,7 @@
         <v>2.74399995803833</v>
       </c>
       <c r="G89" t="n">
-        <v>2.47084617614746</v>
+        <v>2.47084641456604</v>
       </c>
       <c r="H89" t="n">
         <v>196450</v>
@@ -2979,7 +2979,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G90" t="n">
-        <v>2.46724462509155</v>
+        <v>2.46724438667297</v>
       </c>
       <c r="H90" t="n">
         <v>158160</v>
@@ -3095,7 +3095,7 @@
         <v>2.84599995613098</v>
       </c>
       <c r="G94" t="n">
-        <v>2.56269264221191</v>
+        <v>2.56269240379333</v>
       </c>
       <c r="H94" t="n">
         <v>207064</v>
@@ -3240,7 +3240,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G99" t="n">
-        <v>2.54828524589539</v>
+        <v>2.54828548431396</v>
       </c>
       <c r="H99" t="n">
         <v>101935</v>
@@ -3269,7 +3269,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G100" t="n">
-        <v>2.62032198905945</v>
+        <v>2.62032175064087</v>
       </c>
       <c r="H100" t="n">
         <v>107418</v>
@@ -3356,7 +3356,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G103" t="n">
-        <v>2.72837615013123</v>
+        <v>2.7283763885498</v>
       </c>
       <c r="H103" t="n">
         <v>552357</v>
@@ -3414,7 +3414,7 @@
         <v>3.04800009727478</v>
       </c>
       <c r="G105" t="n">
-        <v>2.74458456039429</v>
+        <v>2.74458432197571</v>
       </c>
       <c r="H105" t="n">
         <v>558900</v>
@@ -3501,7 +3501,7 @@
         <v>2.90400004386902</v>
       </c>
       <c r="G108" t="n">
-        <v>2.61491918563843</v>
+        <v>2.61491894721985</v>
       </c>
       <c r="H108" t="n">
         <v>295869</v>
@@ -3559,7 +3559,7 @@
         <v>2.9760000705719</v>
       </c>
       <c r="G110" t="n">
-        <v>2.67975163459778</v>
+        <v>2.67975187301636</v>
       </c>
       <c r="H110" t="n">
         <v>343647</v>
@@ -3646,7 +3646,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G113" t="n">
-        <v>2.62032198905945</v>
+        <v>2.62032175064087</v>
       </c>
       <c r="H113" t="n">
         <v>3703132</v>
@@ -3733,7 +3733,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G116" t="n">
-        <v>2.65633988380432</v>
+        <v>2.6563401222229</v>
       </c>
       <c r="H116" t="n">
         <v>209509</v>
@@ -3762,7 +3762,7 @@
         <v>2.98600006103516</v>
       </c>
       <c r="G117" t="n">
-        <v>2.68875622749329</v>
+        <v>2.68875646591187</v>
       </c>
       <c r="H117" t="n">
         <v>230218</v>
@@ -3791,7 +3791,7 @@
         <v>2.98799991607666</v>
       </c>
       <c r="G118" t="n">
-        <v>2.69055700302124</v>
+        <v>2.69055724143982</v>
       </c>
       <c r="H118" t="n">
         <v>164670</v>
@@ -3820,7 +3820,7 @@
         <v>2.9760000705719</v>
       </c>
       <c r="G119" t="n">
-        <v>2.67975163459778</v>
+        <v>2.67975187301636</v>
       </c>
       <c r="H119" t="n">
         <v>138195</v>
@@ -3878,7 +3878,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G121" t="n">
-        <v>2.68335342407227</v>
+        <v>2.68335366249084</v>
       </c>
       <c r="H121" t="n">
         <v>230872</v>
@@ -3907,7 +3907,7 @@
         <v>3.00200009346008</v>
       </c>
       <c r="G122" t="n">
-        <v>2.70316362380981</v>
+        <v>2.70316338539124</v>
       </c>
       <c r="H122" t="n">
         <v>492519</v>
@@ -3965,7 +3965,7 @@
         <v>2.96600008010864</v>
       </c>
       <c r="G124" t="n">
-        <v>2.67074728012085</v>
+        <v>2.67074704170227</v>
       </c>
       <c r="H124" t="n">
         <v>538453</v>
@@ -3994,7 +3994,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G125" t="n">
-        <v>2.65633988380432</v>
+        <v>2.6563401222229</v>
       </c>
       <c r="H125" t="n">
         <v>301292</v>
@@ -4023,7 +4023,7 @@
         <v>2.99200010299683</v>
       </c>
       <c r="G126" t="n">
-        <v>2.69415926933289</v>
+        <v>2.69415903091431</v>
       </c>
       <c r="H126" t="n">
         <v>265025</v>
@@ -4052,7 +4052,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G127" t="n">
-        <v>2.71937155723572</v>
+        <v>2.7193717956543</v>
       </c>
       <c r="H127" t="n">
         <v>472950</v>
@@ -4081,7 +4081,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G128" t="n">
-        <v>2.68335342407227</v>
+        <v>2.68335366249084</v>
       </c>
       <c r="H128" t="n">
         <v>601683</v>
@@ -4139,7 +4139,7 @@
         <v>2.92799997329712</v>
       </c>
       <c r="G130" t="n">
-        <v>2.63652992248535</v>
+        <v>2.63652968406677</v>
       </c>
       <c r="H130" t="n">
         <v>329492</v>
@@ -4168,7 +4168,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G131" t="n">
-        <v>2.62032198905945</v>
+        <v>2.62032175064087</v>
       </c>
       <c r="H131" t="n">
         <v>395059</v>
@@ -4255,7 +4255,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G134" t="n">
-        <v>2.54828524589539</v>
+        <v>2.54828548431396</v>
       </c>
       <c r="H134" t="n">
         <v>228306</v>
@@ -4371,7 +4371,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G138" t="n">
-        <v>2.55728983879089</v>
+        <v>2.55728960037231</v>
       </c>
       <c r="H138" t="n">
         <v>102337</v>
@@ -4400,7 +4400,7 @@
         <v>2.83200001716614</v>
       </c>
       <c r="G139" t="n">
-        <v>2.55008625984192</v>
+        <v>2.5500864982605</v>
       </c>
       <c r="H139" t="n">
         <v>63393</v>
@@ -4487,7 +4487,7 @@
         <v>2.8659999370575</v>
       </c>
       <c r="G142" t="n">
-        <v>2.58070182800293</v>
+        <v>2.58070158958435</v>
       </c>
       <c r="H142" t="n">
         <v>182319</v>
@@ -4603,7 +4603,7 @@
         <v>2.84599995613098</v>
       </c>
       <c r="G146" t="n">
-        <v>2.56269264221191</v>
+        <v>2.56269240379333</v>
       </c>
       <c r="H146" t="n">
         <v>95512</v>
@@ -4632,7 +4632,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G147" t="n">
-        <v>2.58430337905884</v>
+        <v>2.58430361747742</v>
       </c>
       <c r="H147" t="n">
         <v>289366</v>
@@ -4661,7 +4661,7 @@
         <v>2.86800003051758</v>
       </c>
       <c r="G148" t="n">
-        <v>2.58250260353088</v>
+        <v>2.58250284194946</v>
       </c>
       <c r="H148" t="n">
         <v>580188</v>
@@ -4719,7 +4719,7 @@
         <v>2.90799999237061</v>
       </c>
       <c r="G150" t="n">
-        <v>2.61852097511292</v>
+        <v>2.61852073669434</v>
       </c>
       <c r="H150" t="n">
         <v>261501</v>
@@ -4748,7 +4748,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G151" t="n">
-        <v>2.63833069801331</v>
+        <v>2.63833093643188</v>
       </c>
       <c r="H151" t="n">
         <v>366145</v>
@@ -4777,7 +4777,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G152" t="n">
-        <v>2.65633988380432</v>
+        <v>2.6563401222229</v>
       </c>
       <c r="H152" t="n">
         <v>326136</v>
@@ -4864,7 +4864,7 @@
         <v>2.92600011825562</v>
       </c>
       <c r="G155" t="n">
-        <v>2.63472890853882</v>
+        <v>2.6347291469574</v>
       </c>
       <c r="H155" t="n">
         <v>146915</v>
@@ -4922,7 +4922,7 @@
         <v>2.81599998474121</v>
       </c>
       <c r="G157" t="n">
-        <v>2.53567910194397</v>
+        <v>2.53567886352539</v>
       </c>
       <c r="H157" t="n">
         <v>258393</v>
@@ -5009,7 +5009,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G160" t="n">
-        <v>2.73738074302673</v>
+        <v>2.73738050460815</v>
       </c>
       <c r="H160" t="n">
         <v>1245433</v>
@@ -5067,7 +5067,7 @@
         <v>3.11199998855591</v>
       </c>
       <c r="G162" t="n">
-        <v>2.80221366882324</v>
+        <v>2.80221343040466</v>
       </c>
       <c r="H162" t="n">
         <v>1090032</v>
@@ -5096,7 +5096,7 @@
         <v>3.07800006866455</v>
       </c>
       <c r="G163" t="n">
-        <v>2.77159810066223</v>
+        <v>2.77159786224365</v>
       </c>
       <c r="H163" t="n">
         <v>301973</v>
@@ -5183,7 +5183,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G166" t="n">
-        <v>2.87244892120361</v>
+        <v>2.87244915962219</v>
       </c>
       <c r="H166" t="n">
         <v>973243</v>
@@ -5241,7 +5241,7 @@
         <v>3.2260000705719</v>
       </c>
       <c r="G168" t="n">
-        <v>2.90486526489258</v>
+        <v>2.90486550331116</v>
       </c>
       <c r="H168" t="n">
         <v>1684867</v>
@@ -5299,7 +5299,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G170" t="n">
-        <v>2.9895076751709</v>
+        <v>2.98950791358948</v>
       </c>
       <c r="H170" t="n">
         <v>877610</v>
@@ -5444,7 +5444,7 @@
         <v>3.50600004196167</v>
       </c>
       <c r="G175" t="n">
-        <v>3.15699243545532</v>
+        <v>3.15699219703674</v>
       </c>
       <c r="H175" t="n">
         <v>1959547</v>
@@ -5502,7 +5502,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G177" t="n">
-        <v>3.06154441833496</v>
+        <v>3.06154417991638</v>
       </c>
       <c r="H177" t="n">
         <v>1430963</v>
@@ -5531,7 +5531,7 @@
         <v>3.31800007820129</v>
       </c>
       <c r="G178" t="n">
-        <v>2.98770713806152</v>
+        <v>2.98770689964294</v>
       </c>
       <c r="H178" t="n">
         <v>742754</v>
@@ -5618,7 +5618,7 @@
         <v>3.13199996948242</v>
       </c>
       <c r="G181" t="n">
-        <v>2.8202223777771</v>
+        <v>2.82022261619568</v>
       </c>
       <c r="H181" t="n">
         <v>951170</v>
@@ -5676,7 +5676,7 @@
         <v>3.13199996948242</v>
       </c>
       <c r="G183" t="n">
-        <v>2.8202223777771</v>
+        <v>2.82022261619568</v>
       </c>
       <c r="H183" t="n">
         <v>1171358</v>
@@ -5734,7 +5734,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G185" t="n">
-        <v>2.89045810699463</v>
+        <v>2.89045786857605</v>
       </c>
       <c r="H185" t="n">
         <v>709125</v>
@@ -5792,7 +5792,7 @@
         <v>3.13199996948242</v>
       </c>
       <c r="G187" t="n">
-        <v>2.8202223777771</v>
+        <v>2.82022261619568</v>
       </c>
       <c r="H187" t="n">
         <v>486844</v>
@@ -5908,7 +5908,7 @@
         <v>3.18199992179871</v>
       </c>
       <c r="G191" t="n">
-        <v>2.86524510383606</v>
+        <v>2.86524534225464</v>
       </c>
       <c r="H191" t="n">
         <v>278666</v>
@@ -5937,7 +5937,7 @@
         <v>3.16799998283386</v>
       </c>
       <c r="G192" t="n">
-        <v>2.85263872146606</v>
+        <v>2.85263895988464</v>
       </c>
       <c r="H192" t="n">
         <v>381457</v>
@@ -6024,7 +6024,7 @@
         <v>3.16400003433228</v>
       </c>
       <c r="G195" t="n">
-        <v>2.84903693199158</v>
+        <v>2.84903717041016</v>
       </c>
       <c r="H195" t="n">
         <v>562311</v>
@@ -6053,7 +6053,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G196" t="n">
-        <v>2.80491471290588</v>
+        <v>2.80491495132446</v>
       </c>
       <c r="H196" t="n">
         <v>835838</v>
@@ -6082,7 +6082,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G197" t="n">
-        <v>2.84993743896484</v>
+        <v>2.84993767738342</v>
       </c>
       <c r="H197" t="n">
         <v>267637</v>
@@ -6169,7 +6169,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G200" t="n">
-        <v>2.79591035842896</v>
+        <v>2.79591012001038</v>
       </c>
       <c r="H200" t="n">
         <v>277567</v>
@@ -6227,7 +6227,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G202" t="n">
-        <v>2.77339863777161</v>
+        <v>2.77339887619019</v>
       </c>
       <c r="H202" t="n">
         <v>272137</v>
@@ -6256,7 +6256,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G203" t="n">
-        <v>2.7643940448761</v>
+        <v>2.76439452171326</v>
       </c>
       <c r="H203" t="n">
         <v>271367</v>
@@ -6314,7 +6314,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G205" t="n">
-        <v>2.67434883117676</v>
+        <v>2.67434906959534</v>
       </c>
       <c r="H205" t="n">
         <v>598555</v>
@@ -6372,7 +6372,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G207" t="n">
-        <v>2.63833069801331</v>
+        <v>2.63833093643188</v>
       </c>
       <c r="H207" t="n">
         <v>256503</v>
@@ -6401,7 +6401,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G208" t="n">
-        <v>2.66534447669983</v>
+        <v>2.66534423828125</v>
       </c>
       <c r="H208" t="n">
         <v>290531</v>
@@ -6430,7 +6430,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G209" t="n">
-        <v>2.63833069801331</v>
+        <v>2.63833093643188</v>
       </c>
       <c r="H209" t="n">
         <v>276036</v>
@@ -6488,7 +6488,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G211" t="n">
-        <v>2.57529902458191</v>
+        <v>2.57529878616333</v>
       </c>
       <c r="H211" t="n">
         <v>2239887</v>
@@ -6517,7 +6517,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G212" t="n">
-        <v>2.54828524589539</v>
+        <v>2.54828548431396</v>
       </c>
       <c r="H212" t="n">
         <v>548010</v>
@@ -6575,7 +6575,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G214" t="n">
-        <v>2.55728983879089</v>
+        <v>2.55728960037231</v>
       </c>
       <c r="H214" t="n">
         <v>507186</v>
@@ -6604,7 +6604,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G215" t="n">
-        <v>2.57529902458191</v>
+        <v>2.57529878616333</v>
       </c>
       <c r="H215" t="n">
         <v>1072643</v>
@@ -6633,7 +6633,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G216" t="n">
-        <v>2.58430337905884</v>
+        <v>2.58430361747742</v>
       </c>
       <c r="H216" t="n">
         <v>404218</v>
@@ -6662,7 +6662,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G217" t="n">
-        <v>2.54828524589539</v>
+        <v>2.54828548431396</v>
       </c>
       <c r="H217" t="n">
         <v>601149</v>
@@ -6691,7 +6691,7 @@
         <v>2.875</v>
       </c>
       <c r="G218" t="n">
-        <v>2.58880567550659</v>
+        <v>2.58880591392517</v>
       </c>
       <c r="H218" t="n">
         <v>460755</v>
@@ -6749,7 +6749,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G220" t="n">
-        <v>2.66534447669983</v>
+        <v>2.66534423828125</v>
       </c>
       <c r="H220" t="n">
         <v>807427</v>
@@ -6778,7 +6778,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G221" t="n">
-        <v>2.68785572052002</v>
+        <v>2.68785548210144</v>
       </c>
       <c r="H221" t="n">
         <v>693872</v>
@@ -6836,7 +6836,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G223" t="n">
-        <v>2.68785572052002</v>
+        <v>2.68785548210144</v>
       </c>
       <c r="H223" t="n">
         <v>289774</v>
@@ -6865,7 +6865,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G224" t="n">
-        <v>2.71486949920654</v>
+        <v>2.71486926078796</v>
       </c>
       <c r="H224" t="n">
         <v>302122</v>
@@ -6894,7 +6894,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G225" t="n">
-        <v>2.73287868499756</v>
+        <v>2.73287844657898</v>
       </c>
       <c r="H225" t="n">
         <v>325591</v>
@@ -7010,7 +7010,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G229" t="n">
-        <v>2.80491471290588</v>
+        <v>2.80491495132446</v>
       </c>
       <c r="H229" t="n">
         <v>265295</v>
@@ -7126,7 +7126,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G233" t="n">
-        <v>2.7643940448761</v>
+        <v>2.76439452171326</v>
       </c>
       <c r="H233" t="n">
         <v>219195</v>
@@ -7329,7 +7329,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G240" t="n">
-        <v>2.71036720275879</v>
+        <v>2.71036696434021</v>
       </c>
       <c r="H240" t="n">
         <v>268134</v>
@@ -7358,7 +7358,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G241" t="n">
-        <v>2.73287868499756</v>
+        <v>2.73287844657898</v>
       </c>
       <c r="H241" t="n">
         <v>156956</v>
@@ -7445,7 +7445,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G244" t="n">
-        <v>2.80041265487671</v>
+        <v>2.80041241645813</v>
       </c>
       <c r="H244" t="n">
         <v>672793</v>
@@ -7474,7 +7474,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G245" t="n">
-        <v>2.77339863777161</v>
+        <v>2.77339887619019</v>
       </c>
       <c r="H245" t="n">
         <v>803152</v>
@@ -7532,7 +7532,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G247" t="n">
-        <v>2.71937155723572</v>
+        <v>2.7193717956543</v>
       </c>
       <c r="H247" t="n">
         <v>326171</v>
@@ -7590,7 +7590,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G249" t="n">
-        <v>2.66984677314758</v>
+        <v>2.669846534729</v>
       </c>
       <c r="H249" t="n">
         <v>254041</v>
@@ -7619,7 +7619,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G250" t="n">
-        <v>2.65633988380432</v>
+        <v>2.6563401222229</v>
       </c>
       <c r="H250" t="n">
         <v>375208</v>
@@ -7648,7 +7648,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G251" t="n">
-        <v>2.66534447669983</v>
+        <v>2.66534423828125</v>
       </c>
       <c r="H251" t="n">
         <v>193370</v>
@@ -7677,7 +7677,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G252" t="n">
-        <v>2.65633988380432</v>
+        <v>2.6563401222229</v>
       </c>
       <c r="H252" t="n">
         <v>198249</v>
@@ -7706,7 +7706,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G253" t="n">
-        <v>2.68785572052002</v>
+        <v>2.68785548210144</v>
       </c>
       <c r="H253" t="n">
         <v>521926</v>
@@ -7793,7 +7793,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G256" t="n">
-        <v>2.63852882385254</v>
+        <v>2.63852858543396</v>
       </c>
       <c r="H256" t="n">
         <v>424764</v>
@@ -7822,7 +7822,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G257" t="n">
-        <v>2.63387513160706</v>
+        <v>2.63387537002563</v>
       </c>
       <c r="H257" t="n">
         <v>331330</v>
@@ -8025,7 +8025,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G264" t="n">
-        <v>2.63387513160706</v>
+        <v>2.63387537002563</v>
       </c>
       <c r="H264" t="n">
         <v>380253</v>
@@ -8054,7 +8054,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G265" t="n">
-        <v>2.61991500854492</v>
+        <v>2.61991477012634</v>
       </c>
       <c r="H265" t="n">
         <v>268393</v>
@@ -8083,7 +8083,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G266" t="n">
-        <v>2.61991500854492</v>
+        <v>2.61991477012634</v>
       </c>
       <c r="H266" t="n">
         <v>334646</v>
@@ -8170,7 +8170,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G269" t="n">
-        <v>2.62456798553467</v>
+        <v>2.62456822395325</v>
       </c>
       <c r="H269" t="n">
         <v>267385</v>
@@ -8199,7 +8199,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G270" t="n">
-        <v>2.62456798553467</v>
+        <v>2.62456822395325</v>
       </c>
       <c r="H270" t="n">
         <v>255476</v>
@@ -8344,7 +8344,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G275" t="n">
-        <v>2.62456798553467</v>
+        <v>2.62456822395325</v>
       </c>
       <c r="H275" t="n">
         <v>175603</v>
@@ -8373,7 +8373,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G276" t="n">
-        <v>2.61991500854492</v>
+        <v>2.61991477012634</v>
       </c>
       <c r="H276" t="n">
         <v>180030</v>
@@ -8634,7 +8634,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G285" t="n">
-        <v>2.49427080154419</v>
+        <v>2.49427056312561</v>
       </c>
       <c r="H285" t="n">
         <v>387349</v>
@@ -8692,7 +8692,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G287" t="n">
-        <v>2.52684497833252</v>
+        <v>2.52684473991394</v>
       </c>
       <c r="H287" t="n">
         <v>123001</v>
@@ -8721,7 +8721,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G288" t="n">
-        <v>2.54545879364014</v>
+        <v>2.54545903205872</v>
       </c>
       <c r="H288" t="n">
         <v>248118</v>
@@ -8750,7 +8750,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G289" t="n">
-        <v>2.54080533981323</v>
+        <v>2.54080557823181</v>
       </c>
       <c r="H289" t="n">
         <v>290279</v>
@@ -8779,7 +8779,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G290" t="n">
-        <v>2.531498670578</v>
+        <v>2.53149843215942</v>
       </c>
       <c r="H290" t="n">
         <v>177641</v>
@@ -8924,7 +8924,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G295" t="n">
-        <v>2.61991500854492</v>
+        <v>2.61991477012634</v>
       </c>
       <c r="H295" t="n">
         <v>403095</v>
@@ -8953,7 +8953,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G296" t="n">
-        <v>2.61991500854492</v>
+        <v>2.61991477012634</v>
       </c>
       <c r="H296" t="n">
         <v>436118</v>
@@ -9069,7 +9069,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G300" t="n">
-        <v>2.61991500854492</v>
+        <v>2.61991477012634</v>
       </c>
       <c r="H300" t="n">
         <v>249379</v>
@@ -9272,7 +9272,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G307" t="n">
-        <v>2.33605170249939</v>
+        <v>2.33605194091797</v>
       </c>
       <c r="H307" t="n">
         <v>1179759</v>
@@ -9301,7 +9301,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G308" t="n">
-        <v>2.31743788719177</v>
+        <v>2.31743812561035</v>
       </c>
       <c r="H308" t="n">
         <v>642373</v>
@@ -9359,7 +9359,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G310" t="n">
-        <v>2.33605170249939</v>
+        <v>2.33605194091797</v>
       </c>
       <c r="H310" t="n">
         <v>598360</v>
@@ -9388,7 +9388,7 @@
         <v>2.56500005722046</v>
       </c>
       <c r="G311" t="n">
-        <v>2.38724040985107</v>
+        <v>2.3872401714325</v>
       </c>
       <c r="H311" t="n">
         <v>611830</v>
@@ -9446,7 +9446,7 @@
         <v>2.56500005722046</v>
       </c>
       <c r="G313" t="n">
-        <v>2.38724040985107</v>
+        <v>2.3872401714325</v>
       </c>
       <c r="H313" t="n">
         <v>487152</v>
@@ -9591,7 +9591,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G318" t="n">
-        <v>2.42912149429321</v>
+        <v>2.42912173271179</v>
       </c>
       <c r="H318" t="n">
         <v>143426</v>
@@ -9620,7 +9620,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G319" t="n">
-        <v>2.46169590950012</v>
+        <v>2.4616961479187</v>
       </c>
       <c r="H319" t="n">
         <v>341199</v>
@@ -9765,7 +9765,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G324" t="n">
-        <v>2.63387513160706</v>
+        <v>2.63387537002563</v>
       </c>
       <c r="H324" t="n">
         <v>845890</v>
@@ -9823,7 +9823,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G326" t="n">
-        <v>2.54080533981323</v>
+        <v>2.54080557823181</v>
       </c>
       <c r="H326" t="n">
         <v>1995862</v>
@@ -9968,7 +9968,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G331" t="n">
-        <v>2.52684497833252</v>
+        <v>2.52684473991394</v>
       </c>
       <c r="H331" t="n">
         <v>174270</v>
@@ -10258,7 +10258,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G341" t="n">
-        <v>2.63852882385254</v>
+        <v>2.63852858543396</v>
       </c>
       <c r="H341" t="n">
         <v>386548</v>
@@ -10287,7 +10287,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G342" t="n">
-        <v>2.63387513160706</v>
+        <v>2.63387537002563</v>
       </c>
       <c r="H342" t="n">
         <v>325109</v>
@@ -10432,7 +10432,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G347" t="n">
-        <v>2.49427080154419</v>
+        <v>2.49427056312561</v>
       </c>
       <c r="H347" t="n">
         <v>240234</v>
@@ -10548,7 +10548,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G351" t="n">
-        <v>2.71763801574707</v>
+        <v>2.71763825416565</v>
       </c>
       <c r="H351" t="n">
         <v>1174324</v>
@@ -10606,7 +10606,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G353" t="n">
-        <v>2.63387513160706</v>
+        <v>2.63387537002563</v>
       </c>
       <c r="H353" t="n">
         <v>1343987</v>
@@ -10722,7 +10722,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G357" t="n">
-        <v>2.61991500854492</v>
+        <v>2.61991477012634</v>
       </c>
       <c r="H357" t="n">
         <v>528618</v>
@@ -10780,7 +10780,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G359" t="n">
-        <v>2.531498670578</v>
+        <v>2.53149843215942</v>
       </c>
       <c r="H359" t="n">
         <v>283153</v>
@@ -10809,7 +10809,7 @@
         <v>2.70499992370605</v>
       </c>
       <c r="G360" t="n">
-        <v>2.51753783226013</v>
+        <v>2.51753807067871</v>
       </c>
       <c r="H360" t="n">
         <v>224865</v>
@@ -10925,7 +10925,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G364" t="n">
-        <v>2.63852882385254</v>
+        <v>2.63852858543396</v>
       </c>
       <c r="H364" t="n">
         <v>1117900</v>
@@ -11186,7 +11186,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G373" t="n">
-        <v>2.61991500854492</v>
+        <v>2.61991477012634</v>
       </c>
       <c r="H373" t="n">
         <v>332593</v>
@@ -11273,7 +11273,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G376" t="n">
-        <v>2.68041014671326</v>
+        <v>2.68041038513184</v>
       </c>
       <c r="H376" t="n">
         <v>1005481</v>
@@ -11505,7 +11505,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G384" t="n">
-        <v>2.62456798553467</v>
+        <v>2.62456822395325</v>
       </c>
       <c r="H384" t="n">
         <v>261528</v>
@@ -11534,7 +11534,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G385" t="n">
-        <v>2.61991500854492</v>
+        <v>2.61991477012634</v>
       </c>
       <c r="H385" t="n">
         <v>258305</v>
@@ -11563,7 +11563,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G386" t="n">
-        <v>2.62922167778015</v>
+        <v>2.62922191619873</v>
       </c>
       <c r="H386" t="n">
         <v>122247</v>
@@ -11621,7 +11621,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G388" t="n">
-        <v>2.63852882385254</v>
+        <v>2.63852858543396</v>
       </c>
       <c r="H388" t="n">
         <v>243336</v>
@@ -11882,7 +11882,7 @@
         <v>2.89499998092651</v>
       </c>
       <c r="G397" t="n">
-        <v>2.69437074661255</v>
+        <v>2.69437050819397</v>
       </c>
       <c r="H397" t="n">
         <v>247508</v>
@@ -11940,7 +11940,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G399" t="n">
-        <v>2.71763801574707</v>
+        <v>2.71763825416565</v>
       </c>
       <c r="H399" t="n">
         <v>314529</v>
@@ -12143,7 +12143,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G406" t="n">
-        <v>2.78278708457947</v>
+        <v>2.78278684616089</v>
       </c>
       <c r="H406" t="n">
         <v>858592</v>
@@ -12201,7 +12201,7 @@
         <v>2.93499994277954</v>
       </c>
       <c r="G408" t="n">
-        <v>2.73159861564636</v>
+        <v>2.73159837722778</v>
       </c>
       <c r="H408" t="n">
         <v>366747</v>
@@ -12433,7 +12433,7 @@
         <v>2.93499994277954</v>
       </c>
       <c r="G416" t="n">
-        <v>2.73159861564636</v>
+        <v>2.73159837722778</v>
       </c>
       <c r="H416" t="n">
         <v>420901</v>
@@ -12636,7 +12636,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G423" t="n">
-        <v>2.63387513160706</v>
+        <v>2.63387537002563</v>
       </c>
       <c r="H423" t="n">
         <v>266696</v>
@@ -12694,7 +12694,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G425" t="n">
-        <v>2.71763801574707</v>
+        <v>2.71763825416565</v>
       </c>
       <c r="H425" t="n">
         <v>1259534</v>
@@ -12781,7 +12781,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G428" t="n">
-        <v>2.63852882385254</v>
+        <v>2.63852858543396</v>
       </c>
       <c r="H428" t="n">
         <v>1712952</v>
@@ -12926,7 +12926,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G433" t="n">
-        <v>2.54080533981323</v>
+        <v>2.54080557823181</v>
       </c>
       <c r="H433" t="n">
         <v>554263</v>
@@ -12955,7 +12955,7 @@
         <v>2.70499992370605</v>
       </c>
       <c r="G434" t="n">
-        <v>2.51753783226013</v>
+        <v>2.51753807067871</v>
       </c>
       <c r="H434" t="n">
         <v>1145037</v>
@@ -13013,7 +13013,7 @@
         <v>2.70499992370605</v>
       </c>
       <c r="G436" t="n">
-        <v>2.51753783226013</v>
+        <v>2.51753807067871</v>
       </c>
       <c r="H436" t="n">
         <v>385823</v>
@@ -13042,7 +13042,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G437" t="n">
-        <v>2.54545879364014</v>
+        <v>2.54545903205872</v>
       </c>
       <c r="H437" t="n">
         <v>263202</v>
@@ -13129,7 +13129,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G440" t="n">
-        <v>2.54080533981323</v>
+        <v>2.54080557823181</v>
       </c>
       <c r="H440" t="n">
         <v>201087</v>
@@ -13274,7 +13274,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G445" t="n">
-        <v>2.42912149429321</v>
+        <v>2.42912173271179</v>
       </c>
       <c r="H445" t="n">
         <v>381239</v>
@@ -13303,7 +13303,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G446" t="n">
-        <v>2.4384286403656</v>
+        <v>2.43842840194702</v>
       </c>
       <c r="H446" t="n">
         <v>430895</v>
@@ -13680,7 +13680,7 @@
         <v>2.5</v>
       </c>
       <c r="G459" t="n">
-        <v>2.32674503326416</v>
+        <v>2.32674479484558</v>
       </c>
       <c r="H459" t="n">
         <v>273470</v>
@@ -13738,7 +13738,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G461" t="n">
-        <v>2.33232927322388</v>
+        <v>2.3323290348053</v>
       </c>
       <c r="H461" t="n">
         <v>159605</v>
@@ -13767,7 +13767,7 @@
         <v>2.4539999961853</v>
       </c>
       <c r="G462" t="n">
-        <v>2.28393268585205</v>
+        <v>2.28393292427063</v>
       </c>
       <c r="H462" t="n">
         <v>213603</v>
@@ -13825,7 +13825,7 @@
         <v>2.59200000762939</v>
       </c>
       <c r="G464" t="n">
-        <v>2.41236901283264</v>
+        <v>2.41236925125122</v>
       </c>
       <c r="H464" t="n">
         <v>118274</v>
@@ -13999,7 +13999,7 @@
         <v>2.61400008201599</v>
       </c>
       <c r="G470" t="n">
-        <v>2.43284463882446</v>
+        <v>2.43284440040588</v>
       </c>
       <c r="H470" t="n">
         <v>181112</v>
@@ -14057,7 +14057,7 @@
         <v>2.58599996566772</v>
       </c>
       <c r="G472" t="n">
-        <v>2.40678477287292</v>
+        <v>2.4067850112915</v>
       </c>
       <c r="H472" t="n">
         <v>342752</v>
@@ -14347,7 +14347,7 @@
         <v>2.72399997711182</v>
       </c>
       <c r="G482" t="n">
-        <v>2.53522109985352</v>
+        <v>2.53522133827209</v>
       </c>
       <c r="H482" t="n">
         <v>409776</v>
@@ -14492,7 +14492,7 @@
         <v>2.81200003623962</v>
       </c>
       <c r="G487" t="n">
-        <v>2.61712265014648</v>
+        <v>2.61712288856506</v>
       </c>
       <c r="H487" t="n">
         <v>549599</v>
@@ -24735,6 +24735,64 @@
         <v>160559</v>
       </c>
       <c r="I840" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="s">
+        <v>9</v>
+      </c>
+      <c r="B841" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C841" t="n">
+        <v>2.67199993133545</v>
+      </c>
+      <c r="D841" t="n">
+        <v>2.67199993133545</v>
+      </c>
+      <c r="E841" t="n">
+        <v>2.60599994659424</v>
+      </c>
+      <c r="F841" t="n">
+        <v>2.61999988555908</v>
+      </c>
+      <c r="G841" t="n">
+        <v>2.61999988555908</v>
+      </c>
+      <c r="H841" t="n">
+        <v>133109</v>
+      </c>
+      <c r="I841" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="s">
+        <v>9</v>
+      </c>
+      <c r="B842" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C842" t="n">
+        <v>2.59999990463257</v>
+      </c>
+      <c r="D842" t="n">
+        <v>2.66400003433228</v>
+      </c>
+      <c r="E842" t="n">
+        <v>2.59200000762939</v>
+      </c>
+      <c r="F842" t="n">
+        <v>2.65000009536743</v>
+      </c>
+      <c r="G842" t="n">
+        <v>2.65000009536743</v>
+      </c>
+      <c r="H842" t="n">
+        <v>115099</v>
+      </c>
+      <c r="I842" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/YACHT.MI.xlsx
+++ b/data/YACHT.MI.xlsx
@@ -427,7 +427,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G2" t="n">
-        <v>2.68335366249084</v>
+        <v>2.68335342407227</v>
       </c>
       <c r="H2" t="n">
         <v>9271589</v>
@@ -485,7 +485,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G4" t="n">
-        <v>2.57529878616333</v>
+        <v>2.57529902458191</v>
       </c>
       <c r="H4" t="n">
         <v>2742684</v>
@@ -862,7 +862,7 @@
         <v>2.99799990653992</v>
       </c>
       <c r="G17" t="n">
-        <v>2.69956135749817</v>
+        <v>2.69956159591675</v>
       </c>
       <c r="H17" t="n">
         <v>721392</v>
@@ -891,7 +891,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G18" t="n">
-        <v>2.84543514251709</v>
+        <v>2.84543538093567</v>
       </c>
       <c r="H18" t="n">
         <v>1195492</v>
@@ -920,7 +920,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G19" t="n">
-        <v>2.81842160224915</v>
+        <v>2.81842184066772</v>
       </c>
       <c r="H19" t="n">
         <v>1196581</v>
@@ -949,7 +949,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G20" t="n">
-        <v>2.83643102645874</v>
+        <v>2.83643078804016</v>
       </c>
       <c r="H20" t="n">
         <v>573734</v>
@@ -1152,7 +1152,7 @@
         <v>3.2039999961853</v>
       </c>
       <c r="G27" t="n">
-        <v>2.88505506515503</v>
+        <v>2.88505530357361</v>
       </c>
       <c r="H27" t="n">
         <v>920776</v>
@@ -1297,7 +1297,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G32" t="n">
-        <v>2.74638533592224</v>
+        <v>2.74638509750366</v>
       </c>
       <c r="H32" t="n">
         <v>706131</v>
@@ -1326,7 +1326,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G33" t="n">
-        <v>2.7283763885498</v>
+        <v>2.72837615013123</v>
       </c>
       <c r="H33" t="n">
         <v>552267</v>
@@ -1500,7 +1500,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G39" t="n">
-        <v>2.6563401222229</v>
+        <v>2.65633988380432</v>
       </c>
       <c r="H39" t="n">
         <v>413206</v>
@@ -1616,7 +1616,7 @@
         <v>2.90599989891052</v>
       </c>
       <c r="G43" t="n">
-        <v>2.61671996116638</v>
+        <v>2.6167197227478</v>
       </c>
       <c r="H43" t="n">
         <v>160349</v>
@@ -1790,7 +1790,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G49" t="n">
-        <v>2.6563401222229</v>
+        <v>2.65633988380432</v>
       </c>
       <c r="H49" t="n">
         <v>278184</v>
@@ -1848,7 +1848,7 @@
         <v>2.89199995994568</v>
       </c>
       <c r="G51" t="n">
-        <v>2.60411357879639</v>
+        <v>2.60411334037781</v>
       </c>
       <c r="H51" t="n">
         <v>301022</v>
@@ -1993,7 +1993,7 @@
         <v>2.8840000629425</v>
       </c>
       <c r="G56" t="n">
-        <v>2.59690976142883</v>
+        <v>2.59690999984741</v>
       </c>
       <c r="H56" t="n">
         <v>223974</v>
@@ -2080,7 +2080,7 @@
         <v>2.93600010871887</v>
       </c>
       <c r="G59" t="n">
-        <v>2.64373373985291</v>
+        <v>2.64373350143433</v>
       </c>
       <c r="H59" t="n">
         <v>1235755</v>
@@ -2138,7 +2138,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G61" t="n">
-        <v>2.6563401222229</v>
+        <v>2.65633988380432</v>
       </c>
       <c r="H61" t="n">
         <v>481432</v>
@@ -2167,7 +2167,7 @@
         <v>3.0239999294281</v>
       </c>
       <c r="G62" t="n">
-        <v>2.72297358512878</v>
+        <v>2.72297334671021</v>
       </c>
       <c r="H62" t="n">
         <v>610853</v>
@@ -2196,7 +2196,7 @@
         <v>2.99799990653992</v>
       </c>
       <c r="G63" t="n">
-        <v>2.69956135749817</v>
+        <v>2.69956159591675</v>
       </c>
       <c r="H63" t="n">
         <v>323387</v>
@@ -2312,7 +2312,7 @@
         <v>2.84599995613098</v>
       </c>
       <c r="G67" t="n">
-        <v>2.56269240379333</v>
+        <v>2.56269264221191</v>
       </c>
       <c r="H67" t="n">
         <v>325027</v>
@@ -2428,7 +2428,7 @@
         <v>2.81599998474121</v>
       </c>
       <c r="G71" t="n">
-        <v>2.53567886352539</v>
+        <v>2.53567910194397</v>
       </c>
       <c r="H71" t="n">
         <v>188200</v>
@@ -2457,7 +2457,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G72" t="n">
-        <v>2.49425792694092</v>
+        <v>2.4942581653595</v>
       </c>
       <c r="H72" t="n">
         <v>268719</v>
@@ -2544,7 +2544,7 @@
         <v>2.81399989128113</v>
       </c>
       <c r="G75" t="n">
-        <v>2.53387784957886</v>
+        <v>2.53387808799744</v>
       </c>
       <c r="H75" t="n">
         <v>173870</v>
@@ -2631,7 +2631,7 @@
         <v>2.83599996566772</v>
       </c>
       <c r="G78" t="n">
-        <v>2.55368828773499</v>
+        <v>2.55368804931641</v>
       </c>
       <c r="H78" t="n">
         <v>311069</v>
@@ -2718,7 +2718,7 @@
         <v>2.80200004577637</v>
       </c>
       <c r="G81" t="n">
-        <v>2.5230724811554</v>
+        <v>2.52307271957397</v>
       </c>
       <c r="H81" t="n">
         <v>98753</v>
@@ -2747,7 +2747,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G82" t="n">
-        <v>2.49425792694092</v>
+        <v>2.4942581653595</v>
       </c>
       <c r="H82" t="n">
         <v>89415</v>
@@ -2776,7 +2776,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G83" t="n">
-        <v>2.52127170562744</v>
+        <v>2.52127194404602</v>
       </c>
       <c r="H83" t="n">
         <v>119812</v>
@@ -2979,7 +2979,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G90" t="n">
-        <v>2.46724438667297</v>
+        <v>2.46724462509155</v>
       </c>
       <c r="H90" t="n">
         <v>158160</v>
@@ -3095,7 +3095,7 @@
         <v>2.84599995613098</v>
       </c>
       <c r="G94" t="n">
-        <v>2.56269240379333</v>
+        <v>2.56269264221191</v>
       </c>
       <c r="H94" t="n">
         <v>207064</v>
@@ -3182,7 +3182,7 @@
         <v>2.84400010108948</v>
       </c>
       <c r="G97" t="n">
-        <v>2.56089186668396</v>
+        <v>2.56089210510254</v>
       </c>
       <c r="H97" t="n">
         <v>709527</v>
@@ -3327,7 +3327,7 @@
         <v>3.07599997520447</v>
       </c>
       <c r="G102" t="n">
-        <v>2.7697970867157</v>
+        <v>2.76979732513428</v>
       </c>
       <c r="H102" t="n">
         <v>1350396</v>
@@ -3356,7 +3356,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G103" t="n">
-        <v>2.7283763885498</v>
+        <v>2.72837615013123</v>
       </c>
       <c r="H103" t="n">
         <v>552357</v>
@@ -3414,7 +3414,7 @@
         <v>3.04800009727478</v>
       </c>
       <c r="G105" t="n">
-        <v>2.74458432197571</v>
+        <v>2.74458456039429</v>
       </c>
       <c r="H105" t="n">
         <v>558900</v>
@@ -3733,7 +3733,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G116" t="n">
-        <v>2.6563401222229</v>
+        <v>2.65633988380432</v>
       </c>
       <c r="H116" t="n">
         <v>209509</v>
@@ -3762,7 +3762,7 @@
         <v>2.98600006103516</v>
       </c>
       <c r="G117" t="n">
-        <v>2.68875646591187</v>
+        <v>2.68875622749329</v>
       </c>
       <c r="H117" t="n">
         <v>230218</v>
@@ -3878,7 +3878,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G121" t="n">
-        <v>2.68335366249084</v>
+        <v>2.68335342407227</v>
       </c>
       <c r="H121" t="n">
         <v>230872</v>
@@ -3907,7 +3907,7 @@
         <v>3.00200009346008</v>
       </c>
       <c r="G122" t="n">
-        <v>2.70316338539124</v>
+        <v>2.70316362380981</v>
       </c>
       <c r="H122" t="n">
         <v>492519</v>
@@ -3994,7 +3994,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G125" t="n">
-        <v>2.6563401222229</v>
+        <v>2.65633988380432</v>
       </c>
       <c r="H125" t="n">
         <v>301292</v>
@@ -4081,7 +4081,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G128" t="n">
-        <v>2.68335366249084</v>
+        <v>2.68335342407227</v>
       </c>
       <c r="H128" t="n">
         <v>601683</v>
@@ -4139,7 +4139,7 @@
         <v>2.92799997329712</v>
       </c>
       <c r="G130" t="n">
-        <v>2.63652968406677</v>
+        <v>2.63652992248535</v>
       </c>
       <c r="H130" t="n">
         <v>329492</v>
@@ -4371,7 +4371,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G138" t="n">
-        <v>2.55728960037231</v>
+        <v>2.55728983879089</v>
       </c>
       <c r="H138" t="n">
         <v>102337</v>
@@ -4400,7 +4400,7 @@
         <v>2.83200001716614</v>
       </c>
       <c r="G139" t="n">
-        <v>2.5500864982605</v>
+        <v>2.55008625984192</v>
       </c>
       <c r="H139" t="n">
         <v>63393</v>
@@ -4516,7 +4516,7 @@
         <v>2.84400010108948</v>
       </c>
       <c r="G143" t="n">
-        <v>2.56089186668396</v>
+        <v>2.56089210510254</v>
       </c>
       <c r="H143" t="n">
         <v>127287</v>
@@ -4603,7 +4603,7 @@
         <v>2.84599995613098</v>
       </c>
       <c r="G146" t="n">
-        <v>2.56269240379333</v>
+        <v>2.56269264221191</v>
       </c>
       <c r="H146" t="n">
         <v>95512</v>
@@ -4661,7 +4661,7 @@
         <v>2.86800003051758</v>
       </c>
       <c r="G148" t="n">
-        <v>2.58250284194946</v>
+        <v>2.58250260353088</v>
       </c>
       <c r="H148" t="n">
         <v>580188</v>
@@ -4777,7 +4777,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G152" t="n">
-        <v>2.6563401222229</v>
+        <v>2.65633988380432</v>
       </c>
       <c r="H152" t="n">
         <v>326136</v>
@@ -4893,7 +4893,7 @@
         <v>2.88800001144409</v>
       </c>
       <c r="G156" t="n">
-        <v>2.6005117893219</v>
+        <v>2.60051202774048</v>
       </c>
       <c r="H156" t="n">
         <v>309123</v>
@@ -4922,7 +4922,7 @@
         <v>2.81599998474121</v>
       </c>
       <c r="G157" t="n">
-        <v>2.53567886352539</v>
+        <v>2.53567910194397</v>
       </c>
       <c r="H157" t="n">
         <v>258393</v>
@@ -5241,7 +5241,7 @@
         <v>3.2260000705719</v>
       </c>
       <c r="G168" t="n">
-        <v>2.90486550331116</v>
+        <v>2.90486526489258</v>
       </c>
       <c r="H168" t="n">
         <v>1684867</v>
@@ -5357,7 +5357,7 @@
         <v>3.50200009346008</v>
       </c>
       <c r="G172" t="n">
-        <v>3.15339088439941</v>
+        <v>3.15339064598083</v>
       </c>
       <c r="H172" t="n">
         <v>2891760</v>
@@ -5444,7 +5444,7 @@
         <v>3.50600004196167</v>
       </c>
       <c r="G175" t="n">
-        <v>3.15699219703674</v>
+        <v>3.15699243545532</v>
       </c>
       <c r="H175" t="n">
         <v>1959547</v>
@@ -5531,7 +5531,7 @@
         <v>3.31800007820129</v>
       </c>
       <c r="G178" t="n">
-        <v>2.98770689964294</v>
+        <v>2.98770713806152</v>
       </c>
       <c r="H178" t="n">
         <v>742754</v>
@@ -5589,7 +5589,7 @@
         <v>3.25200009346008</v>
       </c>
       <c r="G180" t="n">
-        <v>2.92827725410461</v>
+        <v>2.92827701568604</v>
       </c>
       <c r="H180" t="n">
         <v>687235</v>
@@ -5850,7 +5850,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G189" t="n">
-        <v>2.80941700935364</v>
+        <v>2.80941724777222</v>
       </c>
       <c r="H189" t="n">
         <v>424007</v>
@@ -5908,7 +5908,7 @@
         <v>3.18199992179871</v>
       </c>
       <c r="G191" t="n">
-        <v>2.86524534225464</v>
+        <v>2.86524510383606</v>
       </c>
       <c r="H191" t="n">
         <v>278666</v>
@@ -5937,7 +5937,7 @@
         <v>3.16799998283386</v>
       </c>
       <c r="G192" t="n">
-        <v>2.85263895988464</v>
+        <v>2.85263872146606</v>
       </c>
       <c r="H192" t="n">
         <v>381457</v>
@@ -5966,7 +5966,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G193" t="n">
-        <v>2.83643102645874</v>
+        <v>2.83643078804016</v>
       </c>
       <c r="H193" t="n">
         <v>295806</v>
@@ -6082,7 +6082,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G197" t="n">
-        <v>2.84993767738342</v>
+        <v>2.84993743896484</v>
       </c>
       <c r="H197" t="n">
         <v>267637</v>
@@ -6111,7 +6111,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G198" t="n">
-        <v>2.83643102645874</v>
+        <v>2.83643078804016</v>
       </c>
       <c r="H198" t="n">
         <v>234594</v>
@@ -6140,7 +6140,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G199" t="n">
-        <v>2.80941700935364</v>
+        <v>2.80941724777222</v>
       </c>
       <c r="H199" t="n">
         <v>254363</v>
@@ -6169,7 +6169,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G200" t="n">
-        <v>2.79591012001038</v>
+        <v>2.79591035842896</v>
       </c>
       <c r="H200" t="n">
         <v>277567</v>
@@ -6227,7 +6227,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G202" t="n">
-        <v>2.77339887619019</v>
+        <v>2.77339863777161</v>
       </c>
       <c r="H202" t="n">
         <v>272137</v>
@@ -6256,7 +6256,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G203" t="n">
-        <v>2.76439452171326</v>
+        <v>2.76439428329468</v>
       </c>
       <c r="H203" t="n">
         <v>271367</v>
@@ -6285,7 +6285,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G204" t="n">
-        <v>2.74638533592224</v>
+        <v>2.74638509750366</v>
       </c>
       <c r="H204" t="n">
         <v>300656</v>
@@ -6401,7 +6401,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G208" t="n">
-        <v>2.66534423828125</v>
+        <v>2.66534447669983</v>
       </c>
       <c r="H208" t="n">
         <v>290531</v>
@@ -6488,7 +6488,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G211" t="n">
-        <v>2.57529878616333</v>
+        <v>2.57529902458191</v>
       </c>
       <c r="H211" t="n">
         <v>2239887</v>
@@ -6546,7 +6546,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G213" t="n">
-        <v>2.52127170562744</v>
+        <v>2.52127194404602</v>
       </c>
       <c r="H213" t="n">
         <v>657781</v>
@@ -6575,7 +6575,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G214" t="n">
-        <v>2.55728960037231</v>
+        <v>2.55728983879089</v>
       </c>
       <c r="H214" t="n">
         <v>507186</v>
@@ -6604,7 +6604,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G215" t="n">
-        <v>2.57529878616333</v>
+        <v>2.57529902458191</v>
       </c>
       <c r="H215" t="n">
         <v>1072643</v>
@@ -6749,7 +6749,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G220" t="n">
-        <v>2.66534423828125</v>
+        <v>2.66534447669983</v>
       </c>
       <c r="H220" t="n">
         <v>807427</v>
@@ -6778,7 +6778,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G221" t="n">
-        <v>2.68785548210144</v>
+        <v>2.68785572052002</v>
       </c>
       <c r="H221" t="n">
         <v>693872</v>
@@ -6836,7 +6836,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G223" t="n">
-        <v>2.68785548210144</v>
+        <v>2.68785572052002</v>
       </c>
       <c r="H223" t="n">
         <v>289774</v>
@@ -6865,7 +6865,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G224" t="n">
-        <v>2.71486926078796</v>
+        <v>2.71486949920654</v>
       </c>
       <c r="H224" t="n">
         <v>302122</v>
@@ -6952,7 +6952,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G227" t="n">
-        <v>2.80941700935364</v>
+        <v>2.80941724777222</v>
       </c>
       <c r="H227" t="n">
         <v>1329390</v>
@@ -7126,7 +7126,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G233" t="n">
-        <v>2.76439452171326</v>
+        <v>2.76439428329468</v>
       </c>
       <c r="H233" t="n">
         <v>219195</v>
@@ -7474,7 +7474,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G245" t="n">
-        <v>2.77339887619019</v>
+        <v>2.77339863777161</v>
       </c>
       <c r="H245" t="n">
         <v>803152</v>
@@ -7619,7 +7619,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G250" t="n">
-        <v>2.6563401222229</v>
+        <v>2.65633988380432</v>
       </c>
       <c r="H250" t="n">
         <v>375208</v>
@@ -7648,7 +7648,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G251" t="n">
-        <v>2.66534423828125</v>
+        <v>2.66534447669983</v>
       </c>
       <c r="H251" t="n">
         <v>193370</v>
@@ -7677,7 +7677,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G252" t="n">
-        <v>2.6563401222229</v>
+        <v>2.65633988380432</v>
       </c>
       <c r="H252" t="n">
         <v>198249</v>
@@ -7706,7 +7706,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G253" t="n">
-        <v>2.68785548210144</v>
+        <v>2.68785572052002</v>
       </c>
       <c r="H253" t="n">
         <v>521926</v>
@@ -24793,6 +24793,35 @@
         <v>115099</v>
       </c>
       <c r="I842" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="s">
+        <v>9</v>
+      </c>
+      <c r="B843" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C843" t="n">
+        <v>2.65000009536743</v>
+      </c>
+      <c r="D843" t="n">
+        <v>2.69199991226196</v>
+      </c>
+      <c r="E843" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="F843" t="n">
+        <v>2.69000005722046</v>
+      </c>
+      <c r="G843" t="n">
+        <v>2.69000005722046</v>
+      </c>
+      <c r="H843" t="n">
+        <v>182992</v>
+      </c>
+      <c r="I843" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/YACHT.MI.xlsx
+++ b/data/YACHT.MI.xlsx
@@ -427,7 +427,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G2" t="n">
-        <v>2.68335342407227</v>
+        <v>2.68335366249084</v>
       </c>
       <c r="H2" t="n">
         <v>9271589</v>
@@ -485,7 +485,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G4" t="n">
-        <v>2.57529902458191</v>
+        <v>2.57529878616333</v>
       </c>
       <c r="H4" t="n">
         <v>2742684</v>
@@ -862,7 +862,7 @@
         <v>2.99799990653992</v>
       </c>
       <c r="G17" t="n">
-        <v>2.69956159591675</v>
+        <v>2.69956135749817</v>
       </c>
       <c r="H17" t="n">
         <v>721392</v>
@@ -891,7 +891,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G18" t="n">
-        <v>2.84543538093567</v>
+        <v>2.84543514251709</v>
       </c>
       <c r="H18" t="n">
         <v>1195492</v>
@@ -920,7 +920,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G19" t="n">
-        <v>2.81842184066772</v>
+        <v>2.81842160224915</v>
       </c>
       <c r="H19" t="n">
         <v>1196581</v>
@@ -949,7 +949,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G20" t="n">
-        <v>2.83643078804016</v>
+        <v>2.83643102645874</v>
       </c>
       <c r="H20" t="n">
         <v>573734</v>
@@ -1152,7 +1152,7 @@
         <v>3.2039999961853</v>
       </c>
       <c r="G27" t="n">
-        <v>2.88505530357361</v>
+        <v>2.88505506515503</v>
       </c>
       <c r="H27" t="n">
         <v>920776</v>
@@ -1297,7 +1297,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G32" t="n">
-        <v>2.74638509750366</v>
+        <v>2.74638533592224</v>
       </c>
       <c r="H32" t="n">
         <v>706131</v>
@@ -1326,7 +1326,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G33" t="n">
-        <v>2.72837615013123</v>
+        <v>2.7283763885498</v>
       </c>
       <c r="H33" t="n">
         <v>552267</v>
@@ -1500,7 +1500,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G39" t="n">
-        <v>2.65633988380432</v>
+        <v>2.6563401222229</v>
       </c>
       <c r="H39" t="n">
         <v>413206</v>
@@ -1616,7 +1616,7 @@
         <v>2.90599989891052</v>
       </c>
       <c r="G43" t="n">
-        <v>2.6167197227478</v>
+        <v>2.61671996116638</v>
       </c>
       <c r="H43" t="n">
         <v>160349</v>
@@ -1790,7 +1790,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G49" t="n">
-        <v>2.65633988380432</v>
+        <v>2.6563401222229</v>
       </c>
       <c r="H49" t="n">
         <v>278184</v>
@@ -1848,7 +1848,7 @@
         <v>2.89199995994568</v>
       </c>
       <c r="G51" t="n">
-        <v>2.60411334037781</v>
+        <v>2.60411357879639</v>
       </c>
       <c r="H51" t="n">
         <v>301022</v>
@@ -1993,7 +1993,7 @@
         <v>2.8840000629425</v>
       </c>
       <c r="G56" t="n">
-        <v>2.59690999984741</v>
+        <v>2.59690976142883</v>
       </c>
       <c r="H56" t="n">
         <v>223974</v>
@@ -2080,7 +2080,7 @@
         <v>2.93600010871887</v>
       </c>
       <c r="G59" t="n">
-        <v>2.64373350143433</v>
+        <v>2.64373373985291</v>
       </c>
       <c r="H59" t="n">
         <v>1235755</v>
@@ -2138,7 +2138,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G61" t="n">
-        <v>2.65633988380432</v>
+        <v>2.6563401222229</v>
       </c>
       <c r="H61" t="n">
         <v>481432</v>
@@ -2167,7 +2167,7 @@
         <v>3.0239999294281</v>
       </c>
       <c r="G62" t="n">
-        <v>2.72297334671021</v>
+        <v>2.72297358512878</v>
       </c>
       <c r="H62" t="n">
         <v>610853</v>
@@ -2196,7 +2196,7 @@
         <v>2.99799990653992</v>
       </c>
       <c r="G63" t="n">
-        <v>2.69956159591675</v>
+        <v>2.69956135749817</v>
       </c>
       <c r="H63" t="n">
         <v>323387</v>
@@ -2312,7 +2312,7 @@
         <v>2.84599995613098</v>
       </c>
       <c r="G67" t="n">
-        <v>2.56269264221191</v>
+        <v>2.56269240379333</v>
       </c>
       <c r="H67" t="n">
         <v>325027</v>
@@ -2428,7 +2428,7 @@
         <v>2.81599998474121</v>
       </c>
       <c r="G71" t="n">
-        <v>2.53567910194397</v>
+        <v>2.53567886352539</v>
       </c>
       <c r="H71" t="n">
         <v>188200</v>
@@ -2457,7 +2457,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G72" t="n">
-        <v>2.4942581653595</v>
+        <v>2.49425792694092</v>
       </c>
       <c r="H72" t="n">
         <v>268719</v>
@@ -2544,7 +2544,7 @@
         <v>2.81399989128113</v>
       </c>
       <c r="G75" t="n">
-        <v>2.53387808799744</v>
+        <v>2.53387784957886</v>
       </c>
       <c r="H75" t="n">
         <v>173870</v>
@@ -2631,7 +2631,7 @@
         <v>2.83599996566772</v>
       </c>
       <c r="G78" t="n">
-        <v>2.55368804931641</v>
+        <v>2.55368828773499</v>
       </c>
       <c r="H78" t="n">
         <v>311069</v>
@@ -2718,7 +2718,7 @@
         <v>2.80200004577637</v>
       </c>
       <c r="G81" t="n">
-        <v>2.52307271957397</v>
+        <v>2.5230724811554</v>
       </c>
       <c r="H81" t="n">
         <v>98753</v>
@@ -2747,7 +2747,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G82" t="n">
-        <v>2.4942581653595</v>
+        <v>2.49425792694092</v>
       </c>
       <c r="H82" t="n">
         <v>89415</v>
@@ -2776,7 +2776,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G83" t="n">
-        <v>2.52127194404602</v>
+        <v>2.52127170562744</v>
       </c>
       <c r="H83" t="n">
         <v>119812</v>
@@ -2979,7 +2979,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G90" t="n">
-        <v>2.46724462509155</v>
+        <v>2.46724438667297</v>
       </c>
       <c r="H90" t="n">
         <v>158160</v>
@@ -3095,7 +3095,7 @@
         <v>2.84599995613098</v>
       </c>
       <c r="G94" t="n">
-        <v>2.56269264221191</v>
+        <v>2.56269240379333</v>
       </c>
       <c r="H94" t="n">
         <v>207064</v>
@@ -3182,7 +3182,7 @@
         <v>2.84400010108948</v>
       </c>
       <c r="G97" t="n">
-        <v>2.56089210510254</v>
+        <v>2.56089186668396</v>
       </c>
       <c r="H97" t="n">
         <v>709527</v>
@@ -3327,7 +3327,7 @@
         <v>3.07599997520447</v>
       </c>
       <c r="G102" t="n">
-        <v>2.76979732513428</v>
+        <v>2.7697970867157</v>
       </c>
       <c r="H102" t="n">
         <v>1350396</v>
@@ -3356,7 +3356,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G103" t="n">
-        <v>2.72837615013123</v>
+        <v>2.7283763885498</v>
       </c>
       <c r="H103" t="n">
         <v>552357</v>
@@ -3414,7 +3414,7 @@
         <v>3.04800009727478</v>
       </c>
       <c r="G105" t="n">
-        <v>2.74458456039429</v>
+        <v>2.74458432197571</v>
       </c>
       <c r="H105" t="n">
         <v>558900</v>
@@ -3733,7 +3733,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G116" t="n">
-        <v>2.65633988380432</v>
+        <v>2.6563401222229</v>
       </c>
       <c r="H116" t="n">
         <v>209509</v>
@@ -3762,7 +3762,7 @@
         <v>2.98600006103516</v>
       </c>
       <c r="G117" t="n">
-        <v>2.68875622749329</v>
+        <v>2.68875646591187</v>
       </c>
       <c r="H117" t="n">
         <v>230218</v>
@@ -3878,7 +3878,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G121" t="n">
-        <v>2.68335342407227</v>
+        <v>2.68335366249084</v>
       </c>
       <c r="H121" t="n">
         <v>230872</v>
@@ -3907,7 +3907,7 @@
         <v>3.00200009346008</v>
       </c>
       <c r="G122" t="n">
-        <v>2.70316362380981</v>
+        <v>2.70316338539124</v>
       </c>
       <c r="H122" t="n">
         <v>492519</v>
@@ -3994,7 +3994,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G125" t="n">
-        <v>2.65633988380432</v>
+        <v>2.6563401222229</v>
       </c>
       <c r="H125" t="n">
         <v>301292</v>
@@ -4081,7 +4081,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G128" t="n">
-        <v>2.68335342407227</v>
+        <v>2.68335366249084</v>
       </c>
       <c r="H128" t="n">
         <v>601683</v>
@@ -4139,7 +4139,7 @@
         <v>2.92799997329712</v>
       </c>
       <c r="G130" t="n">
-        <v>2.63652992248535</v>
+        <v>2.63652968406677</v>
       </c>
       <c r="H130" t="n">
         <v>329492</v>
@@ -4371,7 +4371,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G138" t="n">
-        <v>2.55728983879089</v>
+        <v>2.55728960037231</v>
       </c>
       <c r="H138" t="n">
         <v>102337</v>
@@ -4400,7 +4400,7 @@
         <v>2.83200001716614</v>
       </c>
       <c r="G139" t="n">
-        <v>2.55008625984192</v>
+        <v>2.5500864982605</v>
       </c>
       <c r="H139" t="n">
         <v>63393</v>
@@ -4516,7 +4516,7 @@
         <v>2.84400010108948</v>
       </c>
       <c r="G143" t="n">
-        <v>2.56089210510254</v>
+        <v>2.56089186668396</v>
       </c>
       <c r="H143" t="n">
         <v>127287</v>
@@ -4603,7 +4603,7 @@
         <v>2.84599995613098</v>
       </c>
       <c r="G146" t="n">
-        <v>2.56269264221191</v>
+        <v>2.56269240379333</v>
       </c>
       <c r="H146" t="n">
         <v>95512</v>
@@ -4661,7 +4661,7 @@
         <v>2.86800003051758</v>
       </c>
       <c r="G148" t="n">
-        <v>2.58250260353088</v>
+        <v>2.58250284194946</v>
       </c>
       <c r="H148" t="n">
         <v>580188</v>
@@ -4777,7 +4777,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G152" t="n">
-        <v>2.65633988380432</v>
+        <v>2.6563401222229</v>
       </c>
       <c r="H152" t="n">
         <v>326136</v>
@@ -4893,7 +4893,7 @@
         <v>2.88800001144409</v>
       </c>
       <c r="G156" t="n">
-        <v>2.60051202774048</v>
+        <v>2.6005117893219</v>
       </c>
       <c r="H156" t="n">
         <v>309123</v>
@@ -4922,7 +4922,7 @@
         <v>2.81599998474121</v>
       </c>
       <c r="G157" t="n">
-        <v>2.53567910194397</v>
+        <v>2.53567886352539</v>
       </c>
       <c r="H157" t="n">
         <v>258393</v>
@@ -5241,7 +5241,7 @@
         <v>3.2260000705719</v>
       </c>
       <c r="G168" t="n">
-        <v>2.90486526489258</v>
+        <v>2.90486550331116</v>
       </c>
       <c r="H168" t="n">
         <v>1684867</v>
@@ -5357,7 +5357,7 @@
         <v>3.50200009346008</v>
       </c>
       <c r="G172" t="n">
-        <v>3.15339064598083</v>
+        <v>3.15339088439941</v>
       </c>
       <c r="H172" t="n">
         <v>2891760</v>
@@ -5444,7 +5444,7 @@
         <v>3.50600004196167</v>
       </c>
       <c r="G175" t="n">
-        <v>3.15699243545532</v>
+        <v>3.15699219703674</v>
       </c>
       <c r="H175" t="n">
         <v>1959547</v>
@@ -5531,7 +5531,7 @@
         <v>3.31800007820129</v>
       </c>
       <c r="G178" t="n">
-        <v>2.98770713806152</v>
+        <v>2.98770689964294</v>
       </c>
       <c r="H178" t="n">
         <v>742754</v>
@@ -5589,7 +5589,7 @@
         <v>3.25200009346008</v>
       </c>
       <c r="G180" t="n">
-        <v>2.92827701568604</v>
+        <v>2.92827725410461</v>
       </c>
       <c r="H180" t="n">
         <v>687235</v>
@@ -5850,7 +5850,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G189" t="n">
-        <v>2.80941724777222</v>
+        <v>2.80941700935364</v>
       </c>
       <c r="H189" t="n">
         <v>424007</v>
@@ -5908,7 +5908,7 @@
         <v>3.18199992179871</v>
       </c>
       <c r="G191" t="n">
-        <v>2.86524510383606</v>
+        <v>2.86524534225464</v>
       </c>
       <c r="H191" t="n">
         <v>278666</v>
@@ -5937,7 +5937,7 @@
         <v>3.16799998283386</v>
       </c>
       <c r="G192" t="n">
-        <v>2.85263872146606</v>
+        <v>2.85263895988464</v>
       </c>
       <c r="H192" t="n">
         <v>381457</v>
@@ -5966,7 +5966,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G193" t="n">
-        <v>2.83643078804016</v>
+        <v>2.83643102645874</v>
       </c>
       <c r="H193" t="n">
         <v>295806</v>
@@ -6082,7 +6082,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G197" t="n">
-        <v>2.84993743896484</v>
+        <v>2.84993767738342</v>
       </c>
       <c r="H197" t="n">
         <v>267637</v>
@@ -6111,7 +6111,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G198" t="n">
-        <v>2.83643078804016</v>
+        <v>2.83643102645874</v>
       </c>
       <c r="H198" t="n">
         <v>234594</v>
@@ -6140,7 +6140,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G199" t="n">
-        <v>2.80941724777222</v>
+        <v>2.80941700935364</v>
       </c>
       <c r="H199" t="n">
         <v>254363</v>
@@ -6169,7 +6169,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G200" t="n">
-        <v>2.79591035842896</v>
+        <v>2.79591012001038</v>
       </c>
       <c r="H200" t="n">
         <v>277567</v>
@@ -6227,7 +6227,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G202" t="n">
-        <v>2.77339863777161</v>
+        <v>2.77339887619019</v>
       </c>
       <c r="H202" t="n">
         <v>272137</v>
@@ -6256,7 +6256,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G203" t="n">
-        <v>2.76439428329468</v>
+        <v>2.76439452171326</v>
       </c>
       <c r="H203" t="n">
         <v>271367</v>
@@ -6285,7 +6285,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G204" t="n">
-        <v>2.74638509750366</v>
+        <v>2.74638533592224</v>
       </c>
       <c r="H204" t="n">
         <v>300656</v>
@@ -6401,7 +6401,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G208" t="n">
-        <v>2.66534447669983</v>
+        <v>2.66534423828125</v>
       </c>
       <c r="H208" t="n">
         <v>290531</v>
@@ -6488,7 +6488,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G211" t="n">
-        <v>2.57529902458191</v>
+        <v>2.57529878616333</v>
       </c>
       <c r="H211" t="n">
         <v>2239887</v>
@@ -6546,7 +6546,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G213" t="n">
-        <v>2.52127194404602</v>
+        <v>2.52127170562744</v>
       </c>
       <c r="H213" t="n">
         <v>657781</v>
@@ -6575,7 +6575,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G214" t="n">
-        <v>2.55728983879089</v>
+        <v>2.55728960037231</v>
       </c>
       <c r="H214" t="n">
         <v>507186</v>
@@ -6604,7 +6604,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G215" t="n">
-        <v>2.57529902458191</v>
+        <v>2.57529878616333</v>
       </c>
       <c r="H215" t="n">
         <v>1072643</v>
@@ -6749,7 +6749,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G220" t="n">
-        <v>2.66534447669983</v>
+        <v>2.66534423828125</v>
       </c>
       <c r="H220" t="n">
         <v>807427</v>
@@ -6778,7 +6778,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G221" t="n">
-        <v>2.68785572052002</v>
+        <v>2.68785548210144</v>
       </c>
       <c r="H221" t="n">
         <v>693872</v>
@@ -6836,7 +6836,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G223" t="n">
-        <v>2.68785572052002</v>
+        <v>2.68785548210144</v>
       </c>
       <c r="H223" t="n">
         <v>289774</v>
@@ -6865,7 +6865,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G224" t="n">
-        <v>2.71486949920654</v>
+        <v>2.71486926078796</v>
       </c>
       <c r="H224" t="n">
         <v>302122</v>
@@ -6952,7 +6952,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G227" t="n">
-        <v>2.80941724777222</v>
+        <v>2.80941700935364</v>
       </c>
       <c r="H227" t="n">
         <v>1329390</v>
@@ -7126,7 +7126,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G233" t="n">
-        <v>2.76439428329468</v>
+        <v>2.76439452171326</v>
       </c>
       <c r="H233" t="n">
         <v>219195</v>
@@ -7474,7 +7474,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G245" t="n">
-        <v>2.77339863777161</v>
+        <v>2.77339887619019</v>
       </c>
       <c r="H245" t="n">
         <v>803152</v>
@@ -7619,7 +7619,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G250" t="n">
-        <v>2.65633988380432</v>
+        <v>2.6563401222229</v>
       </c>
       <c r="H250" t="n">
         <v>375208</v>
@@ -7648,7 +7648,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G251" t="n">
-        <v>2.66534447669983</v>
+        <v>2.66534423828125</v>
       </c>
       <c r="H251" t="n">
         <v>193370</v>
@@ -7677,7 +7677,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G252" t="n">
-        <v>2.65633988380432</v>
+        <v>2.6563401222229</v>
       </c>
       <c r="H252" t="n">
         <v>198249</v>
@@ -7706,7 +7706,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G253" t="n">
-        <v>2.68785572052002</v>
+        <v>2.68785548210144</v>
       </c>
       <c r="H253" t="n">
         <v>521926</v>
@@ -24822,6 +24822,35 @@
         <v>182992</v>
       </c>
       <c r="I843" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="s">
+        <v>9</v>
+      </c>
+      <c r="B844" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C844" t="n">
+        <v>2.71000003814697</v>
+      </c>
+      <c r="D844" t="n">
+        <v>2.71000003814697</v>
+      </c>
+      <c r="E844" t="n">
+        <v>2.65000009536743</v>
+      </c>
+      <c r="F844" t="n">
+        <v>2.67799997329712</v>
+      </c>
+      <c r="G844" t="n">
+        <v>2.67799997329712</v>
+      </c>
+      <c r="H844" t="n">
+        <v>62566</v>
+      </c>
+      <c r="I844" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/YACHT.MI.xlsx
+++ b/data/YACHT.MI.xlsx
@@ -24854,6 +24854,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="845">
+      <c r="A845" t="s">
+        <v>9</v>
+      </c>
+      <c r="B845" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C845" t="n">
+        <v>2.65000009536743</v>
+      </c>
+      <c r="D845" t="n">
+        <v>2.69400000572205</v>
+      </c>
+      <c r="E845" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="F845" t="n">
+        <v>2.64199995994568</v>
+      </c>
+      <c r="G845" t="n">
+        <v>2.64199995994568</v>
+      </c>
+      <c r="H845" t="n">
+        <v>104369</v>
+      </c>
+      <c r="I845" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/YACHT.MI.xlsx
+++ b/data/YACHT.MI.xlsx
@@ -427,7 +427,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G2" t="n">
-        <v>2.68335366249084</v>
+        <v>2.68335342407227</v>
       </c>
       <c r="H2" t="n">
         <v>9271589</v>
@@ -456,7 +456,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G3" t="n">
-        <v>2.62932634353638</v>
+        <v>2.6293261051178</v>
       </c>
       <c r="H3" t="n">
         <v>5523202</v>
@@ -485,7 +485,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G4" t="n">
-        <v>2.57529878616333</v>
+        <v>2.57529902458191</v>
       </c>
       <c r="H4" t="n">
         <v>2742684</v>
@@ -572,7 +572,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G7" t="n">
-        <v>2.62032175064087</v>
+        <v>2.62032198905945</v>
       </c>
       <c r="H7" t="n">
         <v>462954</v>
@@ -601,7 +601,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G8" t="n">
-        <v>2.62932634353638</v>
+        <v>2.6293261051178</v>
       </c>
       <c r="H8" t="n">
         <v>470527</v>
@@ -630,7 +630,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G9" t="n">
-        <v>2.60231256484985</v>
+        <v>2.60231280326843</v>
       </c>
       <c r="H9" t="n">
         <v>370604</v>
@@ -659,7 +659,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G10" t="n">
-        <v>2.62932634353638</v>
+        <v>2.6293261051178</v>
       </c>
       <c r="H10" t="n">
         <v>167157</v>
@@ -688,7 +688,7 @@
         <v>2.88199996948242</v>
       </c>
       <c r="G11" t="n">
-        <v>2.59510898590088</v>
+        <v>2.5951087474823</v>
       </c>
       <c r="H11" t="n">
         <v>527158</v>
@@ -746,7 +746,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G13" t="n">
-        <v>2.60231256484985</v>
+        <v>2.60231280326843</v>
       </c>
       <c r="H13" t="n">
         <v>258873</v>
@@ -833,7 +833,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G16" t="n">
-        <v>2.62932634353638</v>
+        <v>2.6293261051178</v>
       </c>
       <c r="H16" t="n">
         <v>234246</v>
@@ -862,7 +862,7 @@
         <v>2.99799990653992</v>
       </c>
       <c r="G17" t="n">
-        <v>2.69956135749817</v>
+        <v>2.69956159591675</v>
       </c>
       <c r="H17" t="n">
         <v>721392</v>
@@ -891,7 +891,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G18" t="n">
-        <v>2.84543514251709</v>
+        <v>2.84543561935425</v>
       </c>
       <c r="H18" t="n">
         <v>1195492</v>
@@ -920,7 +920,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G19" t="n">
-        <v>2.81842160224915</v>
+        <v>2.81842184066772</v>
       </c>
       <c r="H19" t="n">
         <v>1196581</v>
@@ -1152,7 +1152,7 @@
         <v>3.2039999961853</v>
       </c>
       <c r="G27" t="n">
-        <v>2.88505506515503</v>
+        <v>2.88505530357361</v>
       </c>
       <c r="H27" t="n">
         <v>920776</v>
@@ -1210,7 +1210,7 @@
         <v>3.12199997901917</v>
       </c>
       <c r="G29" t="n">
-        <v>2.81121778488159</v>
+        <v>2.81121802330017</v>
       </c>
       <c r="H29" t="n">
         <v>544144</v>
@@ -1239,7 +1239,7 @@
         <v>3.17799997329712</v>
       </c>
       <c r="G30" t="n">
-        <v>2.86164355278015</v>
+        <v>2.86164331436157</v>
       </c>
       <c r="H30" t="n">
         <v>594226</v>
@@ -1326,7 +1326,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G33" t="n">
-        <v>2.7283763885498</v>
+        <v>2.72837615013123</v>
       </c>
       <c r="H33" t="n">
         <v>552267</v>
@@ -1413,7 +1413,7 @@
         <v>2.96199989318848</v>
       </c>
       <c r="G36" t="n">
-        <v>2.66714525222778</v>
+        <v>2.66714549064636</v>
       </c>
       <c r="H36" t="n">
         <v>99000</v>
@@ -1442,7 +1442,7 @@
         <v>2.96199989318848</v>
       </c>
       <c r="G37" t="n">
-        <v>2.66714525222778</v>
+        <v>2.66714549064636</v>
       </c>
       <c r="H37" t="n">
         <v>318498</v>
@@ -1471,7 +1471,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G38" t="n">
-        <v>2.62932634353638</v>
+        <v>2.6293261051178</v>
       </c>
       <c r="H38" t="n">
         <v>113466</v>
@@ -1500,7 +1500,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G39" t="n">
-        <v>2.6563401222229</v>
+        <v>2.65633988380432</v>
       </c>
       <c r="H39" t="n">
         <v>413206</v>
@@ -1529,7 +1529,7 @@
         <v>2.93400001525879</v>
       </c>
       <c r="G40" t="n">
-        <v>2.64193248748779</v>
+        <v>2.64193272590637</v>
       </c>
       <c r="H40" t="n">
         <v>560977</v>
@@ -1616,7 +1616,7 @@
         <v>2.90599989891052</v>
       </c>
       <c r="G43" t="n">
-        <v>2.61671996116638</v>
+        <v>2.6167197227478</v>
       </c>
       <c r="H43" t="n">
         <v>160349</v>
@@ -1732,7 +1732,7 @@
         <v>2.91400003433228</v>
       </c>
       <c r="G47" t="n">
-        <v>2.62392354011536</v>
+        <v>2.62392377853394</v>
       </c>
       <c r="H47" t="n">
         <v>681087</v>
@@ -1761,7 +1761,7 @@
         <v>2.90799999237061</v>
       </c>
       <c r="G48" t="n">
-        <v>2.61852073669434</v>
+        <v>2.61852097511292</v>
       </c>
       <c r="H48" t="n">
         <v>395238</v>
@@ -1790,7 +1790,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G49" t="n">
-        <v>2.6563401222229</v>
+        <v>2.65633988380432</v>
       </c>
       <c r="H49" t="n">
         <v>278184</v>
@@ -1819,7 +1819,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G50" t="n">
-        <v>2.63833093643188</v>
+        <v>2.63833069801331</v>
       </c>
       <c r="H50" t="n">
         <v>440815</v>
@@ -1848,7 +1848,7 @@
         <v>2.89199995994568</v>
       </c>
       <c r="G51" t="n">
-        <v>2.60411357879639</v>
+        <v>2.60411334037781</v>
       </c>
       <c r="H51" t="n">
         <v>301022</v>
@@ -1877,7 +1877,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G52" t="n">
-        <v>2.58430361747742</v>
+        <v>2.58430337905884</v>
       </c>
       <c r="H52" t="n">
         <v>406342</v>
@@ -1935,7 +1935,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G54" t="n">
-        <v>2.62032175064087</v>
+        <v>2.62032198905945</v>
       </c>
       <c r="H54" t="n">
         <v>470047</v>
@@ -1993,7 +1993,7 @@
         <v>2.8840000629425</v>
       </c>
       <c r="G56" t="n">
-        <v>2.59690976142883</v>
+        <v>2.59690999984741</v>
       </c>
       <c r="H56" t="n">
         <v>223974</v>
@@ -2080,7 +2080,7 @@
         <v>2.93600010871887</v>
       </c>
       <c r="G59" t="n">
-        <v>2.64373373985291</v>
+        <v>2.64373350143433</v>
       </c>
       <c r="H59" t="n">
         <v>1235755</v>
@@ -2138,7 +2138,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G61" t="n">
-        <v>2.6563401222229</v>
+        <v>2.65633988380432</v>
       </c>
       <c r="H61" t="n">
         <v>481432</v>
@@ -2167,7 +2167,7 @@
         <v>3.0239999294281</v>
       </c>
       <c r="G62" t="n">
-        <v>2.72297358512878</v>
+        <v>2.72297334671021</v>
       </c>
       <c r="H62" t="n">
         <v>610853</v>
@@ -2196,7 +2196,7 @@
         <v>2.99799990653992</v>
       </c>
       <c r="G63" t="n">
-        <v>2.69956135749817</v>
+        <v>2.69956159591675</v>
       </c>
       <c r="H63" t="n">
         <v>323387</v>
@@ -2225,7 +2225,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G64" t="n">
-        <v>2.67434906959534</v>
+        <v>2.67434883117676</v>
       </c>
       <c r="H64" t="n">
         <v>215337</v>
@@ -2312,7 +2312,7 @@
         <v>2.84599995613098</v>
       </c>
       <c r="G67" t="n">
-        <v>2.56269240379333</v>
+        <v>2.56269264221191</v>
       </c>
       <c r="H67" t="n">
         <v>325027</v>
@@ -2341,7 +2341,7 @@
         <v>2.80399990081787</v>
       </c>
       <c r="G68" t="n">
-        <v>2.52487349510193</v>
+        <v>2.52487373352051</v>
       </c>
       <c r="H68" t="n">
         <v>241271</v>
@@ -2428,7 +2428,7 @@
         <v>2.81599998474121</v>
       </c>
       <c r="G71" t="n">
-        <v>2.53567886352539</v>
+        <v>2.53567910194397</v>
       </c>
       <c r="H71" t="n">
         <v>188200</v>
@@ -2457,7 +2457,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G72" t="n">
-        <v>2.49425792694092</v>
+        <v>2.4942581653595</v>
       </c>
       <c r="H72" t="n">
         <v>268719</v>
@@ -2486,7 +2486,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G73" t="n">
-        <v>2.58430361747742</v>
+        <v>2.58430337905884</v>
       </c>
       <c r="H73" t="n">
         <v>296618</v>
@@ -2544,7 +2544,7 @@
         <v>2.81399989128113</v>
       </c>
       <c r="G75" t="n">
-        <v>2.53387784957886</v>
+        <v>2.53387832641602</v>
       </c>
       <c r="H75" t="n">
         <v>173870</v>
@@ -2573,7 +2573,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G76" t="n">
-        <v>2.58430361747742</v>
+        <v>2.58430337905884</v>
       </c>
       <c r="H76" t="n">
         <v>271694</v>
@@ -2602,7 +2602,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G77" t="n">
-        <v>2.58430361747742</v>
+        <v>2.58430337905884</v>
       </c>
       <c r="H77" t="n">
         <v>304675</v>
@@ -2631,7 +2631,7 @@
         <v>2.83599996566772</v>
       </c>
       <c r="G78" t="n">
-        <v>2.55368828773499</v>
+        <v>2.55368804931641</v>
       </c>
       <c r="H78" t="n">
         <v>311069</v>
@@ -2689,7 +2689,7 @@
         <v>2.80800008773804</v>
       </c>
       <c r="G80" t="n">
-        <v>2.52847528457642</v>
+        <v>2.528475522995</v>
       </c>
       <c r="H80" t="n">
         <v>109058</v>
@@ -2718,7 +2718,7 @@
         <v>2.80200004577637</v>
       </c>
       <c r="G81" t="n">
-        <v>2.5230724811554</v>
+        <v>2.52307271957397</v>
       </c>
       <c r="H81" t="n">
         <v>98753</v>
@@ -2747,7 +2747,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G82" t="n">
-        <v>2.49425792694092</v>
+        <v>2.4942581653595</v>
       </c>
       <c r="H82" t="n">
         <v>89415</v>
@@ -2805,7 +2805,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G84" t="n">
-        <v>2.48525357246399</v>
+        <v>2.48525381088257</v>
       </c>
       <c r="H84" t="n">
         <v>88572</v>
@@ -2863,7 +2863,7 @@
         <v>2.76399993896484</v>
       </c>
       <c r="G86" t="n">
-        <v>2.4888551235199</v>
+        <v>2.48885536193848</v>
       </c>
       <c r="H86" t="n">
         <v>72690</v>
@@ -2921,7 +2921,7 @@
         <v>2.74600005149841</v>
       </c>
       <c r="G88" t="n">
-        <v>2.47264719009399</v>
+        <v>2.47264742851257</v>
       </c>
       <c r="H88" t="n">
         <v>107336</v>
@@ -2950,7 +2950,7 @@
         <v>2.74399995803833</v>
       </c>
       <c r="G89" t="n">
-        <v>2.47084641456604</v>
+        <v>2.47084617614746</v>
       </c>
       <c r="H89" t="n">
         <v>196450</v>
@@ -2979,7 +2979,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G90" t="n">
-        <v>2.46724438667297</v>
+        <v>2.46724462509155</v>
       </c>
       <c r="H90" t="n">
         <v>158160</v>
@@ -3095,7 +3095,7 @@
         <v>2.84599995613098</v>
       </c>
       <c r="G94" t="n">
-        <v>2.56269240379333</v>
+        <v>2.56269264221191</v>
       </c>
       <c r="H94" t="n">
         <v>207064</v>
@@ -3240,7 +3240,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G99" t="n">
-        <v>2.54828548431396</v>
+        <v>2.54828524589539</v>
       </c>
       <c r="H99" t="n">
         <v>101935</v>
@@ -3269,7 +3269,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G100" t="n">
-        <v>2.62032175064087</v>
+        <v>2.62032198905945</v>
       </c>
       <c r="H100" t="n">
         <v>107418</v>
@@ -3356,7 +3356,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G103" t="n">
-        <v>2.7283763885498</v>
+        <v>2.72837615013123</v>
       </c>
       <c r="H103" t="n">
         <v>552357</v>
@@ -3414,7 +3414,7 @@
         <v>3.04800009727478</v>
       </c>
       <c r="G105" t="n">
-        <v>2.74458432197571</v>
+        <v>2.74458456039429</v>
       </c>
       <c r="H105" t="n">
         <v>558900</v>
@@ -3501,7 +3501,7 @@
         <v>2.90400004386902</v>
       </c>
       <c r="G108" t="n">
-        <v>2.61491894721985</v>
+        <v>2.61491918563843</v>
       </c>
       <c r="H108" t="n">
         <v>295869</v>
@@ -3559,7 +3559,7 @@
         <v>2.9760000705719</v>
       </c>
       <c r="G110" t="n">
-        <v>2.67975187301636</v>
+        <v>2.67975163459778</v>
       </c>
       <c r="H110" t="n">
         <v>343647</v>
@@ -3646,7 +3646,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G113" t="n">
-        <v>2.62032175064087</v>
+        <v>2.62032198905945</v>
       </c>
       <c r="H113" t="n">
         <v>3703132</v>
@@ -3733,7 +3733,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G116" t="n">
-        <v>2.6563401222229</v>
+        <v>2.65633988380432</v>
       </c>
       <c r="H116" t="n">
         <v>209509</v>
@@ -3762,7 +3762,7 @@
         <v>2.98600006103516</v>
       </c>
       <c r="G117" t="n">
-        <v>2.68875646591187</v>
+        <v>2.68875622749329</v>
       </c>
       <c r="H117" t="n">
         <v>230218</v>
@@ -3791,7 +3791,7 @@
         <v>2.98799991607666</v>
       </c>
       <c r="G118" t="n">
-        <v>2.69055724143982</v>
+        <v>2.69055700302124</v>
       </c>
       <c r="H118" t="n">
         <v>164670</v>
@@ -3820,7 +3820,7 @@
         <v>2.9760000705719</v>
       </c>
       <c r="G119" t="n">
-        <v>2.67975187301636</v>
+        <v>2.67975163459778</v>
       </c>
       <c r="H119" t="n">
         <v>138195</v>
@@ -3878,7 +3878,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G121" t="n">
-        <v>2.68335366249084</v>
+        <v>2.68335342407227</v>
       </c>
       <c r="H121" t="n">
         <v>230872</v>
@@ -3907,7 +3907,7 @@
         <v>3.00200009346008</v>
       </c>
       <c r="G122" t="n">
-        <v>2.70316338539124</v>
+        <v>2.70316362380981</v>
       </c>
       <c r="H122" t="n">
         <v>492519</v>
@@ -3965,7 +3965,7 @@
         <v>2.96600008010864</v>
       </c>
       <c r="G124" t="n">
-        <v>2.67074704170227</v>
+        <v>2.67074728012085</v>
       </c>
       <c r="H124" t="n">
         <v>538453</v>
@@ -3994,7 +3994,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G125" t="n">
-        <v>2.6563401222229</v>
+        <v>2.65633988380432</v>
       </c>
       <c r="H125" t="n">
         <v>301292</v>
@@ -4023,7 +4023,7 @@
         <v>2.99200010299683</v>
       </c>
       <c r="G126" t="n">
-        <v>2.69415903091431</v>
+        <v>2.69415926933289</v>
       </c>
       <c r="H126" t="n">
         <v>265025</v>
@@ -4052,7 +4052,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G127" t="n">
-        <v>2.7193717956543</v>
+        <v>2.71937155723572</v>
       </c>
       <c r="H127" t="n">
         <v>472950</v>
@@ -4081,7 +4081,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G128" t="n">
-        <v>2.68335366249084</v>
+        <v>2.68335342407227</v>
       </c>
       <c r="H128" t="n">
         <v>601683</v>
@@ -4139,7 +4139,7 @@
         <v>2.92799997329712</v>
       </c>
       <c r="G130" t="n">
-        <v>2.63652968406677</v>
+        <v>2.63652992248535</v>
       </c>
       <c r="H130" t="n">
         <v>329492</v>
@@ -4168,7 +4168,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G131" t="n">
-        <v>2.62032175064087</v>
+        <v>2.62032198905945</v>
       </c>
       <c r="H131" t="n">
         <v>395059</v>
@@ -4255,7 +4255,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G134" t="n">
-        <v>2.54828548431396</v>
+        <v>2.54828524589539</v>
       </c>
       <c r="H134" t="n">
         <v>228306</v>
@@ -4371,7 +4371,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G138" t="n">
-        <v>2.55728960037231</v>
+        <v>2.55728983879089</v>
       </c>
       <c r="H138" t="n">
         <v>102337</v>
@@ -4400,7 +4400,7 @@
         <v>2.83200001716614</v>
       </c>
       <c r="G139" t="n">
-        <v>2.5500864982605</v>
+        <v>2.55008625984192</v>
       </c>
       <c r="H139" t="n">
         <v>63393</v>
@@ -4487,7 +4487,7 @@
         <v>2.8659999370575</v>
       </c>
       <c r="G142" t="n">
-        <v>2.58070158958435</v>
+        <v>2.58070182800293</v>
       </c>
       <c r="H142" t="n">
         <v>182319</v>
@@ -4603,7 +4603,7 @@
         <v>2.84599995613098</v>
       </c>
       <c r="G146" t="n">
-        <v>2.56269240379333</v>
+        <v>2.56269264221191</v>
       </c>
       <c r="H146" t="n">
         <v>95512</v>
@@ -4632,7 +4632,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G147" t="n">
-        <v>2.58430361747742</v>
+        <v>2.58430337905884</v>
       </c>
       <c r="H147" t="n">
         <v>289366</v>
@@ -4661,7 +4661,7 @@
         <v>2.86800003051758</v>
       </c>
       <c r="G148" t="n">
-        <v>2.58250284194946</v>
+        <v>2.58250260353088</v>
       </c>
       <c r="H148" t="n">
         <v>580188</v>
@@ -4719,7 +4719,7 @@
         <v>2.90799999237061</v>
       </c>
       <c r="G150" t="n">
-        <v>2.61852073669434</v>
+        <v>2.61852097511292</v>
       </c>
       <c r="H150" t="n">
         <v>261501</v>
@@ -4748,7 +4748,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G151" t="n">
-        <v>2.63833093643188</v>
+        <v>2.63833069801331</v>
       </c>
       <c r="H151" t="n">
         <v>366145</v>
@@ -4777,7 +4777,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G152" t="n">
-        <v>2.6563401222229</v>
+        <v>2.65633988380432</v>
       </c>
       <c r="H152" t="n">
         <v>326136</v>
@@ -4864,7 +4864,7 @@
         <v>2.92600011825562</v>
       </c>
       <c r="G155" t="n">
-        <v>2.6347291469574</v>
+        <v>2.63472890853882</v>
       </c>
       <c r="H155" t="n">
         <v>146915</v>
@@ -4922,7 +4922,7 @@
         <v>2.81599998474121</v>
       </c>
       <c r="G157" t="n">
-        <v>2.53567886352539</v>
+        <v>2.53567910194397</v>
       </c>
       <c r="H157" t="n">
         <v>258393</v>
@@ -5009,7 +5009,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G160" t="n">
-        <v>2.73738050460815</v>
+        <v>2.73738074302673</v>
       </c>
       <c r="H160" t="n">
         <v>1245433</v>
@@ -5067,7 +5067,7 @@
         <v>3.11199998855591</v>
       </c>
       <c r="G162" t="n">
-        <v>2.80221343040466</v>
+        <v>2.80221366882324</v>
       </c>
       <c r="H162" t="n">
         <v>1090032</v>
@@ -5096,7 +5096,7 @@
         <v>3.07800006866455</v>
       </c>
       <c r="G163" t="n">
-        <v>2.77159786224365</v>
+        <v>2.77159810066223</v>
       </c>
       <c r="H163" t="n">
         <v>301973</v>
@@ -5183,7 +5183,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G166" t="n">
-        <v>2.87244915962219</v>
+        <v>2.87244892120361</v>
       </c>
       <c r="H166" t="n">
         <v>973243</v>
@@ -5241,7 +5241,7 @@
         <v>3.2260000705719</v>
       </c>
       <c r="G168" t="n">
-        <v>2.90486550331116</v>
+        <v>2.90486526489258</v>
       </c>
       <c r="H168" t="n">
         <v>1684867</v>
@@ -5299,7 +5299,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G170" t="n">
-        <v>2.98950791358948</v>
+        <v>2.9895076751709</v>
       </c>
       <c r="H170" t="n">
         <v>877610</v>
@@ -5444,7 +5444,7 @@
         <v>3.50600004196167</v>
       </c>
       <c r="G175" t="n">
-        <v>3.15699219703674</v>
+        <v>3.15699243545532</v>
       </c>
       <c r="H175" t="n">
         <v>1959547</v>
@@ -5502,7 +5502,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G177" t="n">
-        <v>3.06154417991638</v>
+        <v>3.06154441833496</v>
       </c>
       <c r="H177" t="n">
         <v>1430963</v>
@@ -5531,7 +5531,7 @@
         <v>3.31800007820129</v>
       </c>
       <c r="G178" t="n">
-        <v>2.98770689964294</v>
+        <v>2.98770713806152</v>
       </c>
       <c r="H178" t="n">
         <v>742754</v>
@@ -5618,7 +5618,7 @@
         <v>3.13199996948242</v>
       </c>
       <c r="G181" t="n">
-        <v>2.82022261619568</v>
+        <v>2.8202223777771</v>
       </c>
       <c r="H181" t="n">
         <v>951170</v>
@@ -5676,7 +5676,7 @@
         <v>3.13199996948242</v>
       </c>
       <c r="G183" t="n">
-        <v>2.82022261619568</v>
+        <v>2.8202223777771</v>
       </c>
       <c r="H183" t="n">
         <v>1171358</v>
@@ -5734,7 +5734,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G185" t="n">
-        <v>2.89045786857605</v>
+        <v>2.89045810699463</v>
       </c>
       <c r="H185" t="n">
         <v>709125</v>
@@ -5792,7 +5792,7 @@
         <v>3.13199996948242</v>
       </c>
       <c r="G187" t="n">
-        <v>2.82022261619568</v>
+        <v>2.8202223777771</v>
       </c>
       <c r="H187" t="n">
         <v>486844</v>
@@ -5908,7 +5908,7 @@
         <v>3.18199992179871</v>
       </c>
       <c r="G191" t="n">
-        <v>2.86524534225464</v>
+        <v>2.86524510383606</v>
       </c>
       <c r="H191" t="n">
         <v>278666</v>
@@ -5937,7 +5937,7 @@
         <v>3.16799998283386</v>
       </c>
       <c r="G192" t="n">
-        <v>2.85263895988464</v>
+        <v>2.85263872146606</v>
       </c>
       <c r="H192" t="n">
         <v>381457</v>
@@ -6024,7 +6024,7 @@
         <v>3.16400003433228</v>
       </c>
       <c r="G195" t="n">
-        <v>2.84903717041016</v>
+        <v>2.84903693199158</v>
       </c>
       <c r="H195" t="n">
         <v>562311</v>
@@ -6053,7 +6053,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G196" t="n">
-        <v>2.80491495132446</v>
+        <v>2.80491471290588</v>
       </c>
       <c r="H196" t="n">
         <v>835838</v>
@@ -6082,7 +6082,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G197" t="n">
-        <v>2.84993767738342</v>
+        <v>2.84993743896484</v>
       </c>
       <c r="H197" t="n">
         <v>267637</v>
@@ -6169,7 +6169,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G200" t="n">
-        <v>2.79591012001038</v>
+        <v>2.79591035842896</v>
       </c>
       <c r="H200" t="n">
         <v>277567</v>
@@ -6227,7 +6227,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G202" t="n">
-        <v>2.77339887619019</v>
+        <v>2.77339863777161</v>
       </c>
       <c r="H202" t="n">
         <v>272137</v>
@@ -6256,7 +6256,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G203" t="n">
-        <v>2.76439452171326</v>
+        <v>2.7643940448761</v>
       </c>
       <c r="H203" t="n">
         <v>271367</v>
@@ -6314,7 +6314,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G205" t="n">
-        <v>2.67434906959534</v>
+        <v>2.67434883117676</v>
       </c>
       <c r="H205" t="n">
         <v>598555</v>
@@ -6372,7 +6372,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G207" t="n">
-        <v>2.63833093643188</v>
+        <v>2.63833069801331</v>
       </c>
       <c r="H207" t="n">
         <v>256503</v>
@@ -6401,7 +6401,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G208" t="n">
-        <v>2.66534423828125</v>
+        <v>2.66534447669983</v>
       </c>
       <c r="H208" t="n">
         <v>290531</v>
@@ -6430,7 +6430,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G209" t="n">
-        <v>2.63833093643188</v>
+        <v>2.63833069801331</v>
       </c>
       <c r="H209" t="n">
         <v>276036</v>
@@ -6488,7 +6488,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G211" t="n">
-        <v>2.57529878616333</v>
+        <v>2.57529902458191</v>
       </c>
       <c r="H211" t="n">
         <v>2239887</v>
@@ -6517,7 +6517,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G212" t="n">
-        <v>2.54828548431396</v>
+        <v>2.54828524589539</v>
       </c>
       <c r="H212" t="n">
         <v>548010</v>
@@ -6575,7 +6575,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G214" t="n">
-        <v>2.55728960037231</v>
+        <v>2.55728983879089</v>
       </c>
       <c r="H214" t="n">
         <v>507186</v>
@@ -6604,7 +6604,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G215" t="n">
-        <v>2.57529878616333</v>
+        <v>2.57529902458191</v>
       </c>
       <c r="H215" t="n">
         <v>1072643</v>
@@ -6633,7 +6633,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G216" t="n">
-        <v>2.58430361747742</v>
+        <v>2.58430337905884</v>
       </c>
       <c r="H216" t="n">
         <v>404218</v>
@@ -6662,7 +6662,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G217" t="n">
-        <v>2.54828548431396</v>
+        <v>2.54828524589539</v>
       </c>
       <c r="H217" t="n">
         <v>601149</v>
@@ -6691,7 +6691,7 @@
         <v>2.875</v>
       </c>
       <c r="G218" t="n">
-        <v>2.58880591392517</v>
+        <v>2.58880567550659</v>
       </c>
       <c r="H218" t="n">
         <v>460755</v>
@@ -6749,7 +6749,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G220" t="n">
-        <v>2.66534423828125</v>
+        <v>2.66534447669983</v>
       </c>
       <c r="H220" t="n">
         <v>807427</v>
@@ -6778,7 +6778,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G221" t="n">
-        <v>2.68785548210144</v>
+        <v>2.68785572052002</v>
       </c>
       <c r="H221" t="n">
         <v>693872</v>
@@ -6836,7 +6836,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G223" t="n">
-        <v>2.68785548210144</v>
+        <v>2.68785572052002</v>
       </c>
       <c r="H223" t="n">
         <v>289774</v>
@@ -6865,7 +6865,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G224" t="n">
-        <v>2.71486926078796</v>
+        <v>2.71486949920654</v>
       </c>
       <c r="H224" t="n">
         <v>302122</v>
@@ -6894,7 +6894,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G225" t="n">
-        <v>2.73287844657898</v>
+        <v>2.73287868499756</v>
       </c>
       <c r="H225" t="n">
         <v>325591</v>
@@ -7010,7 +7010,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G229" t="n">
-        <v>2.80491495132446</v>
+        <v>2.80491471290588</v>
       </c>
       <c r="H229" t="n">
         <v>265295</v>
@@ -7126,7 +7126,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G233" t="n">
-        <v>2.76439452171326</v>
+        <v>2.7643940448761</v>
       </c>
       <c r="H233" t="n">
         <v>219195</v>
@@ -7329,7 +7329,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G240" t="n">
-        <v>2.71036696434021</v>
+        <v>2.71036720275879</v>
       </c>
       <c r="H240" t="n">
         <v>268134</v>
@@ -7358,7 +7358,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G241" t="n">
-        <v>2.73287844657898</v>
+        <v>2.73287868499756</v>
       </c>
       <c r="H241" t="n">
         <v>156956</v>
@@ -7445,7 +7445,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G244" t="n">
-        <v>2.80041241645813</v>
+        <v>2.80041265487671</v>
       </c>
       <c r="H244" t="n">
         <v>672793</v>
@@ -7474,7 +7474,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G245" t="n">
-        <v>2.77339887619019</v>
+        <v>2.77339863777161</v>
       </c>
       <c r="H245" t="n">
         <v>803152</v>
@@ -7532,7 +7532,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G247" t="n">
-        <v>2.7193717956543</v>
+        <v>2.71937155723572</v>
       </c>
       <c r="H247" t="n">
         <v>326171</v>
@@ -7590,7 +7590,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G249" t="n">
-        <v>2.669846534729</v>
+        <v>2.66984677314758</v>
       </c>
       <c r="H249" t="n">
         <v>254041</v>
@@ -7619,7 +7619,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G250" t="n">
-        <v>2.6563401222229</v>
+        <v>2.65633988380432</v>
       </c>
       <c r="H250" t="n">
         <v>375208</v>
@@ -7648,7 +7648,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G251" t="n">
-        <v>2.66534423828125</v>
+        <v>2.66534447669983</v>
       </c>
       <c r="H251" t="n">
         <v>193370</v>
@@ -7677,7 +7677,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G252" t="n">
-        <v>2.6563401222229</v>
+        <v>2.65633988380432</v>
       </c>
       <c r="H252" t="n">
         <v>198249</v>
@@ -7706,7 +7706,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G253" t="n">
-        <v>2.68785548210144</v>
+        <v>2.68785572052002</v>
       </c>
       <c r="H253" t="n">
         <v>521926</v>
@@ -7793,7 +7793,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G256" t="n">
-        <v>2.63852858543396</v>
+        <v>2.63852882385254</v>
       </c>
       <c r="H256" t="n">
         <v>424764</v>
@@ -7822,7 +7822,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G257" t="n">
-        <v>2.63387537002563</v>
+        <v>2.63387513160706</v>
       </c>
       <c r="H257" t="n">
         <v>331330</v>
@@ -8025,7 +8025,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G264" t="n">
-        <v>2.63387537002563</v>
+        <v>2.63387513160706</v>
       </c>
       <c r="H264" t="n">
         <v>380253</v>
@@ -8054,7 +8054,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G265" t="n">
-        <v>2.61991477012634</v>
+        <v>2.61991500854492</v>
       </c>
       <c r="H265" t="n">
         <v>268393</v>
@@ -8083,7 +8083,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G266" t="n">
-        <v>2.61991477012634</v>
+        <v>2.61991500854492</v>
       </c>
       <c r="H266" t="n">
         <v>334646</v>
@@ -8170,7 +8170,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G269" t="n">
-        <v>2.62456822395325</v>
+        <v>2.62456798553467</v>
       </c>
       <c r="H269" t="n">
         <v>267385</v>
@@ -8199,7 +8199,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G270" t="n">
-        <v>2.62456822395325</v>
+        <v>2.62456798553467</v>
       </c>
       <c r="H270" t="n">
         <v>255476</v>
@@ -8344,7 +8344,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G275" t="n">
-        <v>2.62456822395325</v>
+        <v>2.62456798553467</v>
       </c>
       <c r="H275" t="n">
         <v>175603</v>
@@ -8373,7 +8373,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G276" t="n">
-        <v>2.61991477012634</v>
+        <v>2.61991500854492</v>
       </c>
       <c r="H276" t="n">
         <v>180030</v>
@@ -8634,7 +8634,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G285" t="n">
-        <v>2.49427056312561</v>
+        <v>2.49427080154419</v>
       </c>
       <c r="H285" t="n">
         <v>387349</v>
@@ -8692,7 +8692,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G287" t="n">
-        <v>2.52684473991394</v>
+        <v>2.52684497833252</v>
       </c>
       <c r="H287" t="n">
         <v>123001</v>
@@ -8721,7 +8721,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G288" t="n">
-        <v>2.54545903205872</v>
+        <v>2.54545879364014</v>
       </c>
       <c r="H288" t="n">
         <v>248118</v>
@@ -8750,7 +8750,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G289" t="n">
-        <v>2.54080557823181</v>
+        <v>2.54080533981323</v>
       </c>
       <c r="H289" t="n">
         <v>290279</v>
@@ -8779,7 +8779,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G290" t="n">
-        <v>2.53149843215942</v>
+        <v>2.531498670578</v>
       </c>
       <c r="H290" t="n">
         <v>177641</v>
@@ -8924,7 +8924,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G295" t="n">
-        <v>2.61991477012634</v>
+        <v>2.61991500854492</v>
       </c>
       <c r="H295" t="n">
         <v>403095</v>
@@ -8953,7 +8953,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G296" t="n">
-        <v>2.61991477012634</v>
+        <v>2.61991500854492</v>
       </c>
       <c r="H296" t="n">
         <v>436118</v>
@@ -9069,7 +9069,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G300" t="n">
-        <v>2.61991477012634</v>
+        <v>2.61991500854492</v>
       </c>
       <c r="H300" t="n">
         <v>249379</v>
@@ -9272,7 +9272,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G307" t="n">
-        <v>2.33605194091797</v>
+        <v>2.33605170249939</v>
       </c>
       <c r="H307" t="n">
         <v>1179759</v>
@@ -9301,7 +9301,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G308" t="n">
-        <v>2.31743812561035</v>
+        <v>2.31743788719177</v>
       </c>
       <c r="H308" t="n">
         <v>642373</v>
@@ -9359,7 +9359,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G310" t="n">
-        <v>2.33605194091797</v>
+        <v>2.33605170249939</v>
       </c>
       <c r="H310" t="n">
         <v>598360</v>
@@ -9388,7 +9388,7 @@
         <v>2.56500005722046</v>
       </c>
       <c r="G311" t="n">
-        <v>2.3872401714325</v>
+        <v>2.38724040985107</v>
       </c>
       <c r="H311" t="n">
         <v>611830</v>
@@ -9446,7 +9446,7 @@
         <v>2.56500005722046</v>
       </c>
       <c r="G313" t="n">
-        <v>2.3872401714325</v>
+        <v>2.38724040985107</v>
       </c>
       <c r="H313" t="n">
         <v>487152</v>
@@ -9591,7 +9591,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G318" t="n">
-        <v>2.42912173271179</v>
+        <v>2.42912149429321</v>
       </c>
       <c r="H318" t="n">
         <v>143426</v>
@@ -9620,7 +9620,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G319" t="n">
-        <v>2.4616961479187</v>
+        <v>2.46169590950012</v>
       </c>
       <c r="H319" t="n">
         <v>341199</v>
@@ -9765,7 +9765,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G324" t="n">
-        <v>2.63387537002563</v>
+        <v>2.63387513160706</v>
       </c>
       <c r="H324" t="n">
         <v>845890</v>
@@ -9823,7 +9823,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G326" t="n">
-        <v>2.54080557823181</v>
+        <v>2.54080533981323</v>
       </c>
       <c r="H326" t="n">
         <v>1995862</v>
@@ -9968,7 +9968,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G331" t="n">
-        <v>2.52684473991394</v>
+        <v>2.52684497833252</v>
       </c>
       <c r="H331" t="n">
         <v>174270</v>
@@ -10258,7 +10258,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G341" t="n">
-        <v>2.63852858543396</v>
+        <v>2.63852882385254</v>
       </c>
       <c r="H341" t="n">
         <v>386548</v>
@@ -10287,7 +10287,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G342" t="n">
-        <v>2.63387537002563</v>
+        <v>2.63387513160706</v>
       </c>
       <c r="H342" t="n">
         <v>325109</v>
@@ -10432,7 +10432,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G347" t="n">
-        <v>2.49427056312561</v>
+        <v>2.49427080154419</v>
       </c>
       <c r="H347" t="n">
         <v>240234</v>
@@ -10548,7 +10548,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G351" t="n">
-        <v>2.71763825416565</v>
+        <v>2.71763801574707</v>
       </c>
       <c r="H351" t="n">
         <v>1174324</v>
@@ -10606,7 +10606,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G353" t="n">
-        <v>2.63387537002563</v>
+        <v>2.63387513160706</v>
       </c>
       <c r="H353" t="n">
         <v>1343987</v>
@@ -10722,7 +10722,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G357" t="n">
-        <v>2.61991477012634</v>
+        <v>2.61991500854492</v>
       </c>
       <c r="H357" t="n">
         <v>528618</v>
@@ -10780,7 +10780,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G359" t="n">
-        <v>2.53149843215942</v>
+        <v>2.531498670578</v>
       </c>
       <c r="H359" t="n">
         <v>283153</v>
@@ -10809,7 +10809,7 @@
         <v>2.70499992370605</v>
       </c>
       <c r="G360" t="n">
-        <v>2.51753807067871</v>
+        <v>2.51753783226013</v>
       </c>
       <c r="H360" t="n">
         <v>224865</v>
@@ -10925,7 +10925,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G364" t="n">
-        <v>2.63852858543396</v>
+        <v>2.63852882385254</v>
       </c>
       <c r="H364" t="n">
         <v>1117900</v>
@@ -11186,7 +11186,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G373" t="n">
-        <v>2.61991477012634</v>
+        <v>2.61991500854492</v>
       </c>
       <c r="H373" t="n">
         <v>332593</v>
@@ -11273,7 +11273,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G376" t="n">
-        <v>2.68041038513184</v>
+        <v>2.68041014671326</v>
       </c>
       <c r="H376" t="n">
         <v>1005481</v>
@@ -11505,7 +11505,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G384" t="n">
-        <v>2.62456822395325</v>
+        <v>2.62456798553467</v>
       </c>
       <c r="H384" t="n">
         <v>261528</v>
@@ -11534,7 +11534,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G385" t="n">
-        <v>2.61991477012634</v>
+        <v>2.61991500854492</v>
       </c>
       <c r="H385" t="n">
         <v>258305</v>
@@ -11563,7 +11563,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G386" t="n">
-        <v>2.62922191619873</v>
+        <v>2.62922167778015</v>
       </c>
       <c r="H386" t="n">
         <v>122247</v>
@@ -11621,7 +11621,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G388" t="n">
-        <v>2.63852858543396</v>
+        <v>2.63852882385254</v>
       </c>
       <c r="H388" t="n">
         <v>243336</v>
@@ -11882,7 +11882,7 @@
         <v>2.89499998092651</v>
       </c>
       <c r="G397" t="n">
-        <v>2.69437050819397</v>
+        <v>2.69437074661255</v>
       </c>
       <c r="H397" t="n">
         <v>247508</v>
@@ -11940,7 +11940,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G399" t="n">
-        <v>2.71763825416565</v>
+        <v>2.71763801574707</v>
       </c>
       <c r="H399" t="n">
         <v>314529</v>
@@ -12143,7 +12143,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G406" t="n">
-        <v>2.78278684616089</v>
+        <v>2.78278708457947</v>
       </c>
       <c r="H406" t="n">
         <v>858592</v>
@@ -12201,7 +12201,7 @@
         <v>2.93499994277954</v>
       </c>
       <c r="G408" t="n">
-        <v>2.73159837722778</v>
+        <v>2.73159861564636</v>
       </c>
       <c r="H408" t="n">
         <v>366747</v>
@@ -12433,7 +12433,7 @@
         <v>2.93499994277954</v>
       </c>
       <c r="G416" t="n">
-        <v>2.73159837722778</v>
+        <v>2.73159861564636</v>
       </c>
       <c r="H416" t="n">
         <v>420901</v>
@@ -12636,7 +12636,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G423" t="n">
-        <v>2.63387537002563</v>
+        <v>2.63387513160706</v>
       </c>
       <c r="H423" t="n">
         <v>266696</v>
@@ -12694,7 +12694,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G425" t="n">
-        <v>2.71763825416565</v>
+        <v>2.71763801574707</v>
       </c>
       <c r="H425" t="n">
         <v>1259534</v>
@@ -12781,7 +12781,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G428" t="n">
-        <v>2.63852858543396</v>
+        <v>2.63852882385254</v>
       </c>
       <c r="H428" t="n">
         <v>1712952</v>
@@ -12926,7 +12926,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G433" t="n">
-        <v>2.54080557823181</v>
+        <v>2.54080533981323</v>
       </c>
       <c r="H433" t="n">
         <v>554263</v>
@@ -12955,7 +12955,7 @@
         <v>2.70499992370605</v>
       </c>
       <c r="G434" t="n">
-        <v>2.51753807067871</v>
+        <v>2.51753783226013</v>
       </c>
       <c r="H434" t="n">
         <v>1145037</v>
@@ -13013,7 +13013,7 @@
         <v>2.70499992370605</v>
       </c>
       <c r="G436" t="n">
-        <v>2.51753807067871</v>
+        <v>2.51753783226013</v>
       </c>
       <c r="H436" t="n">
         <v>385823</v>
@@ -13042,7 +13042,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G437" t="n">
-        <v>2.54545903205872</v>
+        <v>2.54545879364014</v>
       </c>
       <c r="H437" t="n">
         <v>263202</v>
@@ -13129,7 +13129,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G440" t="n">
-        <v>2.54080557823181</v>
+        <v>2.54080533981323</v>
       </c>
       <c r="H440" t="n">
         <v>201087</v>
@@ -13274,7 +13274,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G445" t="n">
-        <v>2.42912173271179</v>
+        <v>2.42912149429321</v>
       </c>
       <c r="H445" t="n">
         <v>381239</v>
@@ -13303,7 +13303,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G446" t="n">
-        <v>2.43842840194702</v>
+        <v>2.4384286403656</v>
       </c>
       <c r="H446" t="n">
         <v>430895</v>
@@ -13680,7 +13680,7 @@
         <v>2.5</v>
       </c>
       <c r="G459" t="n">
-        <v>2.32674479484558</v>
+        <v>2.32674503326416</v>
       </c>
       <c r="H459" t="n">
         <v>273470</v>
@@ -13738,7 +13738,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G461" t="n">
-        <v>2.3323290348053</v>
+        <v>2.33232927322388</v>
       </c>
       <c r="H461" t="n">
         <v>159605</v>
@@ -13767,7 +13767,7 @@
         <v>2.4539999961853</v>
       </c>
       <c r="G462" t="n">
-        <v>2.28393292427063</v>
+        <v>2.28393268585205</v>
       </c>
       <c r="H462" t="n">
         <v>213603</v>
@@ -13825,7 +13825,7 @@
         <v>2.59200000762939</v>
       </c>
       <c r="G464" t="n">
-        <v>2.41236925125122</v>
+        <v>2.41236901283264</v>
       </c>
       <c r="H464" t="n">
         <v>118274</v>
@@ -13999,7 +13999,7 @@
         <v>2.61400008201599</v>
       </c>
       <c r="G470" t="n">
-        <v>2.43284440040588</v>
+        <v>2.43284463882446</v>
       </c>
       <c r="H470" t="n">
         <v>181112</v>
@@ -14057,7 +14057,7 @@
         <v>2.58599996566772</v>
       </c>
       <c r="G472" t="n">
-        <v>2.4067850112915</v>
+        <v>2.40678477287292</v>
       </c>
       <c r="H472" t="n">
         <v>342752</v>
@@ -14347,7 +14347,7 @@
         <v>2.72399997711182</v>
       </c>
       <c r="G482" t="n">
-        <v>2.53522133827209</v>
+        <v>2.53522109985352</v>
       </c>
       <c r="H482" t="n">
         <v>409776</v>
@@ -14492,7 +14492,7 @@
         <v>2.81200003623962</v>
       </c>
       <c r="G487" t="n">
-        <v>2.61712288856506</v>
+        <v>2.61712265014648</v>
       </c>
       <c r="H487" t="n">
         <v>549599</v>
@@ -24880,6 +24880,35 @@
         <v>104369</v>
       </c>
       <c r="I845" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="s">
+        <v>9</v>
+      </c>
+      <c r="B846" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C846" t="n">
+        <v>2.64199995994568</v>
+      </c>
+      <c r="D846" t="n">
+        <v>2.68799996376038</v>
+      </c>
+      <c r="E846" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="F846" t="n">
+        <v>2.65599989891052</v>
+      </c>
+      <c r="G846" t="n">
+        <v>2.65599989891052</v>
+      </c>
+      <c r="H846" t="n">
+        <v>116759</v>
+      </c>
+      <c r="I846" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/YACHT.MI.xlsx
+++ b/data/YACHT.MI.xlsx
@@ -427,7 +427,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G2" t="n">
-        <v>2.68335342407227</v>
+        <v>2.68335366249084</v>
       </c>
       <c r="H2" t="n">
         <v>9271589</v>
@@ -456,7 +456,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6293261051178</v>
+        <v>2.62932634353638</v>
       </c>
       <c r="H3" t="n">
         <v>5523202</v>
@@ -485,7 +485,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G4" t="n">
-        <v>2.57529902458191</v>
+        <v>2.57529878616333</v>
       </c>
       <c r="H4" t="n">
         <v>2742684</v>
@@ -572,7 +572,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G7" t="n">
-        <v>2.62032198905945</v>
+        <v>2.62032175064087</v>
       </c>
       <c r="H7" t="n">
         <v>462954</v>
@@ -601,7 +601,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G8" t="n">
-        <v>2.6293261051178</v>
+        <v>2.62932634353638</v>
       </c>
       <c r="H8" t="n">
         <v>470527</v>
@@ -630,7 +630,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G9" t="n">
-        <v>2.60231280326843</v>
+        <v>2.60231256484985</v>
       </c>
       <c r="H9" t="n">
         <v>370604</v>
@@ -659,7 +659,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G10" t="n">
-        <v>2.6293261051178</v>
+        <v>2.62932634353638</v>
       </c>
       <c r="H10" t="n">
         <v>167157</v>
@@ -688,7 +688,7 @@
         <v>2.88199996948242</v>
       </c>
       <c r="G11" t="n">
-        <v>2.5951087474823</v>
+        <v>2.59510898590088</v>
       </c>
       <c r="H11" t="n">
         <v>527158</v>
@@ -746,7 +746,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G13" t="n">
-        <v>2.60231280326843</v>
+        <v>2.60231256484985</v>
       </c>
       <c r="H13" t="n">
         <v>258873</v>
@@ -833,7 +833,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G16" t="n">
-        <v>2.6293261051178</v>
+        <v>2.62932634353638</v>
       </c>
       <c r="H16" t="n">
         <v>234246</v>
@@ -862,7 +862,7 @@
         <v>2.99799990653992</v>
       </c>
       <c r="G17" t="n">
-        <v>2.69956159591675</v>
+        <v>2.69956135749817</v>
       </c>
       <c r="H17" t="n">
         <v>721392</v>
@@ -891,7 +891,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G18" t="n">
-        <v>2.84543561935425</v>
+        <v>2.84543514251709</v>
       </c>
       <c r="H18" t="n">
         <v>1195492</v>
@@ -920,7 +920,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G19" t="n">
-        <v>2.81842184066772</v>
+        <v>2.81842160224915</v>
       </c>
       <c r="H19" t="n">
         <v>1196581</v>
@@ -1152,7 +1152,7 @@
         <v>3.2039999961853</v>
       </c>
       <c r="G27" t="n">
-        <v>2.88505530357361</v>
+        <v>2.88505506515503</v>
       </c>
       <c r="H27" t="n">
         <v>920776</v>
@@ -1210,7 +1210,7 @@
         <v>3.12199997901917</v>
       </c>
       <c r="G29" t="n">
-        <v>2.81121802330017</v>
+        <v>2.81121778488159</v>
       </c>
       <c r="H29" t="n">
         <v>544144</v>
@@ -1239,7 +1239,7 @@
         <v>3.17799997329712</v>
       </c>
       <c r="G30" t="n">
-        <v>2.86164331436157</v>
+        <v>2.86164355278015</v>
       </c>
       <c r="H30" t="n">
         <v>594226</v>
@@ -1326,7 +1326,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G33" t="n">
-        <v>2.72837615013123</v>
+        <v>2.7283763885498</v>
       </c>
       <c r="H33" t="n">
         <v>552267</v>
@@ -1413,7 +1413,7 @@
         <v>2.96199989318848</v>
       </c>
       <c r="G36" t="n">
-        <v>2.66714549064636</v>
+        <v>2.66714525222778</v>
       </c>
       <c r="H36" t="n">
         <v>99000</v>
@@ -1442,7 +1442,7 @@
         <v>2.96199989318848</v>
       </c>
       <c r="G37" t="n">
-        <v>2.66714549064636</v>
+        <v>2.66714525222778</v>
       </c>
       <c r="H37" t="n">
         <v>318498</v>
@@ -1471,7 +1471,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G38" t="n">
-        <v>2.6293261051178</v>
+        <v>2.62932634353638</v>
       </c>
       <c r="H38" t="n">
         <v>113466</v>
@@ -1500,7 +1500,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G39" t="n">
-        <v>2.65633988380432</v>
+        <v>2.6563401222229</v>
       </c>
       <c r="H39" t="n">
         <v>413206</v>
@@ -1529,7 +1529,7 @@
         <v>2.93400001525879</v>
       </c>
       <c r="G40" t="n">
-        <v>2.64193272590637</v>
+        <v>2.64193248748779</v>
       </c>
       <c r="H40" t="n">
         <v>560977</v>
@@ -1616,7 +1616,7 @@
         <v>2.90599989891052</v>
       </c>
       <c r="G43" t="n">
-        <v>2.6167197227478</v>
+        <v>2.61671996116638</v>
       </c>
       <c r="H43" t="n">
         <v>160349</v>
@@ -1732,7 +1732,7 @@
         <v>2.91400003433228</v>
       </c>
       <c r="G47" t="n">
-        <v>2.62392377853394</v>
+        <v>2.62392354011536</v>
       </c>
       <c r="H47" t="n">
         <v>681087</v>
@@ -1761,7 +1761,7 @@
         <v>2.90799999237061</v>
       </c>
       <c r="G48" t="n">
-        <v>2.61852097511292</v>
+        <v>2.61852073669434</v>
       </c>
       <c r="H48" t="n">
         <v>395238</v>
@@ -1790,7 +1790,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G49" t="n">
-        <v>2.65633988380432</v>
+        <v>2.6563401222229</v>
       </c>
       <c r="H49" t="n">
         <v>278184</v>
@@ -1819,7 +1819,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G50" t="n">
-        <v>2.63833069801331</v>
+        <v>2.63833093643188</v>
       </c>
       <c r="H50" t="n">
         <v>440815</v>
@@ -1848,7 +1848,7 @@
         <v>2.89199995994568</v>
       </c>
       <c r="G51" t="n">
-        <v>2.60411334037781</v>
+        <v>2.60411357879639</v>
       </c>
       <c r="H51" t="n">
         <v>301022</v>
@@ -1877,7 +1877,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G52" t="n">
-        <v>2.58430337905884</v>
+        <v>2.58430361747742</v>
       </c>
       <c r="H52" t="n">
         <v>406342</v>
@@ -1935,7 +1935,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G54" t="n">
-        <v>2.62032198905945</v>
+        <v>2.62032175064087</v>
       </c>
       <c r="H54" t="n">
         <v>470047</v>
@@ -1993,7 +1993,7 @@
         <v>2.8840000629425</v>
       </c>
       <c r="G56" t="n">
-        <v>2.59690999984741</v>
+        <v>2.59690976142883</v>
       </c>
       <c r="H56" t="n">
         <v>223974</v>
@@ -2080,7 +2080,7 @@
         <v>2.93600010871887</v>
       </c>
       <c r="G59" t="n">
-        <v>2.64373350143433</v>
+        <v>2.64373373985291</v>
       </c>
       <c r="H59" t="n">
         <v>1235755</v>
@@ -2138,7 +2138,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G61" t="n">
-        <v>2.65633988380432</v>
+        <v>2.6563401222229</v>
       </c>
       <c r="H61" t="n">
         <v>481432</v>
@@ -2167,7 +2167,7 @@
         <v>3.0239999294281</v>
       </c>
       <c r="G62" t="n">
-        <v>2.72297334671021</v>
+        <v>2.72297358512878</v>
       </c>
       <c r="H62" t="n">
         <v>610853</v>
@@ -2196,7 +2196,7 @@
         <v>2.99799990653992</v>
       </c>
       <c r="G63" t="n">
-        <v>2.69956159591675</v>
+        <v>2.69956135749817</v>
       </c>
       <c r="H63" t="n">
         <v>323387</v>
@@ -2225,7 +2225,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G64" t="n">
-        <v>2.67434883117676</v>
+        <v>2.67434906959534</v>
       </c>
       <c r="H64" t="n">
         <v>215337</v>
@@ -2312,7 +2312,7 @@
         <v>2.84599995613098</v>
       </c>
       <c r="G67" t="n">
-        <v>2.56269264221191</v>
+        <v>2.56269240379333</v>
       </c>
       <c r="H67" t="n">
         <v>325027</v>
@@ -2341,7 +2341,7 @@
         <v>2.80399990081787</v>
       </c>
       <c r="G68" t="n">
-        <v>2.52487373352051</v>
+        <v>2.52487349510193</v>
       </c>
       <c r="H68" t="n">
         <v>241271</v>
@@ -2428,7 +2428,7 @@
         <v>2.81599998474121</v>
       </c>
       <c r="G71" t="n">
-        <v>2.53567910194397</v>
+        <v>2.53567886352539</v>
       </c>
       <c r="H71" t="n">
         <v>188200</v>
@@ -2457,7 +2457,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G72" t="n">
-        <v>2.4942581653595</v>
+        <v>2.49425792694092</v>
       </c>
       <c r="H72" t="n">
         <v>268719</v>
@@ -2486,7 +2486,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G73" t="n">
-        <v>2.58430337905884</v>
+        <v>2.58430361747742</v>
       </c>
       <c r="H73" t="n">
         <v>296618</v>
@@ -2544,7 +2544,7 @@
         <v>2.81399989128113</v>
       </c>
       <c r="G75" t="n">
-        <v>2.53387832641602</v>
+        <v>2.53387784957886</v>
       </c>
       <c r="H75" t="n">
         <v>173870</v>
@@ -2573,7 +2573,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G76" t="n">
-        <v>2.58430337905884</v>
+        <v>2.58430361747742</v>
       </c>
       <c r="H76" t="n">
         <v>271694</v>
@@ -2602,7 +2602,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G77" t="n">
-        <v>2.58430337905884</v>
+        <v>2.58430361747742</v>
       </c>
       <c r="H77" t="n">
         <v>304675</v>
@@ -2631,7 +2631,7 @@
         <v>2.83599996566772</v>
       </c>
       <c r="G78" t="n">
-        <v>2.55368804931641</v>
+        <v>2.55368828773499</v>
       </c>
       <c r="H78" t="n">
         <v>311069</v>
@@ -2689,7 +2689,7 @@
         <v>2.80800008773804</v>
       </c>
       <c r="G80" t="n">
-        <v>2.528475522995</v>
+        <v>2.52847528457642</v>
       </c>
       <c r="H80" t="n">
         <v>109058</v>
@@ -2718,7 +2718,7 @@
         <v>2.80200004577637</v>
       </c>
       <c r="G81" t="n">
-        <v>2.52307271957397</v>
+        <v>2.5230724811554</v>
       </c>
       <c r="H81" t="n">
         <v>98753</v>
@@ -2747,7 +2747,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G82" t="n">
-        <v>2.4942581653595</v>
+        <v>2.49425792694092</v>
       </c>
       <c r="H82" t="n">
         <v>89415</v>
@@ -2805,7 +2805,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G84" t="n">
-        <v>2.48525381088257</v>
+        <v>2.48525357246399</v>
       </c>
       <c r="H84" t="n">
         <v>88572</v>
@@ -2863,7 +2863,7 @@
         <v>2.76399993896484</v>
       </c>
       <c r="G86" t="n">
-        <v>2.48885536193848</v>
+        <v>2.4888551235199</v>
       </c>
       <c r="H86" t="n">
         <v>72690</v>
@@ -2921,7 +2921,7 @@
         <v>2.74600005149841</v>
       </c>
       <c r="G88" t="n">
-        <v>2.47264742851257</v>
+        <v>2.47264719009399</v>
       </c>
       <c r="H88" t="n">
         <v>107336</v>
@@ -2950,7 +2950,7 @@
         <v>2.74399995803833</v>
       </c>
       <c r="G89" t="n">
-        <v>2.47084617614746</v>
+        <v>2.47084641456604</v>
       </c>
       <c r="H89" t="n">
         <v>196450</v>
@@ -2979,7 +2979,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G90" t="n">
-        <v>2.46724462509155</v>
+        <v>2.46724438667297</v>
       </c>
       <c r="H90" t="n">
         <v>158160</v>
@@ -3095,7 +3095,7 @@
         <v>2.84599995613098</v>
       </c>
       <c r="G94" t="n">
-        <v>2.56269264221191</v>
+        <v>2.56269240379333</v>
       </c>
       <c r="H94" t="n">
         <v>207064</v>
@@ -3240,7 +3240,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G99" t="n">
-        <v>2.54828524589539</v>
+        <v>2.54828548431396</v>
       </c>
       <c r="H99" t="n">
         <v>101935</v>
@@ -3269,7 +3269,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G100" t="n">
-        <v>2.62032198905945</v>
+        <v>2.62032175064087</v>
       </c>
       <c r="H100" t="n">
         <v>107418</v>
@@ -3356,7 +3356,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G103" t="n">
-        <v>2.72837615013123</v>
+        <v>2.7283763885498</v>
       </c>
       <c r="H103" t="n">
         <v>552357</v>
@@ -3414,7 +3414,7 @@
         <v>3.04800009727478</v>
       </c>
       <c r="G105" t="n">
-        <v>2.74458456039429</v>
+        <v>2.74458432197571</v>
       </c>
       <c r="H105" t="n">
         <v>558900</v>
@@ -3501,7 +3501,7 @@
         <v>2.90400004386902</v>
       </c>
       <c r="G108" t="n">
-        <v>2.61491918563843</v>
+        <v>2.61491894721985</v>
       </c>
       <c r="H108" t="n">
         <v>295869</v>
@@ -3559,7 +3559,7 @@
         <v>2.9760000705719</v>
       </c>
       <c r="G110" t="n">
-        <v>2.67975163459778</v>
+        <v>2.67975187301636</v>
       </c>
       <c r="H110" t="n">
         <v>343647</v>
@@ -3646,7 +3646,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G113" t="n">
-        <v>2.62032198905945</v>
+        <v>2.62032175064087</v>
       </c>
       <c r="H113" t="n">
         <v>3703132</v>
@@ -3733,7 +3733,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G116" t="n">
-        <v>2.65633988380432</v>
+        <v>2.6563401222229</v>
       </c>
       <c r="H116" t="n">
         <v>209509</v>
@@ -3762,7 +3762,7 @@
         <v>2.98600006103516</v>
       </c>
       <c r="G117" t="n">
-        <v>2.68875622749329</v>
+        <v>2.68875646591187</v>
       </c>
       <c r="H117" t="n">
         <v>230218</v>
@@ -3791,7 +3791,7 @@
         <v>2.98799991607666</v>
       </c>
       <c r="G118" t="n">
-        <v>2.69055700302124</v>
+        <v>2.69055724143982</v>
       </c>
       <c r="H118" t="n">
         <v>164670</v>
@@ -3820,7 +3820,7 @@
         <v>2.9760000705719</v>
       </c>
       <c r="G119" t="n">
-        <v>2.67975163459778</v>
+        <v>2.67975187301636</v>
       </c>
       <c r="H119" t="n">
         <v>138195</v>
@@ -3878,7 +3878,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G121" t="n">
-        <v>2.68335342407227</v>
+        <v>2.68335366249084</v>
       </c>
       <c r="H121" t="n">
         <v>230872</v>
@@ -3907,7 +3907,7 @@
         <v>3.00200009346008</v>
       </c>
       <c r="G122" t="n">
-        <v>2.70316362380981</v>
+        <v>2.70316338539124</v>
       </c>
       <c r="H122" t="n">
         <v>492519</v>
@@ -3965,7 +3965,7 @@
         <v>2.96600008010864</v>
       </c>
       <c r="G124" t="n">
-        <v>2.67074728012085</v>
+        <v>2.67074704170227</v>
       </c>
       <c r="H124" t="n">
         <v>538453</v>
@@ -3994,7 +3994,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G125" t="n">
-        <v>2.65633988380432</v>
+        <v>2.6563401222229</v>
       </c>
       <c r="H125" t="n">
         <v>301292</v>
@@ -4023,7 +4023,7 @@
         <v>2.99200010299683</v>
       </c>
       <c r="G126" t="n">
-        <v>2.69415926933289</v>
+        <v>2.69415903091431</v>
       </c>
       <c r="H126" t="n">
         <v>265025</v>
@@ -4052,7 +4052,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G127" t="n">
-        <v>2.71937155723572</v>
+        <v>2.7193717956543</v>
       </c>
       <c r="H127" t="n">
         <v>472950</v>
@@ -4081,7 +4081,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G128" t="n">
-        <v>2.68335342407227</v>
+        <v>2.68335366249084</v>
       </c>
       <c r="H128" t="n">
         <v>601683</v>
@@ -4139,7 +4139,7 @@
         <v>2.92799997329712</v>
       </c>
       <c r="G130" t="n">
-        <v>2.63652992248535</v>
+        <v>2.63652968406677</v>
       </c>
       <c r="H130" t="n">
         <v>329492</v>
@@ -4168,7 +4168,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G131" t="n">
-        <v>2.62032198905945</v>
+        <v>2.62032175064087</v>
       </c>
       <c r="H131" t="n">
         <v>395059</v>
@@ -4255,7 +4255,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G134" t="n">
-        <v>2.54828524589539</v>
+        <v>2.54828548431396</v>
       </c>
       <c r="H134" t="n">
         <v>228306</v>
@@ -4371,7 +4371,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G138" t="n">
-        <v>2.55728983879089</v>
+        <v>2.55728960037231</v>
       </c>
       <c r="H138" t="n">
         <v>102337</v>
@@ -4400,7 +4400,7 @@
         <v>2.83200001716614</v>
       </c>
       <c r="G139" t="n">
-        <v>2.55008625984192</v>
+        <v>2.5500864982605</v>
       </c>
       <c r="H139" t="n">
         <v>63393</v>
@@ -4487,7 +4487,7 @@
         <v>2.8659999370575</v>
       </c>
       <c r="G142" t="n">
-        <v>2.58070182800293</v>
+        <v>2.58070158958435</v>
       </c>
       <c r="H142" t="n">
         <v>182319</v>
@@ -4603,7 +4603,7 @@
         <v>2.84599995613098</v>
       </c>
       <c r="G146" t="n">
-        <v>2.56269264221191</v>
+        <v>2.56269240379333</v>
       </c>
       <c r="H146" t="n">
         <v>95512</v>
@@ -4632,7 +4632,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G147" t="n">
-        <v>2.58430337905884</v>
+        <v>2.58430361747742</v>
       </c>
       <c r="H147" t="n">
         <v>289366</v>
@@ -4661,7 +4661,7 @@
         <v>2.86800003051758</v>
       </c>
       <c r="G148" t="n">
-        <v>2.58250260353088</v>
+        <v>2.58250284194946</v>
       </c>
       <c r="H148" t="n">
         <v>580188</v>
@@ -4719,7 +4719,7 @@
         <v>2.90799999237061</v>
       </c>
       <c r="G150" t="n">
-        <v>2.61852097511292</v>
+        <v>2.61852073669434</v>
       </c>
       <c r="H150" t="n">
         <v>261501</v>
@@ -4748,7 +4748,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G151" t="n">
-        <v>2.63833069801331</v>
+        <v>2.63833093643188</v>
       </c>
       <c r="H151" t="n">
         <v>366145</v>
@@ -4777,7 +4777,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G152" t="n">
-        <v>2.65633988380432</v>
+        <v>2.6563401222229</v>
       </c>
       <c r="H152" t="n">
         <v>326136</v>
@@ -4864,7 +4864,7 @@
         <v>2.92600011825562</v>
       </c>
       <c r="G155" t="n">
-        <v>2.63472890853882</v>
+        <v>2.6347291469574</v>
       </c>
       <c r="H155" t="n">
         <v>146915</v>
@@ -4922,7 +4922,7 @@
         <v>2.81599998474121</v>
       </c>
       <c r="G157" t="n">
-        <v>2.53567910194397</v>
+        <v>2.53567886352539</v>
       </c>
       <c r="H157" t="n">
         <v>258393</v>
@@ -5009,7 +5009,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G160" t="n">
-        <v>2.73738074302673</v>
+        <v>2.73738050460815</v>
       </c>
       <c r="H160" t="n">
         <v>1245433</v>
@@ -5067,7 +5067,7 @@
         <v>3.11199998855591</v>
       </c>
       <c r="G162" t="n">
-        <v>2.80221366882324</v>
+        <v>2.80221343040466</v>
       </c>
       <c r="H162" t="n">
         <v>1090032</v>
@@ -5096,7 +5096,7 @@
         <v>3.07800006866455</v>
       </c>
       <c r="G163" t="n">
-        <v>2.77159810066223</v>
+        <v>2.77159786224365</v>
       </c>
       <c r="H163" t="n">
         <v>301973</v>
@@ -5183,7 +5183,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G166" t="n">
-        <v>2.87244892120361</v>
+        <v>2.87244915962219</v>
       </c>
       <c r="H166" t="n">
         <v>973243</v>
@@ -5241,7 +5241,7 @@
         <v>3.2260000705719</v>
       </c>
       <c r="G168" t="n">
-        <v>2.90486526489258</v>
+        <v>2.90486550331116</v>
       </c>
       <c r="H168" t="n">
         <v>1684867</v>
@@ -5299,7 +5299,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G170" t="n">
-        <v>2.9895076751709</v>
+        <v>2.98950791358948</v>
       </c>
       <c r="H170" t="n">
         <v>877610</v>
@@ -5444,7 +5444,7 @@
         <v>3.50600004196167</v>
       </c>
       <c r="G175" t="n">
-        <v>3.15699243545532</v>
+        <v>3.15699219703674</v>
       </c>
       <c r="H175" t="n">
         <v>1959547</v>
@@ -5502,7 +5502,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G177" t="n">
-        <v>3.06154441833496</v>
+        <v>3.06154417991638</v>
       </c>
       <c r="H177" t="n">
         <v>1430963</v>
@@ -5531,7 +5531,7 @@
         <v>3.31800007820129</v>
       </c>
       <c r="G178" t="n">
-        <v>2.98770713806152</v>
+        <v>2.98770689964294</v>
       </c>
       <c r="H178" t="n">
         <v>742754</v>
@@ -5618,7 +5618,7 @@
         <v>3.13199996948242</v>
       </c>
       <c r="G181" t="n">
-        <v>2.8202223777771</v>
+        <v>2.82022261619568</v>
       </c>
       <c r="H181" t="n">
         <v>951170</v>
@@ -5676,7 +5676,7 @@
         <v>3.13199996948242</v>
       </c>
       <c r="G183" t="n">
-        <v>2.8202223777771</v>
+        <v>2.82022261619568</v>
       </c>
       <c r="H183" t="n">
         <v>1171358</v>
@@ -5734,7 +5734,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G185" t="n">
-        <v>2.89045810699463</v>
+        <v>2.89045786857605</v>
       </c>
       <c r="H185" t="n">
         <v>709125</v>
@@ -5792,7 +5792,7 @@
         <v>3.13199996948242</v>
       </c>
       <c r="G187" t="n">
-        <v>2.8202223777771</v>
+        <v>2.82022261619568</v>
       </c>
       <c r="H187" t="n">
         <v>486844</v>
@@ -5908,7 +5908,7 @@
         <v>3.18199992179871</v>
       </c>
       <c r="G191" t="n">
-        <v>2.86524510383606</v>
+        <v>2.86524534225464</v>
       </c>
       <c r="H191" t="n">
         <v>278666</v>
@@ -5937,7 +5937,7 @@
         <v>3.16799998283386</v>
       </c>
       <c r="G192" t="n">
-        <v>2.85263872146606</v>
+        <v>2.85263895988464</v>
       </c>
       <c r="H192" t="n">
         <v>381457</v>
@@ -6024,7 +6024,7 @@
         <v>3.16400003433228</v>
       </c>
       <c r="G195" t="n">
-        <v>2.84903693199158</v>
+        <v>2.84903717041016</v>
       </c>
       <c r="H195" t="n">
         <v>562311</v>
@@ -6053,7 +6053,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G196" t="n">
-        <v>2.80491471290588</v>
+        <v>2.80491495132446</v>
       </c>
       <c r="H196" t="n">
         <v>835838</v>
@@ -6082,7 +6082,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G197" t="n">
-        <v>2.84993743896484</v>
+        <v>2.84993767738342</v>
       </c>
       <c r="H197" t="n">
         <v>267637</v>
@@ -6169,7 +6169,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G200" t="n">
-        <v>2.79591035842896</v>
+        <v>2.79591012001038</v>
       </c>
       <c r="H200" t="n">
         <v>277567</v>
@@ -6227,7 +6227,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G202" t="n">
-        <v>2.77339863777161</v>
+        <v>2.77339887619019</v>
       </c>
       <c r="H202" t="n">
         <v>272137</v>
@@ -6256,7 +6256,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G203" t="n">
-        <v>2.7643940448761</v>
+        <v>2.76439452171326</v>
       </c>
       <c r="H203" t="n">
         <v>271367</v>
@@ -6314,7 +6314,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G205" t="n">
-        <v>2.67434883117676</v>
+        <v>2.67434906959534</v>
       </c>
       <c r="H205" t="n">
         <v>598555</v>
@@ -6372,7 +6372,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G207" t="n">
-        <v>2.63833069801331</v>
+        <v>2.63833093643188</v>
       </c>
       <c r="H207" t="n">
         <v>256503</v>
@@ -6401,7 +6401,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G208" t="n">
-        <v>2.66534447669983</v>
+        <v>2.66534423828125</v>
       </c>
       <c r="H208" t="n">
         <v>290531</v>
@@ -6430,7 +6430,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G209" t="n">
-        <v>2.63833069801331</v>
+        <v>2.63833093643188</v>
       </c>
       <c r="H209" t="n">
         <v>276036</v>
@@ -6488,7 +6488,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G211" t="n">
-        <v>2.57529902458191</v>
+        <v>2.57529878616333</v>
       </c>
       <c r="H211" t="n">
         <v>2239887</v>
@@ -6517,7 +6517,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G212" t="n">
-        <v>2.54828524589539</v>
+        <v>2.54828548431396</v>
       </c>
       <c r="H212" t="n">
         <v>548010</v>
@@ -6575,7 +6575,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G214" t="n">
-        <v>2.55728983879089</v>
+        <v>2.55728960037231</v>
       </c>
       <c r="H214" t="n">
         <v>507186</v>
@@ -6604,7 +6604,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G215" t="n">
-        <v>2.57529902458191</v>
+        <v>2.57529878616333</v>
       </c>
       <c r="H215" t="n">
         <v>1072643</v>
@@ -6633,7 +6633,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G216" t="n">
-        <v>2.58430337905884</v>
+        <v>2.58430361747742</v>
       </c>
       <c r="H216" t="n">
         <v>404218</v>
@@ -6662,7 +6662,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G217" t="n">
-        <v>2.54828524589539</v>
+        <v>2.54828548431396</v>
       </c>
       <c r="H217" t="n">
         <v>601149</v>
@@ -6691,7 +6691,7 @@
         <v>2.875</v>
       </c>
       <c r="G218" t="n">
-        <v>2.58880567550659</v>
+        <v>2.58880591392517</v>
       </c>
       <c r="H218" t="n">
         <v>460755</v>
@@ -6749,7 +6749,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G220" t="n">
-        <v>2.66534447669983</v>
+        <v>2.66534423828125</v>
       </c>
       <c r="H220" t="n">
         <v>807427</v>
@@ -6778,7 +6778,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G221" t="n">
-        <v>2.68785572052002</v>
+        <v>2.68785548210144</v>
       </c>
       <c r="H221" t="n">
         <v>693872</v>
@@ -6836,7 +6836,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G223" t="n">
-        <v>2.68785572052002</v>
+        <v>2.68785548210144</v>
       </c>
       <c r="H223" t="n">
         <v>289774</v>
@@ -6865,7 +6865,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G224" t="n">
-        <v>2.71486949920654</v>
+        <v>2.71486926078796</v>
       </c>
       <c r="H224" t="n">
         <v>302122</v>
@@ -6894,7 +6894,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G225" t="n">
-        <v>2.73287868499756</v>
+        <v>2.73287844657898</v>
       </c>
       <c r="H225" t="n">
         <v>325591</v>
@@ -7010,7 +7010,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G229" t="n">
-        <v>2.80491471290588</v>
+        <v>2.80491495132446</v>
       </c>
       <c r="H229" t="n">
         <v>265295</v>
@@ -7126,7 +7126,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G233" t="n">
-        <v>2.7643940448761</v>
+        <v>2.76439452171326</v>
       </c>
       <c r="H233" t="n">
         <v>219195</v>
@@ -7329,7 +7329,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G240" t="n">
-        <v>2.71036720275879</v>
+        <v>2.71036696434021</v>
       </c>
       <c r="H240" t="n">
         <v>268134</v>
@@ -7358,7 +7358,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G241" t="n">
-        <v>2.73287868499756</v>
+        <v>2.73287844657898</v>
       </c>
       <c r="H241" t="n">
         <v>156956</v>
@@ -7445,7 +7445,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G244" t="n">
-        <v>2.80041265487671</v>
+        <v>2.80041241645813</v>
       </c>
       <c r="H244" t="n">
         <v>672793</v>
@@ -7474,7 +7474,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G245" t="n">
-        <v>2.77339863777161</v>
+        <v>2.77339887619019</v>
       </c>
       <c r="H245" t="n">
         <v>803152</v>
@@ -7532,7 +7532,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G247" t="n">
-        <v>2.71937155723572</v>
+        <v>2.7193717956543</v>
       </c>
       <c r="H247" t="n">
         <v>326171</v>
@@ -7590,7 +7590,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G249" t="n">
-        <v>2.66984677314758</v>
+        <v>2.669846534729</v>
       </c>
       <c r="H249" t="n">
         <v>254041</v>
@@ -7619,7 +7619,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G250" t="n">
-        <v>2.65633988380432</v>
+        <v>2.6563401222229</v>
       </c>
       <c r="H250" t="n">
         <v>375208</v>
@@ -7648,7 +7648,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G251" t="n">
-        <v>2.66534447669983</v>
+        <v>2.66534423828125</v>
       </c>
       <c r="H251" t="n">
         <v>193370</v>
@@ -7677,7 +7677,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G252" t="n">
-        <v>2.65633988380432</v>
+        <v>2.6563401222229</v>
       </c>
       <c r="H252" t="n">
         <v>198249</v>
@@ -7706,7 +7706,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G253" t="n">
-        <v>2.68785572052002</v>
+        <v>2.68785548210144</v>
       </c>
       <c r="H253" t="n">
         <v>521926</v>
@@ -7793,7 +7793,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G256" t="n">
-        <v>2.63852882385254</v>
+        <v>2.63852858543396</v>
       </c>
       <c r="H256" t="n">
         <v>424764</v>
@@ -7822,7 +7822,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G257" t="n">
-        <v>2.63387513160706</v>
+        <v>2.63387537002563</v>
       </c>
       <c r="H257" t="n">
         <v>331330</v>
@@ -8025,7 +8025,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G264" t="n">
-        <v>2.63387513160706</v>
+        <v>2.63387537002563</v>
       </c>
       <c r="H264" t="n">
         <v>380253</v>
@@ -8054,7 +8054,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G265" t="n">
-        <v>2.61991500854492</v>
+        <v>2.61991477012634</v>
       </c>
       <c r="H265" t="n">
         <v>268393</v>
@@ -8083,7 +8083,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G266" t="n">
-        <v>2.61991500854492</v>
+        <v>2.61991477012634</v>
       </c>
       <c r="H266" t="n">
         <v>334646</v>
@@ -8170,7 +8170,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G269" t="n">
-        <v>2.62456798553467</v>
+        <v>2.62456822395325</v>
       </c>
       <c r="H269" t="n">
         <v>267385</v>
@@ -8199,7 +8199,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G270" t="n">
-        <v>2.62456798553467</v>
+        <v>2.62456822395325</v>
       </c>
       <c r="H270" t="n">
         <v>255476</v>
@@ -8344,7 +8344,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G275" t="n">
-        <v>2.62456798553467</v>
+        <v>2.62456822395325</v>
       </c>
       <c r="H275" t="n">
         <v>175603</v>
@@ -8373,7 +8373,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G276" t="n">
-        <v>2.61991500854492</v>
+        <v>2.61991477012634</v>
       </c>
       <c r="H276" t="n">
         <v>180030</v>
@@ -8634,7 +8634,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G285" t="n">
-        <v>2.49427080154419</v>
+        <v>2.49427056312561</v>
       </c>
       <c r="H285" t="n">
         <v>387349</v>
@@ -8692,7 +8692,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G287" t="n">
-        <v>2.52684497833252</v>
+        <v>2.52684473991394</v>
       </c>
       <c r="H287" t="n">
         <v>123001</v>
@@ -8721,7 +8721,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G288" t="n">
-        <v>2.54545879364014</v>
+        <v>2.54545903205872</v>
       </c>
       <c r="H288" t="n">
         <v>248118</v>
@@ -8750,7 +8750,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G289" t="n">
-        <v>2.54080533981323</v>
+        <v>2.54080557823181</v>
       </c>
       <c r="H289" t="n">
         <v>290279</v>
@@ -8779,7 +8779,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G290" t="n">
-        <v>2.531498670578</v>
+        <v>2.53149843215942</v>
       </c>
       <c r="H290" t="n">
         <v>177641</v>
@@ -8924,7 +8924,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G295" t="n">
-        <v>2.61991500854492</v>
+        <v>2.61991477012634</v>
       </c>
       <c r="H295" t="n">
         <v>403095</v>
@@ -8953,7 +8953,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G296" t="n">
-        <v>2.61991500854492</v>
+        <v>2.61991477012634</v>
       </c>
       <c r="H296" t="n">
         <v>436118</v>
@@ -9069,7 +9069,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G300" t="n">
-        <v>2.61991500854492</v>
+        <v>2.61991477012634</v>
       </c>
       <c r="H300" t="n">
         <v>249379</v>
@@ -9272,7 +9272,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G307" t="n">
-        <v>2.33605170249939</v>
+        <v>2.33605194091797</v>
       </c>
       <c r="H307" t="n">
         <v>1179759</v>
@@ -9301,7 +9301,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G308" t="n">
-        <v>2.31743788719177</v>
+        <v>2.31743812561035</v>
       </c>
       <c r="H308" t="n">
         <v>642373</v>
@@ -9359,7 +9359,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G310" t="n">
-        <v>2.33605170249939</v>
+        <v>2.33605194091797</v>
       </c>
       <c r="H310" t="n">
         <v>598360</v>
@@ -9388,7 +9388,7 @@
         <v>2.56500005722046</v>
       </c>
       <c r="G311" t="n">
-        <v>2.38724040985107</v>
+        <v>2.3872401714325</v>
       </c>
       <c r="H311" t="n">
         <v>611830</v>
@@ -9446,7 +9446,7 @@
         <v>2.56500005722046</v>
       </c>
       <c r="G313" t="n">
-        <v>2.38724040985107</v>
+        <v>2.3872401714325</v>
       </c>
       <c r="H313" t="n">
         <v>487152</v>
@@ -9591,7 +9591,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G318" t="n">
-        <v>2.42912149429321</v>
+        <v>2.42912173271179</v>
       </c>
       <c r="H318" t="n">
         <v>143426</v>
@@ -9620,7 +9620,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G319" t="n">
-        <v>2.46169590950012</v>
+        <v>2.4616961479187</v>
       </c>
       <c r="H319" t="n">
         <v>341199</v>
@@ -9765,7 +9765,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G324" t="n">
-        <v>2.63387513160706</v>
+        <v>2.63387537002563</v>
       </c>
       <c r="H324" t="n">
         <v>845890</v>
@@ -9823,7 +9823,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G326" t="n">
-        <v>2.54080533981323</v>
+        <v>2.54080557823181</v>
       </c>
       <c r="H326" t="n">
         <v>1995862</v>
@@ -9968,7 +9968,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G331" t="n">
-        <v>2.52684497833252</v>
+        <v>2.52684473991394</v>
       </c>
       <c r="H331" t="n">
         <v>174270</v>
@@ -10258,7 +10258,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G341" t="n">
-        <v>2.63852882385254</v>
+        <v>2.63852858543396</v>
       </c>
       <c r="H341" t="n">
         <v>386548</v>
@@ -10287,7 +10287,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G342" t="n">
-        <v>2.63387513160706</v>
+        <v>2.63387537002563</v>
       </c>
       <c r="H342" t="n">
         <v>325109</v>
@@ -10432,7 +10432,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G347" t="n">
-        <v>2.49427080154419</v>
+        <v>2.49427056312561</v>
       </c>
       <c r="H347" t="n">
         <v>240234</v>
@@ -10548,7 +10548,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G351" t="n">
-        <v>2.71763801574707</v>
+        <v>2.71763825416565</v>
       </c>
       <c r="H351" t="n">
         <v>1174324</v>
@@ -10606,7 +10606,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G353" t="n">
-        <v>2.63387513160706</v>
+        <v>2.63387537002563</v>
       </c>
       <c r="H353" t="n">
         <v>1343987</v>
@@ -10722,7 +10722,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G357" t="n">
-        <v>2.61991500854492</v>
+        <v>2.61991477012634</v>
       </c>
       <c r="H357" t="n">
         <v>528618</v>
@@ -10780,7 +10780,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G359" t="n">
-        <v>2.531498670578</v>
+        <v>2.53149843215942</v>
       </c>
       <c r="H359" t="n">
         <v>283153</v>
@@ -10809,7 +10809,7 @@
         <v>2.70499992370605</v>
       </c>
       <c r="G360" t="n">
-        <v>2.51753783226013</v>
+        <v>2.51753807067871</v>
       </c>
       <c r="H360" t="n">
         <v>224865</v>
@@ -10925,7 +10925,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G364" t="n">
-        <v>2.63852882385254</v>
+        <v>2.63852858543396</v>
       </c>
       <c r="H364" t="n">
         <v>1117900</v>
@@ -11186,7 +11186,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G373" t="n">
-        <v>2.61991500854492</v>
+        <v>2.61991477012634</v>
       </c>
       <c r="H373" t="n">
         <v>332593</v>
@@ -11273,7 +11273,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G376" t="n">
-        <v>2.68041014671326</v>
+        <v>2.68041038513184</v>
       </c>
       <c r="H376" t="n">
         <v>1005481</v>
@@ -11505,7 +11505,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G384" t="n">
-        <v>2.62456798553467</v>
+        <v>2.62456822395325</v>
       </c>
       <c r="H384" t="n">
         <v>261528</v>
@@ -11534,7 +11534,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G385" t="n">
-        <v>2.61991500854492</v>
+        <v>2.61991477012634</v>
       </c>
       <c r="H385" t="n">
         <v>258305</v>
@@ -11563,7 +11563,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G386" t="n">
-        <v>2.62922167778015</v>
+        <v>2.62922191619873</v>
       </c>
       <c r="H386" t="n">
         <v>122247</v>
@@ -11621,7 +11621,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G388" t="n">
-        <v>2.63852882385254</v>
+        <v>2.63852858543396</v>
       </c>
       <c r="H388" t="n">
         <v>243336</v>
@@ -11882,7 +11882,7 @@
         <v>2.89499998092651</v>
       </c>
       <c r="G397" t="n">
-        <v>2.69437074661255</v>
+        <v>2.69437050819397</v>
       </c>
       <c r="H397" t="n">
         <v>247508</v>
@@ -11940,7 +11940,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G399" t="n">
-        <v>2.71763801574707</v>
+        <v>2.71763825416565</v>
       </c>
       <c r="H399" t="n">
         <v>314529</v>
@@ -12143,7 +12143,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G406" t="n">
-        <v>2.78278708457947</v>
+        <v>2.78278684616089</v>
       </c>
       <c r="H406" t="n">
         <v>858592</v>
@@ -12201,7 +12201,7 @@
         <v>2.93499994277954</v>
       </c>
       <c r="G408" t="n">
-        <v>2.73159861564636</v>
+        <v>2.73159837722778</v>
       </c>
       <c r="H408" t="n">
         <v>366747</v>
@@ -12433,7 +12433,7 @@
         <v>2.93499994277954</v>
       </c>
       <c r="G416" t="n">
-        <v>2.73159861564636</v>
+        <v>2.73159837722778</v>
       </c>
       <c r="H416" t="n">
         <v>420901</v>
@@ -12636,7 +12636,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G423" t="n">
-        <v>2.63387513160706</v>
+        <v>2.63387537002563</v>
       </c>
       <c r="H423" t="n">
         <v>266696</v>
@@ -12694,7 +12694,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G425" t="n">
-        <v>2.71763801574707</v>
+        <v>2.71763825416565</v>
       </c>
       <c r="H425" t="n">
         <v>1259534</v>
@@ -12781,7 +12781,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G428" t="n">
-        <v>2.63852882385254</v>
+        <v>2.63852858543396</v>
       </c>
       <c r="H428" t="n">
         <v>1712952</v>
@@ -12926,7 +12926,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G433" t="n">
-        <v>2.54080533981323</v>
+        <v>2.54080557823181</v>
       </c>
       <c r="H433" t="n">
         <v>554263</v>
@@ -12955,7 +12955,7 @@
         <v>2.70499992370605</v>
       </c>
       <c r="G434" t="n">
-        <v>2.51753783226013</v>
+        <v>2.51753807067871</v>
       </c>
       <c r="H434" t="n">
         <v>1145037</v>
@@ -13013,7 +13013,7 @@
         <v>2.70499992370605</v>
       </c>
       <c r="G436" t="n">
-        <v>2.51753783226013</v>
+        <v>2.51753807067871</v>
       </c>
       <c r="H436" t="n">
         <v>385823</v>
@@ -13042,7 +13042,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G437" t="n">
-        <v>2.54545879364014</v>
+        <v>2.54545903205872</v>
       </c>
       <c r="H437" t="n">
         <v>263202</v>
@@ -13129,7 +13129,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G440" t="n">
-        <v>2.54080533981323</v>
+        <v>2.54080557823181</v>
       </c>
       <c r="H440" t="n">
         <v>201087</v>
@@ -13274,7 +13274,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G445" t="n">
-        <v>2.42912149429321</v>
+        <v>2.42912173271179</v>
       </c>
       <c r="H445" t="n">
         <v>381239</v>
@@ -13303,7 +13303,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G446" t="n">
-        <v>2.4384286403656</v>
+        <v>2.43842840194702</v>
       </c>
       <c r="H446" t="n">
         <v>430895</v>
@@ -13680,7 +13680,7 @@
         <v>2.5</v>
       </c>
       <c r="G459" t="n">
-        <v>2.32674503326416</v>
+        <v>2.32674479484558</v>
       </c>
       <c r="H459" t="n">
         <v>273470</v>
@@ -13738,7 +13738,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G461" t="n">
-        <v>2.33232927322388</v>
+        <v>2.3323290348053</v>
       </c>
       <c r="H461" t="n">
         <v>159605</v>
@@ -13767,7 +13767,7 @@
         <v>2.4539999961853</v>
       </c>
       <c r="G462" t="n">
-        <v>2.28393268585205</v>
+        <v>2.28393292427063</v>
       </c>
       <c r="H462" t="n">
         <v>213603</v>
@@ -13825,7 +13825,7 @@
         <v>2.59200000762939</v>
       </c>
       <c r="G464" t="n">
-        <v>2.41236901283264</v>
+        <v>2.41236925125122</v>
       </c>
       <c r="H464" t="n">
         <v>118274</v>
@@ -13999,7 +13999,7 @@
         <v>2.61400008201599</v>
       </c>
       <c r="G470" t="n">
-        <v>2.43284463882446</v>
+        <v>2.43284440040588</v>
       </c>
       <c r="H470" t="n">
         <v>181112</v>
@@ -14057,7 +14057,7 @@
         <v>2.58599996566772</v>
       </c>
       <c r="G472" t="n">
-        <v>2.40678477287292</v>
+        <v>2.4067850112915</v>
       </c>
       <c r="H472" t="n">
         <v>342752</v>
@@ -14347,7 +14347,7 @@
         <v>2.72399997711182</v>
       </c>
       <c r="G482" t="n">
-        <v>2.53522109985352</v>
+        <v>2.53522133827209</v>
       </c>
       <c r="H482" t="n">
         <v>409776</v>
@@ -14492,7 +14492,7 @@
         <v>2.81200003623962</v>
       </c>
       <c r="G487" t="n">
-        <v>2.61712265014648</v>
+        <v>2.61712288856506</v>
       </c>
       <c r="H487" t="n">
         <v>549599</v>
@@ -24909,6 +24909,35 @@
         <v>116759</v>
       </c>
       <c r="I846" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="s">
+        <v>9</v>
+      </c>
+      <c r="B847" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C847" t="n">
+        <v>2.50999999046326</v>
+      </c>
+      <c r="D847" t="n">
+        <v>2.63800001144409</v>
+      </c>
+      <c r="E847" t="n">
+        <v>2.40199995040894</v>
+      </c>
+      <c r="F847" t="n">
+        <v>2.60199999809265</v>
+      </c>
+      <c r="G847" t="n">
+        <v>2.60199999809265</v>
+      </c>
+      <c r="H847" t="n">
+        <v>586598</v>
+      </c>
+      <c r="I847" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/YACHT.MI.xlsx
+++ b/data/YACHT.MI.xlsx
@@ -427,7 +427,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G2" t="n">
-        <v>2.68335366249084</v>
+        <v>2.68335342407227</v>
       </c>
       <c r="H2" t="n">
         <v>9271589</v>
@@ -456,7 +456,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G3" t="n">
-        <v>2.62932634353638</v>
+        <v>2.6293261051178</v>
       </c>
       <c r="H3" t="n">
         <v>5523202</v>
@@ -485,7 +485,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G4" t="n">
-        <v>2.57529878616333</v>
+        <v>2.57529902458191</v>
       </c>
       <c r="H4" t="n">
         <v>2742684</v>
@@ -514,7 +514,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G5" t="n">
-        <v>2.59330821037292</v>
+        <v>2.59330797195435</v>
       </c>
       <c r="H5" t="n">
         <v>1453933</v>
@@ -543,7 +543,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G6" t="n">
-        <v>2.61131739616394</v>
+        <v>2.61131715774536</v>
       </c>
       <c r="H6" t="n">
         <v>687076</v>
@@ -601,7 +601,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G8" t="n">
-        <v>2.62932634353638</v>
+        <v>2.6293261051178</v>
       </c>
       <c r="H8" t="n">
         <v>470527</v>
@@ -630,7 +630,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G9" t="n">
-        <v>2.60231256484985</v>
+        <v>2.60231280326843</v>
       </c>
       <c r="H9" t="n">
         <v>370604</v>
@@ -659,7 +659,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G10" t="n">
-        <v>2.62932634353638</v>
+        <v>2.6293261051178</v>
       </c>
       <c r="H10" t="n">
         <v>167157</v>
@@ -717,7 +717,7 @@
         <v>2.89800000190735</v>
       </c>
       <c r="G12" t="n">
-        <v>2.60951638221741</v>
+        <v>2.60951614379883</v>
       </c>
       <c r="H12" t="n">
         <v>224571</v>
@@ -746,7 +746,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G13" t="n">
-        <v>2.60231256484985</v>
+        <v>2.60231280326843</v>
       </c>
       <c r="H13" t="n">
         <v>258873</v>
@@ -775,7 +775,7 @@
         <v>2.89599990844727</v>
       </c>
       <c r="G14" t="n">
-        <v>2.60771512985229</v>
+        <v>2.60771536827087</v>
       </c>
       <c r="H14" t="n">
         <v>336225</v>
@@ -833,7 +833,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G16" t="n">
-        <v>2.62932634353638</v>
+        <v>2.6293261051178</v>
       </c>
       <c r="H16" t="n">
         <v>234246</v>
@@ -862,7 +862,7 @@
         <v>2.99799990653992</v>
       </c>
       <c r="G17" t="n">
-        <v>2.69956135749817</v>
+        <v>2.69956159591675</v>
       </c>
       <c r="H17" t="n">
         <v>721392</v>
@@ -891,7 +891,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G18" t="n">
-        <v>2.84543514251709</v>
+        <v>2.84543538093567</v>
       </c>
       <c r="H18" t="n">
         <v>1195492</v>
@@ -920,7 +920,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G19" t="n">
-        <v>2.81842160224915</v>
+        <v>2.81842184066772</v>
       </c>
       <c r="H19" t="n">
         <v>1196581</v>
@@ -978,7 +978,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G21" t="n">
-        <v>2.82742643356323</v>
+        <v>2.82742619514465</v>
       </c>
       <c r="H21" t="n">
         <v>380820</v>
@@ -1007,7 +1007,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G22" t="n">
-        <v>2.7914080619812</v>
+        <v>2.79140782356262</v>
       </c>
       <c r="H22" t="n">
         <v>534782</v>
@@ -1065,7 +1065,7 @@
         <v>3.08200001716614</v>
       </c>
       <c r="G24" t="n">
-        <v>2.77519989013672</v>
+        <v>2.77519965171814</v>
       </c>
       <c r="H24" t="n">
         <v>383171</v>
@@ -1152,7 +1152,7 @@
         <v>3.2039999961853</v>
       </c>
       <c r="G27" t="n">
-        <v>2.88505506515503</v>
+        <v>2.88505530357361</v>
       </c>
       <c r="H27" t="n">
         <v>920776</v>
@@ -1181,7 +1181,7 @@
         <v>3.16599988937378</v>
       </c>
       <c r="G28" t="n">
-        <v>2.85083770751953</v>
+        <v>2.85083794593811</v>
       </c>
       <c r="H28" t="n">
         <v>869768</v>
@@ -1384,7 +1384,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G35" t="n">
-        <v>2.69235801696777</v>
+        <v>2.69235825538635</v>
       </c>
       <c r="H35" t="n">
         <v>358854</v>
@@ -1471,7 +1471,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G38" t="n">
-        <v>2.62932634353638</v>
+        <v>2.6293261051178</v>
       </c>
       <c r="H38" t="n">
         <v>113466</v>
@@ -1558,7 +1558,7 @@
         <v>2.89800000190735</v>
       </c>
       <c r="G41" t="n">
-        <v>2.60951638221741</v>
+        <v>2.60951614379883</v>
       </c>
       <c r="H41" t="n">
         <v>443086</v>
@@ -1587,7 +1587,7 @@
         <v>2.91599988937378</v>
       </c>
       <c r="G42" t="n">
-        <v>2.62572431564331</v>
+        <v>2.62572455406189</v>
       </c>
       <c r="H42" t="n">
         <v>438565</v>
@@ -1616,7 +1616,7 @@
         <v>2.90599989891052</v>
       </c>
       <c r="G43" t="n">
-        <v>2.61671996116638</v>
+        <v>2.6167197227478</v>
       </c>
       <c r="H43" t="n">
         <v>160349</v>
@@ -1645,7 +1645,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G44" t="n">
-        <v>2.61131739616394</v>
+        <v>2.61131715774536</v>
       </c>
       <c r="H44" t="n">
         <v>199436</v>
@@ -1674,7 +1674,7 @@
         <v>2.89800000190735</v>
       </c>
       <c r="G45" t="n">
-        <v>2.60951638221741</v>
+        <v>2.60951614379883</v>
       </c>
       <c r="H45" t="n">
         <v>158184</v>
@@ -1761,7 +1761,7 @@
         <v>2.90799999237061</v>
       </c>
       <c r="G48" t="n">
-        <v>2.61852073669434</v>
+        <v>2.61852097511292</v>
       </c>
       <c r="H48" t="n">
         <v>395238</v>
@@ -1877,7 +1877,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G52" t="n">
-        <v>2.58430361747742</v>
+        <v>2.58430337905884</v>
       </c>
       <c r="H52" t="n">
         <v>406342</v>
@@ -1906,7 +1906,7 @@
         <v>2.81200003623962</v>
       </c>
       <c r="G53" t="n">
-        <v>2.53207731246948</v>
+        <v>2.5320770740509</v>
       </c>
       <c r="H53" t="n">
         <v>479328</v>
@@ -1964,7 +1964,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G55" t="n">
-        <v>2.59330821037292</v>
+        <v>2.59330797195435</v>
       </c>
       <c r="H55" t="n">
         <v>397112</v>
@@ -1993,7 +1993,7 @@
         <v>2.8840000629425</v>
       </c>
       <c r="G56" t="n">
-        <v>2.59690976142883</v>
+        <v>2.59690999984741</v>
       </c>
       <c r="H56" t="n">
         <v>223974</v>
@@ -2022,7 +2022,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G57" t="n">
-        <v>2.59330821037292</v>
+        <v>2.59330797195435</v>
       </c>
       <c r="H57" t="n">
         <v>345784</v>
@@ -2051,7 +2051,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G58" t="n">
-        <v>2.61131739616394</v>
+        <v>2.61131715774536</v>
       </c>
       <c r="H58" t="n">
         <v>212860</v>
@@ -2109,7 +2109,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G60" t="n">
-        <v>2.61131739616394</v>
+        <v>2.61131715774536</v>
       </c>
       <c r="H60" t="n">
         <v>266199</v>
@@ -2167,7 +2167,7 @@
         <v>3.0239999294281</v>
       </c>
       <c r="G62" t="n">
-        <v>2.72297358512878</v>
+        <v>2.72297334671021</v>
       </c>
       <c r="H62" t="n">
         <v>610853</v>
@@ -2196,7 +2196,7 @@
         <v>2.99799990653992</v>
       </c>
       <c r="G63" t="n">
-        <v>2.69956135749817</v>
+        <v>2.69956159591675</v>
       </c>
       <c r="H63" t="n">
         <v>323387</v>
@@ -2254,7 +2254,7 @@
         <v>2.88599991798401</v>
       </c>
       <c r="G65" t="n">
-        <v>2.59871077537537</v>
+        <v>2.59871053695679</v>
       </c>
       <c r="H65" t="n">
         <v>297762</v>
@@ -2283,7 +2283,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G66" t="n">
-        <v>2.61131739616394</v>
+        <v>2.61131715774536</v>
       </c>
       <c r="H66" t="n">
         <v>155416</v>
@@ -2341,7 +2341,7 @@
         <v>2.80399990081787</v>
       </c>
       <c r="G68" t="n">
-        <v>2.52487349510193</v>
+        <v>2.52487325668335</v>
       </c>
       <c r="H68" t="n">
         <v>241271</v>
@@ -2370,7 +2370,7 @@
         <v>2.85800004005432</v>
       </c>
       <c r="G69" t="n">
-        <v>2.57349801063538</v>
+        <v>2.57349824905396</v>
       </c>
       <c r="H69" t="n">
         <v>362600</v>
@@ -2428,7 +2428,7 @@
         <v>2.81599998474121</v>
       </c>
       <c r="G71" t="n">
-        <v>2.53567886352539</v>
+        <v>2.53567910194397</v>
       </c>
       <c r="H71" t="n">
         <v>188200</v>
@@ -2457,7 +2457,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G72" t="n">
-        <v>2.49425792694092</v>
+        <v>2.4942581653595</v>
       </c>
       <c r="H72" t="n">
         <v>268719</v>
@@ -2486,7 +2486,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G73" t="n">
-        <v>2.58430361747742</v>
+        <v>2.58430337905884</v>
       </c>
       <c r="H73" t="n">
         <v>296618</v>
@@ -2544,7 +2544,7 @@
         <v>2.81399989128113</v>
       </c>
       <c r="G75" t="n">
-        <v>2.53387784957886</v>
+        <v>2.53387808799744</v>
       </c>
       <c r="H75" t="n">
         <v>173870</v>
@@ -2573,7 +2573,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G76" t="n">
-        <v>2.58430361747742</v>
+        <v>2.58430337905884</v>
       </c>
       <c r="H76" t="n">
         <v>271694</v>
@@ -2602,7 +2602,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G77" t="n">
-        <v>2.58430361747742</v>
+        <v>2.58430337905884</v>
       </c>
       <c r="H77" t="n">
         <v>304675</v>
@@ -2631,7 +2631,7 @@
         <v>2.83599996566772</v>
       </c>
       <c r="G78" t="n">
-        <v>2.55368828773499</v>
+        <v>2.55368804931641</v>
       </c>
       <c r="H78" t="n">
         <v>311069</v>
@@ -2660,7 +2660,7 @@
         <v>2.81200003623962</v>
       </c>
       <c r="G79" t="n">
-        <v>2.53207731246948</v>
+        <v>2.5320770740509</v>
       </c>
       <c r="H79" t="n">
         <v>101378</v>
@@ -2689,7 +2689,7 @@
         <v>2.80800008773804</v>
       </c>
       <c r="G80" t="n">
-        <v>2.52847528457642</v>
+        <v>2.528475522995</v>
       </c>
       <c r="H80" t="n">
         <v>109058</v>
@@ -2718,7 +2718,7 @@
         <v>2.80200004577637</v>
       </c>
       <c r="G81" t="n">
-        <v>2.5230724811554</v>
+        <v>2.52307271957397</v>
       </c>
       <c r="H81" t="n">
         <v>98753</v>
@@ -2747,7 +2747,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G82" t="n">
-        <v>2.49425792694092</v>
+        <v>2.4942581653595</v>
       </c>
       <c r="H82" t="n">
         <v>89415</v>
@@ -2776,7 +2776,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G83" t="n">
-        <v>2.52127170562744</v>
+        <v>2.52127194404602</v>
       </c>
       <c r="H83" t="n">
         <v>119812</v>
@@ -2805,7 +2805,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G84" t="n">
-        <v>2.48525357246399</v>
+        <v>2.48525381088257</v>
       </c>
       <c r="H84" t="n">
         <v>88572</v>
@@ -2834,7 +2834,7 @@
         <v>2.73399996757507</v>
       </c>
       <c r="G85" t="n">
-        <v>2.46184158325195</v>
+        <v>2.46184182167053</v>
       </c>
       <c r="H85" t="n">
         <v>130892</v>
@@ -2921,7 +2921,7 @@
         <v>2.74600005149841</v>
       </c>
       <c r="G88" t="n">
-        <v>2.47264719009399</v>
+        <v>2.47264742851257</v>
       </c>
       <c r="H88" t="n">
         <v>107336</v>
@@ -2950,7 +2950,7 @@
         <v>2.74399995803833</v>
       </c>
       <c r="G89" t="n">
-        <v>2.47084641456604</v>
+        <v>2.47084617614746</v>
       </c>
       <c r="H89" t="n">
         <v>196450</v>
@@ -2979,7 +2979,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G90" t="n">
-        <v>2.46724438667297</v>
+        <v>2.46724462509155</v>
       </c>
       <c r="H90" t="n">
         <v>158160</v>
@@ -3008,7 +3008,7 @@
         <v>2.77600002288818</v>
       </c>
       <c r="G91" t="n">
-        <v>2.49966073036194</v>
+        <v>2.49966096878052</v>
       </c>
       <c r="H91" t="n">
         <v>97549</v>
@@ -3240,7 +3240,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G99" t="n">
-        <v>2.54828548431396</v>
+        <v>2.54828524589539</v>
       </c>
       <c r="H99" t="n">
         <v>101935</v>
@@ -3298,7 +3298,7 @@
         <v>2.93799996376038</v>
       </c>
       <c r="G101" t="n">
-        <v>2.64553451538086</v>
+        <v>2.64553427696228</v>
       </c>
       <c r="H101" t="n">
         <v>346899</v>
@@ -3414,7 +3414,7 @@
         <v>3.04800009727478</v>
       </c>
       <c r="G105" t="n">
-        <v>2.74458432197571</v>
+        <v>2.74458456039429</v>
       </c>
       <c r="H105" t="n">
         <v>558900</v>
@@ -3443,7 +3443,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G106" t="n">
-        <v>2.61131739616394</v>
+        <v>2.61131715774536</v>
       </c>
       <c r="H106" t="n">
         <v>635280</v>
@@ -3530,7 +3530,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G109" t="n">
-        <v>2.69235801696777</v>
+        <v>2.69235825538635</v>
       </c>
       <c r="H109" t="n">
         <v>399236</v>
@@ -3559,7 +3559,7 @@
         <v>2.9760000705719</v>
       </c>
       <c r="G110" t="n">
-        <v>2.67975187301636</v>
+        <v>2.67975163459778</v>
       </c>
       <c r="H110" t="n">
         <v>343647</v>
@@ -3617,7 +3617,7 @@
         <v>3</v>
       </c>
       <c r="G112" t="n">
-        <v>2.70136260986328</v>
+        <v>2.7013623714447</v>
       </c>
       <c r="H112" t="n">
         <v>552276</v>
@@ -3762,7 +3762,7 @@
         <v>2.98600006103516</v>
       </c>
       <c r="G117" t="n">
-        <v>2.68875646591187</v>
+        <v>2.68875622749329</v>
       </c>
       <c r="H117" t="n">
         <v>230218</v>
@@ -3820,7 +3820,7 @@
         <v>2.9760000705719</v>
       </c>
       <c r="G119" t="n">
-        <v>2.67975187301636</v>
+        <v>2.67975163459778</v>
       </c>
       <c r="H119" t="n">
         <v>138195</v>
@@ -3878,7 +3878,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G121" t="n">
-        <v>2.68335366249084</v>
+        <v>2.68335342407227</v>
       </c>
       <c r="H121" t="n">
         <v>230872</v>
@@ -3907,7 +3907,7 @@
         <v>3.00200009346008</v>
       </c>
       <c r="G122" t="n">
-        <v>2.70316338539124</v>
+        <v>2.70316362380981</v>
       </c>
       <c r="H122" t="n">
         <v>492519</v>
@@ -3965,7 +3965,7 @@
         <v>2.96600008010864</v>
       </c>
       <c r="G124" t="n">
-        <v>2.67074704170227</v>
+        <v>2.67074728012085</v>
       </c>
       <c r="H124" t="n">
         <v>538453</v>
@@ -4052,7 +4052,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G127" t="n">
-        <v>2.7193717956543</v>
+        <v>2.71937155723572</v>
       </c>
       <c r="H127" t="n">
         <v>472950</v>
@@ -4081,7 +4081,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G128" t="n">
-        <v>2.68335366249084</v>
+        <v>2.68335342407227</v>
       </c>
       <c r="H128" t="n">
         <v>601683</v>
@@ -4139,7 +4139,7 @@
         <v>2.92799997329712</v>
       </c>
       <c r="G130" t="n">
-        <v>2.63652968406677</v>
+        <v>2.63652992248535</v>
       </c>
       <c r="H130" t="n">
         <v>329492</v>
@@ -4197,7 +4197,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G132" t="n">
-        <v>2.59330821037292</v>
+        <v>2.59330797195435</v>
       </c>
       <c r="H132" t="n">
         <v>294667</v>
@@ -4255,7 +4255,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G134" t="n">
-        <v>2.54828548431396</v>
+        <v>2.54828524589539</v>
       </c>
       <c r="H134" t="n">
         <v>228306</v>
@@ -4313,7 +4313,7 @@
         <v>2.80599999427795</v>
       </c>
       <c r="G136" t="n">
-        <v>2.52667450904846</v>
+        <v>2.52667427062988</v>
       </c>
       <c r="H136" t="n">
         <v>138883</v>
@@ -4371,7 +4371,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G138" t="n">
-        <v>2.55728960037231</v>
+        <v>2.55728983879089</v>
       </c>
       <c r="H138" t="n">
         <v>102337</v>
@@ -4400,7 +4400,7 @@
         <v>2.83200001716614</v>
       </c>
       <c r="G139" t="n">
-        <v>2.5500864982605</v>
+        <v>2.55008625984192</v>
       </c>
       <c r="H139" t="n">
         <v>63393</v>
@@ -4458,7 +4458,7 @@
         <v>2.85800004005432</v>
       </c>
       <c r="G141" t="n">
-        <v>2.57349801063538</v>
+        <v>2.57349824905396</v>
       </c>
       <c r="H141" t="n">
         <v>157341</v>
@@ -4632,7 +4632,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G147" t="n">
-        <v>2.58430361747742</v>
+        <v>2.58430337905884</v>
       </c>
       <c r="H147" t="n">
         <v>289366</v>
@@ -4690,7 +4690,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G149" t="n">
-        <v>2.61131739616394</v>
+        <v>2.61131715774536</v>
       </c>
       <c r="H149" t="n">
         <v>610447</v>
@@ -4719,7 +4719,7 @@
         <v>2.90799999237061</v>
       </c>
       <c r="G150" t="n">
-        <v>2.61852073669434</v>
+        <v>2.61852097511292</v>
       </c>
       <c r="H150" t="n">
         <v>261501</v>
@@ -4864,7 +4864,7 @@
         <v>2.92600011825562</v>
       </c>
       <c r="G155" t="n">
-        <v>2.6347291469574</v>
+        <v>2.63472890853882</v>
       </c>
       <c r="H155" t="n">
         <v>146915</v>
@@ -4922,7 +4922,7 @@
         <v>2.81599998474121</v>
       </c>
       <c r="G157" t="n">
-        <v>2.53567886352539</v>
+        <v>2.53567910194397</v>
       </c>
       <c r="H157" t="n">
         <v>258393</v>
@@ -4980,7 +4980,7 @@
         <v>3.00799989700317</v>
       </c>
       <c r="G159" t="n">
-        <v>2.70856618881226</v>
+        <v>2.70856595039368</v>
       </c>
       <c r="H159" t="n">
         <v>1219518</v>
@@ -5009,7 +5009,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G160" t="n">
-        <v>2.73738050460815</v>
+        <v>2.73738074302673</v>
       </c>
       <c r="H160" t="n">
         <v>1245433</v>
@@ -5038,7 +5038,7 @@
         <v>3.12800002098083</v>
       </c>
       <c r="G161" t="n">
-        <v>2.81662058830261</v>
+        <v>2.81662082672119</v>
       </c>
       <c r="H161" t="n">
         <v>1210333</v>
@@ -5067,7 +5067,7 @@
         <v>3.11199998855591</v>
       </c>
       <c r="G162" t="n">
-        <v>2.80221343040466</v>
+        <v>2.80221366882324</v>
       </c>
       <c r="H162" t="n">
         <v>1090032</v>
@@ -5096,7 +5096,7 @@
         <v>3.07800006866455</v>
       </c>
       <c r="G163" t="n">
-        <v>2.77159786224365</v>
+        <v>2.77159810066223</v>
       </c>
       <c r="H163" t="n">
         <v>301973</v>
@@ -5125,7 +5125,7 @@
         <v>3.07399988174438</v>
       </c>
       <c r="G164" t="n">
-        <v>2.76799607276917</v>
+        <v>2.76799583435059</v>
       </c>
       <c r="H164" t="n">
         <v>359787</v>
@@ -5183,7 +5183,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G166" t="n">
-        <v>2.87244915962219</v>
+        <v>2.87244892120361</v>
       </c>
       <c r="H166" t="n">
         <v>973243</v>
@@ -5270,7 +5270,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G169" t="n">
-        <v>2.94448518753052</v>
+        <v>2.94448494911194</v>
       </c>
       <c r="H169" t="n">
         <v>1196461</v>
@@ -5502,7 +5502,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G177" t="n">
-        <v>3.06154417991638</v>
+        <v>3.06154441833496</v>
       </c>
       <c r="H177" t="n">
         <v>1430963</v>
@@ -5560,7 +5560,7 @@
         <v>3.29200005531311</v>
       </c>
       <c r="G179" t="n">
-        <v>2.96429514884949</v>
+        <v>2.96429538726807</v>
       </c>
       <c r="H179" t="n">
         <v>510602</v>
@@ -5618,7 +5618,7 @@
         <v>3.13199996948242</v>
       </c>
       <c r="G181" t="n">
-        <v>2.82022261619568</v>
+        <v>2.8202223777771</v>
       </c>
       <c r="H181" t="n">
         <v>951170</v>
@@ -5676,7 +5676,7 @@
         <v>3.13199996948242</v>
       </c>
       <c r="G183" t="n">
-        <v>2.82022261619568</v>
+        <v>2.8202223777771</v>
       </c>
       <c r="H183" t="n">
         <v>1171358</v>
@@ -5763,7 +5763,7 @@
         <v>3.19600009918213</v>
       </c>
       <c r="G186" t="n">
-        <v>2.87785172462463</v>
+        <v>2.87785148620605</v>
       </c>
       <c r="H186" t="n">
         <v>566793</v>
@@ -5792,7 +5792,7 @@
         <v>3.13199996948242</v>
       </c>
       <c r="G187" t="n">
-        <v>2.82022261619568</v>
+        <v>2.8202223777771</v>
       </c>
       <c r="H187" t="n">
         <v>486844</v>
@@ -5879,7 +5879,7 @@
         <v>3.16599988937378</v>
       </c>
       <c r="G190" t="n">
-        <v>2.85083770751953</v>
+        <v>2.85083794593811</v>
       </c>
       <c r="H190" t="n">
         <v>558141</v>
@@ -5908,7 +5908,7 @@
         <v>3.18199992179871</v>
       </c>
       <c r="G191" t="n">
-        <v>2.86524534225464</v>
+        <v>2.86524510383606</v>
       </c>
       <c r="H191" t="n">
         <v>278666</v>
@@ -6053,7 +6053,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G196" t="n">
-        <v>2.80491495132446</v>
+        <v>2.80491471290588</v>
       </c>
       <c r="H196" t="n">
         <v>835838</v>
@@ -6169,7 +6169,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G200" t="n">
-        <v>2.79591012001038</v>
+        <v>2.79591035842896</v>
       </c>
       <c r="H200" t="n">
         <v>277567</v>
@@ -6488,7 +6488,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G211" t="n">
-        <v>2.57529878616333</v>
+        <v>2.57529902458191</v>
       </c>
       <c r="H211" t="n">
         <v>2239887</v>
@@ -6517,7 +6517,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G212" t="n">
-        <v>2.54828548431396</v>
+        <v>2.54828524589539</v>
       </c>
       <c r="H212" t="n">
         <v>548010</v>
@@ -6546,7 +6546,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G213" t="n">
-        <v>2.52127170562744</v>
+        <v>2.52127194404602</v>
       </c>
       <c r="H213" t="n">
         <v>657781</v>
@@ -6575,7 +6575,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G214" t="n">
-        <v>2.55728960037231</v>
+        <v>2.55728983879089</v>
       </c>
       <c r="H214" t="n">
         <v>507186</v>
@@ -6604,7 +6604,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G215" t="n">
-        <v>2.57529878616333</v>
+        <v>2.57529902458191</v>
       </c>
       <c r="H215" t="n">
         <v>1072643</v>
@@ -6633,7 +6633,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G216" t="n">
-        <v>2.58430361747742</v>
+        <v>2.58430337905884</v>
       </c>
       <c r="H216" t="n">
         <v>404218</v>
@@ -6662,7 +6662,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G217" t="n">
-        <v>2.54828548431396</v>
+        <v>2.54828524589539</v>
       </c>
       <c r="H217" t="n">
         <v>601149</v>
@@ -6720,7 +6720,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G219" t="n">
-        <v>2.61131739616394</v>
+        <v>2.61131715774536</v>
       </c>
       <c r="H219" t="n">
         <v>259416</v>
@@ -6778,7 +6778,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G221" t="n">
-        <v>2.68785548210144</v>
+        <v>2.68785572052002</v>
       </c>
       <c r="H221" t="n">
         <v>693872</v>
@@ -6807,7 +6807,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G222" t="n">
-        <v>2.70586514472961</v>
+        <v>2.70586490631104</v>
       </c>
       <c r="H222" t="n">
         <v>301429</v>
@@ -6836,7 +6836,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G223" t="n">
-        <v>2.68785548210144</v>
+        <v>2.68785572052002</v>
       </c>
       <c r="H223" t="n">
         <v>289774</v>
@@ -6865,7 +6865,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G224" t="n">
-        <v>2.71486926078796</v>
+        <v>2.71486949920654</v>
       </c>
       <c r="H224" t="n">
         <v>302122</v>
@@ -6923,7 +6923,7 @@
         <v>3.04500007629395</v>
       </c>
       <c r="G226" t="n">
-        <v>2.74188327789307</v>
+        <v>2.74188303947449</v>
       </c>
       <c r="H226" t="n">
         <v>320777</v>
@@ -7010,7 +7010,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G229" t="n">
-        <v>2.80491495132446</v>
+        <v>2.80491471290588</v>
       </c>
       <c r="H229" t="n">
         <v>265295</v>
@@ -7039,7 +7039,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G230" t="n">
-        <v>2.7914080619812</v>
+        <v>2.79140782356262</v>
       </c>
       <c r="H230" t="n">
         <v>707525</v>
@@ -7155,7 +7155,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G234" t="n">
-        <v>2.7914080619812</v>
+        <v>2.79140782356262</v>
       </c>
       <c r="H234" t="n">
         <v>307932</v>
@@ -7184,7 +7184,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G235" t="n">
-        <v>2.78690576553345</v>
+        <v>2.78690552711487</v>
       </c>
       <c r="H235" t="n">
         <v>572294</v>
@@ -7329,7 +7329,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G240" t="n">
-        <v>2.71036696434021</v>
+        <v>2.71036720275879</v>
       </c>
       <c r="H240" t="n">
         <v>268134</v>
@@ -7445,7 +7445,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G244" t="n">
-        <v>2.80041241645813</v>
+        <v>2.80041265487671</v>
       </c>
       <c r="H244" t="n">
         <v>672793</v>
@@ -7503,7 +7503,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G246" t="n">
-        <v>2.78690576553345</v>
+        <v>2.78690552711487</v>
       </c>
       <c r="H246" t="n">
         <v>482864</v>
@@ -7532,7 +7532,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G247" t="n">
-        <v>2.7193717956543</v>
+        <v>2.71937155723572</v>
       </c>
       <c r="H247" t="n">
         <v>326171</v>
@@ -7706,7 +7706,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G253" t="n">
-        <v>2.68785548210144</v>
+        <v>2.68785572052002</v>
       </c>
       <c r="H253" t="n">
         <v>521926</v>
@@ -7793,7 +7793,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G256" t="n">
-        <v>2.63852858543396</v>
+        <v>2.63852882385254</v>
       </c>
       <c r="H256" t="n">
         <v>424764</v>
@@ -7822,7 +7822,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G257" t="n">
-        <v>2.63387537002563</v>
+        <v>2.63387513160706</v>
       </c>
       <c r="H257" t="n">
         <v>331330</v>
@@ -8025,7 +8025,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G264" t="n">
-        <v>2.63387537002563</v>
+        <v>2.63387513160706</v>
       </c>
       <c r="H264" t="n">
         <v>380253</v>
@@ -8054,7 +8054,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G265" t="n">
-        <v>2.61991477012634</v>
+        <v>2.61991500854492</v>
       </c>
       <c r="H265" t="n">
         <v>268393</v>
@@ -8083,7 +8083,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G266" t="n">
-        <v>2.61991477012634</v>
+        <v>2.61991500854492</v>
       </c>
       <c r="H266" t="n">
         <v>334646</v>
@@ -8170,7 +8170,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G269" t="n">
-        <v>2.62456822395325</v>
+        <v>2.62456798553467</v>
       </c>
       <c r="H269" t="n">
         <v>267385</v>
@@ -8199,7 +8199,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G270" t="n">
-        <v>2.62456822395325</v>
+        <v>2.62456798553467</v>
       </c>
       <c r="H270" t="n">
         <v>255476</v>
@@ -8344,7 +8344,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G275" t="n">
-        <v>2.62456822395325</v>
+        <v>2.62456798553467</v>
       </c>
       <c r="H275" t="n">
         <v>175603</v>
@@ -8373,7 +8373,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G276" t="n">
-        <v>2.61991477012634</v>
+        <v>2.61991500854492</v>
       </c>
       <c r="H276" t="n">
         <v>180030</v>
@@ -8634,7 +8634,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G285" t="n">
-        <v>2.49427056312561</v>
+        <v>2.49427080154419</v>
       </c>
       <c r="H285" t="n">
         <v>387349</v>
@@ -8692,7 +8692,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G287" t="n">
-        <v>2.52684473991394</v>
+        <v>2.52684497833252</v>
       </c>
       <c r="H287" t="n">
         <v>123001</v>
@@ -8721,7 +8721,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G288" t="n">
-        <v>2.54545903205872</v>
+        <v>2.54545879364014</v>
       </c>
       <c r="H288" t="n">
         <v>248118</v>
@@ -8750,7 +8750,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G289" t="n">
-        <v>2.54080557823181</v>
+        <v>2.54080533981323</v>
       </c>
       <c r="H289" t="n">
         <v>290279</v>
@@ -8779,7 +8779,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G290" t="n">
-        <v>2.53149843215942</v>
+        <v>2.531498670578</v>
       </c>
       <c r="H290" t="n">
         <v>177641</v>
@@ -8924,7 +8924,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G295" t="n">
-        <v>2.61991477012634</v>
+        <v>2.61991500854492</v>
       </c>
       <c r="H295" t="n">
         <v>403095</v>
@@ -8953,7 +8953,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G296" t="n">
-        <v>2.61991477012634</v>
+        <v>2.61991500854492</v>
       </c>
       <c r="H296" t="n">
         <v>436118</v>
@@ -9069,7 +9069,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G300" t="n">
-        <v>2.61991477012634</v>
+        <v>2.61991500854492</v>
       </c>
       <c r="H300" t="n">
         <v>249379</v>
@@ -9272,7 +9272,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G307" t="n">
-        <v>2.33605194091797</v>
+        <v>2.33605170249939</v>
       </c>
       <c r="H307" t="n">
         <v>1179759</v>
@@ -9301,7 +9301,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G308" t="n">
-        <v>2.31743812561035</v>
+        <v>2.31743788719177</v>
       </c>
       <c r="H308" t="n">
         <v>642373</v>
@@ -9359,7 +9359,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G310" t="n">
-        <v>2.33605194091797</v>
+        <v>2.33605170249939</v>
       </c>
       <c r="H310" t="n">
         <v>598360</v>
@@ -9388,7 +9388,7 @@
         <v>2.56500005722046</v>
       </c>
       <c r="G311" t="n">
-        <v>2.3872401714325</v>
+        <v>2.38724040985107</v>
       </c>
       <c r="H311" t="n">
         <v>611830</v>
@@ -9446,7 +9446,7 @@
         <v>2.56500005722046</v>
       </c>
       <c r="G313" t="n">
-        <v>2.3872401714325</v>
+        <v>2.38724040985107</v>
       </c>
       <c r="H313" t="n">
         <v>487152</v>
@@ -9591,7 +9591,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G318" t="n">
-        <v>2.42912173271179</v>
+        <v>2.42912149429321</v>
       </c>
       <c r="H318" t="n">
         <v>143426</v>
@@ -9620,7 +9620,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G319" t="n">
-        <v>2.4616961479187</v>
+        <v>2.46169590950012</v>
       </c>
       <c r="H319" t="n">
         <v>341199</v>
@@ -9765,7 +9765,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G324" t="n">
-        <v>2.63387537002563</v>
+        <v>2.63387513160706</v>
       </c>
       <c r="H324" t="n">
         <v>845890</v>
@@ -9823,7 +9823,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G326" t="n">
-        <v>2.54080557823181</v>
+        <v>2.54080533981323</v>
       </c>
       <c r="H326" t="n">
         <v>1995862</v>
@@ -9968,7 +9968,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G331" t="n">
-        <v>2.52684473991394</v>
+        <v>2.52684497833252</v>
       </c>
       <c r="H331" t="n">
         <v>174270</v>
@@ -10258,7 +10258,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G341" t="n">
-        <v>2.63852858543396</v>
+        <v>2.63852882385254</v>
       </c>
       <c r="H341" t="n">
         <v>386548</v>
@@ -10287,7 +10287,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G342" t="n">
-        <v>2.63387537002563</v>
+        <v>2.63387513160706</v>
       </c>
       <c r="H342" t="n">
         <v>325109</v>
@@ -10432,7 +10432,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G347" t="n">
-        <v>2.49427056312561</v>
+        <v>2.49427080154419</v>
       </c>
       <c r="H347" t="n">
         <v>240234</v>
@@ -10548,7 +10548,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G351" t="n">
-        <v>2.71763825416565</v>
+        <v>2.71763801574707</v>
       </c>
       <c r="H351" t="n">
         <v>1174324</v>
@@ -10606,7 +10606,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G353" t="n">
-        <v>2.63387537002563</v>
+        <v>2.63387513160706</v>
       </c>
       <c r="H353" t="n">
         <v>1343987</v>
@@ -10722,7 +10722,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G357" t="n">
-        <v>2.61991477012634</v>
+        <v>2.61991500854492</v>
       </c>
       <c r="H357" t="n">
         <v>528618</v>
@@ -10780,7 +10780,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G359" t="n">
-        <v>2.53149843215942</v>
+        <v>2.531498670578</v>
       </c>
       <c r="H359" t="n">
         <v>283153</v>
@@ -10809,7 +10809,7 @@
         <v>2.70499992370605</v>
       </c>
       <c r="G360" t="n">
-        <v>2.51753807067871</v>
+        <v>2.51753783226013</v>
       </c>
       <c r="H360" t="n">
         <v>224865</v>
@@ -10925,7 +10925,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G364" t="n">
-        <v>2.63852858543396</v>
+        <v>2.63852882385254</v>
       </c>
       <c r="H364" t="n">
         <v>1117900</v>
@@ -11186,7 +11186,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G373" t="n">
-        <v>2.61991477012634</v>
+        <v>2.61991500854492</v>
       </c>
       <c r="H373" t="n">
         <v>332593</v>
@@ -11273,7 +11273,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G376" t="n">
-        <v>2.68041038513184</v>
+        <v>2.68041014671326</v>
       </c>
       <c r="H376" t="n">
         <v>1005481</v>
@@ -11505,7 +11505,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G384" t="n">
-        <v>2.62456822395325</v>
+        <v>2.62456798553467</v>
       </c>
       <c r="H384" t="n">
         <v>261528</v>
@@ -11534,7 +11534,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G385" t="n">
-        <v>2.61991477012634</v>
+        <v>2.61991500854492</v>
       </c>
       <c r="H385" t="n">
         <v>258305</v>
@@ -11563,7 +11563,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G386" t="n">
-        <v>2.62922191619873</v>
+        <v>2.62922167778015</v>
       </c>
       <c r="H386" t="n">
         <v>122247</v>
@@ -11621,7 +11621,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G388" t="n">
-        <v>2.63852858543396</v>
+        <v>2.63852882385254</v>
       </c>
       <c r="H388" t="n">
         <v>243336</v>
@@ -11882,7 +11882,7 @@
         <v>2.89499998092651</v>
       </c>
       <c r="G397" t="n">
-        <v>2.69437050819397</v>
+        <v>2.69437074661255</v>
       </c>
       <c r="H397" t="n">
         <v>247508</v>
@@ -11940,7 +11940,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G399" t="n">
-        <v>2.71763825416565</v>
+        <v>2.71763801574707</v>
       </c>
       <c r="H399" t="n">
         <v>314529</v>
@@ -12143,7 +12143,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G406" t="n">
-        <v>2.78278684616089</v>
+        <v>2.78278708457947</v>
       </c>
       <c r="H406" t="n">
         <v>858592</v>
@@ -12201,7 +12201,7 @@
         <v>2.93499994277954</v>
       </c>
       <c r="G408" t="n">
-        <v>2.73159837722778</v>
+        <v>2.73159861564636</v>
       </c>
       <c r="H408" t="n">
         <v>366747</v>
@@ -12433,7 +12433,7 @@
         <v>2.93499994277954</v>
       </c>
       <c r="G416" t="n">
-        <v>2.73159837722778</v>
+        <v>2.73159861564636</v>
       </c>
       <c r="H416" t="n">
         <v>420901</v>
@@ -12636,7 +12636,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G423" t="n">
-        <v>2.63387537002563</v>
+        <v>2.63387513160706</v>
       </c>
       <c r="H423" t="n">
         <v>266696</v>
@@ -12694,7 +12694,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G425" t="n">
-        <v>2.71763825416565</v>
+        <v>2.71763801574707</v>
       </c>
       <c r="H425" t="n">
         <v>1259534</v>
@@ -12781,7 +12781,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G428" t="n">
-        <v>2.63852858543396</v>
+        <v>2.63852882385254</v>
       </c>
       <c r="H428" t="n">
         <v>1712952</v>
@@ -12926,7 +12926,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G433" t="n">
-        <v>2.54080557823181</v>
+        <v>2.54080533981323</v>
       </c>
       <c r="H433" t="n">
         <v>554263</v>
@@ -12955,7 +12955,7 @@
         <v>2.70499992370605</v>
       </c>
       <c r="G434" t="n">
-        <v>2.51753807067871</v>
+        <v>2.51753783226013</v>
       </c>
       <c r="H434" t="n">
         <v>1145037</v>
@@ -13013,7 +13013,7 @@
         <v>2.70499992370605</v>
       </c>
       <c r="G436" t="n">
-        <v>2.51753807067871</v>
+        <v>2.51753783226013</v>
       </c>
       <c r="H436" t="n">
         <v>385823</v>
@@ -13042,7 +13042,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G437" t="n">
-        <v>2.54545903205872</v>
+        <v>2.54545879364014</v>
       </c>
       <c r="H437" t="n">
         <v>263202</v>
@@ -13129,7 +13129,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G440" t="n">
-        <v>2.54080557823181</v>
+        <v>2.54080533981323</v>
       </c>
       <c r="H440" t="n">
         <v>201087</v>
@@ -13274,7 +13274,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G445" t="n">
-        <v>2.42912173271179</v>
+        <v>2.42912149429321</v>
       </c>
       <c r="H445" t="n">
         <v>381239</v>
@@ -13303,7 +13303,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G446" t="n">
-        <v>2.43842840194702</v>
+        <v>2.4384286403656</v>
       </c>
       <c r="H446" t="n">
         <v>430895</v>
@@ -13680,7 +13680,7 @@
         <v>2.5</v>
       </c>
       <c r="G459" t="n">
-        <v>2.32674479484558</v>
+        <v>2.32674503326416</v>
       </c>
       <c r="H459" t="n">
         <v>273470</v>
@@ -13738,7 +13738,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G461" t="n">
-        <v>2.3323290348053</v>
+        <v>2.33232927322388</v>
       </c>
       <c r="H461" t="n">
         <v>159605</v>
@@ -13767,7 +13767,7 @@
         <v>2.4539999961853</v>
       </c>
       <c r="G462" t="n">
-        <v>2.28393292427063</v>
+        <v>2.28393268585205</v>
       </c>
       <c r="H462" t="n">
         <v>213603</v>
@@ -13825,7 +13825,7 @@
         <v>2.59200000762939</v>
       </c>
       <c r="G464" t="n">
-        <v>2.41236925125122</v>
+        <v>2.41236901283264</v>
       </c>
       <c r="H464" t="n">
         <v>118274</v>
@@ -13999,7 +13999,7 @@
         <v>2.61400008201599</v>
       </c>
       <c r="G470" t="n">
-        <v>2.43284440040588</v>
+        <v>2.43284463882446</v>
       </c>
       <c r="H470" t="n">
         <v>181112</v>
@@ -14057,7 +14057,7 @@
         <v>2.58599996566772</v>
       </c>
       <c r="G472" t="n">
-        <v>2.4067850112915</v>
+        <v>2.40678477287292</v>
       </c>
       <c r="H472" t="n">
         <v>342752</v>
@@ -14347,7 +14347,7 @@
         <v>2.72399997711182</v>
       </c>
       <c r="G482" t="n">
-        <v>2.53522133827209</v>
+        <v>2.53522109985352</v>
       </c>
       <c r="H482" t="n">
         <v>409776</v>
@@ -14492,7 +14492,7 @@
         <v>2.81200003623962</v>
       </c>
       <c r="G487" t="n">
-        <v>2.61712288856506</v>
+        <v>2.61712265014648</v>
       </c>
       <c r="H487" t="n">
         <v>549599</v>
@@ -24938,6 +24938,35 @@
         <v>586598</v>
       </c>
       <c r="I847" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="s">
+        <v>9</v>
+      </c>
+      <c r="B848" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C848" t="n">
+        <v>2.55800008773804</v>
+      </c>
+      <c r="D848" t="n">
+        <v>2.63599991798401</v>
+      </c>
+      <c r="E848" t="n">
+        <v>2.55800008773804</v>
+      </c>
+      <c r="F848" t="n">
+        <v>2.58599996566772</v>
+      </c>
+      <c r="G848" t="n">
+        <v>2.58599996566772</v>
+      </c>
+      <c r="H848" t="n">
+        <v>173660</v>
+      </c>
+      <c r="I848" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/YACHT.MI.xlsx
+++ b/data/YACHT.MI.xlsx
@@ -24970,6 +24970,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="849">
+      <c r="A849" t="s">
+        <v>9</v>
+      </c>
+      <c r="B849" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C849" t="n">
+        <v>2.59999990463257</v>
+      </c>
+      <c r="D849" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="E849" t="n">
+        <v>2.55800008773804</v>
+      </c>
+      <c r="F849" t="n">
+        <v>2.55800008773804</v>
+      </c>
+      <c r="G849" t="n">
+        <v>2.55800008773804</v>
+      </c>
+      <c r="H849" t="n">
+        <v>208216</v>
+      </c>
+      <c r="I849" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/YACHT.MI.xlsx
+++ b/data/YACHT.MI.xlsx
@@ -514,7 +514,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G5" t="n">
-        <v>2.59330797195435</v>
+        <v>2.59330821037292</v>
       </c>
       <c r="H5" t="n">
         <v>1453933</v>
@@ -543,7 +543,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G6" t="n">
-        <v>2.61131715774536</v>
+        <v>2.61131739616394</v>
       </c>
       <c r="H6" t="n">
         <v>687076</v>
@@ -572,7 +572,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G7" t="n">
-        <v>2.62032175064087</v>
+        <v>2.62032198905945</v>
       </c>
       <c r="H7" t="n">
         <v>462954</v>
@@ -688,7 +688,7 @@
         <v>2.88199996948242</v>
       </c>
       <c r="G11" t="n">
-        <v>2.59510898590088</v>
+        <v>2.5951087474823</v>
       </c>
       <c r="H11" t="n">
         <v>527158</v>
@@ -717,7 +717,7 @@
         <v>2.89800000190735</v>
       </c>
       <c r="G12" t="n">
-        <v>2.60951614379883</v>
+        <v>2.60951638221741</v>
       </c>
       <c r="H12" t="n">
         <v>224571</v>
@@ -775,7 +775,7 @@
         <v>2.89599990844727</v>
       </c>
       <c r="G14" t="n">
-        <v>2.60771536827087</v>
+        <v>2.60771512985229</v>
       </c>
       <c r="H14" t="n">
         <v>336225</v>
@@ -891,7 +891,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G18" t="n">
-        <v>2.84543538093567</v>
+        <v>2.84543561935425</v>
       </c>
       <c r="H18" t="n">
         <v>1195492</v>
@@ -978,7 +978,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G21" t="n">
-        <v>2.82742619514465</v>
+        <v>2.82742643356323</v>
       </c>
       <c r="H21" t="n">
         <v>380820</v>
@@ -1007,7 +1007,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G22" t="n">
-        <v>2.79140782356262</v>
+        <v>2.7914080619812</v>
       </c>
       <c r="H22" t="n">
         <v>534782</v>
@@ -1065,7 +1065,7 @@
         <v>3.08200001716614</v>
       </c>
       <c r="G24" t="n">
-        <v>2.77519965171814</v>
+        <v>2.77519989013672</v>
       </c>
       <c r="H24" t="n">
         <v>383171</v>
@@ -1181,7 +1181,7 @@
         <v>3.16599988937378</v>
       </c>
       <c r="G28" t="n">
-        <v>2.85083794593811</v>
+        <v>2.85083770751953</v>
       </c>
       <c r="H28" t="n">
         <v>869768</v>
@@ -1210,7 +1210,7 @@
         <v>3.12199997901917</v>
       </c>
       <c r="G29" t="n">
-        <v>2.81121778488159</v>
+        <v>2.81121802330017</v>
       </c>
       <c r="H29" t="n">
         <v>544144</v>
@@ -1239,7 +1239,7 @@
         <v>3.17799997329712</v>
       </c>
       <c r="G30" t="n">
-        <v>2.86164355278015</v>
+        <v>2.86164331436157</v>
       </c>
       <c r="H30" t="n">
         <v>594226</v>
@@ -1326,7 +1326,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G33" t="n">
-        <v>2.7283763885498</v>
+        <v>2.72837615013123</v>
       </c>
       <c r="H33" t="n">
         <v>552267</v>
@@ -1384,7 +1384,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G35" t="n">
-        <v>2.69235825538635</v>
+        <v>2.69235801696777</v>
       </c>
       <c r="H35" t="n">
         <v>358854</v>
@@ -1413,7 +1413,7 @@
         <v>2.96199989318848</v>
       </c>
       <c r="G36" t="n">
-        <v>2.66714525222778</v>
+        <v>2.66714549064636</v>
       </c>
       <c r="H36" t="n">
         <v>99000</v>
@@ -1442,7 +1442,7 @@
         <v>2.96199989318848</v>
       </c>
       <c r="G37" t="n">
-        <v>2.66714525222778</v>
+        <v>2.66714549064636</v>
       </c>
       <c r="H37" t="n">
         <v>318498</v>
@@ -1500,7 +1500,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G39" t="n">
-        <v>2.6563401222229</v>
+        <v>2.65633988380432</v>
       </c>
       <c r="H39" t="n">
         <v>413206</v>
@@ -1529,7 +1529,7 @@
         <v>2.93400001525879</v>
       </c>
       <c r="G40" t="n">
-        <v>2.64193248748779</v>
+        <v>2.64193272590637</v>
       </c>
       <c r="H40" t="n">
         <v>560977</v>
@@ -1558,7 +1558,7 @@
         <v>2.89800000190735</v>
       </c>
       <c r="G41" t="n">
-        <v>2.60951614379883</v>
+        <v>2.60951638221741</v>
       </c>
       <c r="H41" t="n">
         <v>443086</v>
@@ -1587,7 +1587,7 @@
         <v>2.91599988937378</v>
       </c>
       <c r="G42" t="n">
-        <v>2.62572455406189</v>
+        <v>2.62572431564331</v>
       </c>
       <c r="H42" t="n">
         <v>438565</v>
@@ -1645,7 +1645,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G44" t="n">
-        <v>2.61131715774536</v>
+        <v>2.61131739616394</v>
       </c>
       <c r="H44" t="n">
         <v>199436</v>
@@ -1674,7 +1674,7 @@
         <v>2.89800000190735</v>
       </c>
       <c r="G45" t="n">
-        <v>2.60951614379883</v>
+        <v>2.60951638221741</v>
       </c>
       <c r="H45" t="n">
         <v>158184</v>
@@ -1732,7 +1732,7 @@
         <v>2.91400003433228</v>
       </c>
       <c r="G47" t="n">
-        <v>2.62392354011536</v>
+        <v>2.62392377853394</v>
       </c>
       <c r="H47" t="n">
         <v>681087</v>
@@ -1790,7 +1790,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G49" t="n">
-        <v>2.6563401222229</v>
+        <v>2.65633988380432</v>
       </c>
       <c r="H49" t="n">
         <v>278184</v>
@@ -1819,7 +1819,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G50" t="n">
-        <v>2.63833093643188</v>
+        <v>2.63833069801331</v>
       </c>
       <c r="H50" t="n">
         <v>440815</v>
@@ -1848,7 +1848,7 @@
         <v>2.89199995994568</v>
       </c>
       <c r="G51" t="n">
-        <v>2.60411357879639</v>
+        <v>2.60411334037781</v>
       </c>
       <c r="H51" t="n">
         <v>301022</v>
@@ -1906,7 +1906,7 @@
         <v>2.81200003623962</v>
       </c>
       <c r="G53" t="n">
-        <v>2.5320770740509</v>
+        <v>2.53207731246948</v>
       </c>
       <c r="H53" t="n">
         <v>479328</v>
@@ -1935,7 +1935,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G54" t="n">
-        <v>2.62032175064087</v>
+        <v>2.62032198905945</v>
       </c>
       <c r="H54" t="n">
         <v>470047</v>
@@ -1964,7 +1964,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G55" t="n">
-        <v>2.59330797195435</v>
+        <v>2.59330821037292</v>
       </c>
       <c r="H55" t="n">
         <v>397112</v>
@@ -2022,7 +2022,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G57" t="n">
-        <v>2.59330797195435</v>
+        <v>2.59330821037292</v>
       </c>
       <c r="H57" t="n">
         <v>345784</v>
@@ -2051,7 +2051,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G58" t="n">
-        <v>2.61131715774536</v>
+        <v>2.61131739616394</v>
       </c>
       <c r="H58" t="n">
         <v>212860</v>
@@ -2080,7 +2080,7 @@
         <v>2.93600010871887</v>
       </c>
       <c r="G59" t="n">
-        <v>2.64373373985291</v>
+        <v>2.64373350143433</v>
       </c>
       <c r="H59" t="n">
         <v>1235755</v>
@@ -2109,7 +2109,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G60" t="n">
-        <v>2.61131715774536</v>
+        <v>2.61131739616394</v>
       </c>
       <c r="H60" t="n">
         <v>266199</v>
@@ -2138,7 +2138,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G61" t="n">
-        <v>2.6563401222229</v>
+        <v>2.65633988380432</v>
       </c>
       <c r="H61" t="n">
         <v>481432</v>
@@ -2225,7 +2225,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G64" t="n">
-        <v>2.67434906959534</v>
+        <v>2.67434883117676</v>
       </c>
       <c r="H64" t="n">
         <v>215337</v>
@@ -2254,7 +2254,7 @@
         <v>2.88599991798401</v>
       </c>
       <c r="G65" t="n">
-        <v>2.59871053695679</v>
+        <v>2.59871077537537</v>
       </c>
       <c r="H65" t="n">
         <v>297762</v>
@@ -2283,7 +2283,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G66" t="n">
-        <v>2.61131715774536</v>
+        <v>2.61131739616394</v>
       </c>
       <c r="H66" t="n">
         <v>155416</v>
@@ -2312,7 +2312,7 @@
         <v>2.84599995613098</v>
       </c>
       <c r="G67" t="n">
-        <v>2.56269240379333</v>
+        <v>2.56269264221191</v>
       </c>
       <c r="H67" t="n">
         <v>325027</v>
@@ -2341,7 +2341,7 @@
         <v>2.80399990081787</v>
       </c>
       <c r="G68" t="n">
-        <v>2.52487325668335</v>
+        <v>2.52487373352051</v>
       </c>
       <c r="H68" t="n">
         <v>241271</v>
@@ -2370,7 +2370,7 @@
         <v>2.85800004005432</v>
       </c>
       <c r="G69" t="n">
-        <v>2.57349824905396</v>
+        <v>2.57349801063538</v>
       </c>
       <c r="H69" t="n">
         <v>362600</v>
@@ -2544,7 +2544,7 @@
         <v>2.81399989128113</v>
       </c>
       <c r="G75" t="n">
-        <v>2.53387808799744</v>
+        <v>2.53387832641602</v>
       </c>
       <c r="H75" t="n">
         <v>173870</v>
@@ -2660,7 +2660,7 @@
         <v>2.81200003623962</v>
       </c>
       <c r="G79" t="n">
-        <v>2.5320770740509</v>
+        <v>2.53207731246948</v>
       </c>
       <c r="H79" t="n">
         <v>101378</v>
@@ -2776,7 +2776,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G83" t="n">
-        <v>2.52127194404602</v>
+        <v>2.52127170562744</v>
       </c>
       <c r="H83" t="n">
         <v>119812</v>
@@ -2834,7 +2834,7 @@
         <v>2.73399996757507</v>
       </c>
       <c r="G85" t="n">
-        <v>2.46184182167053</v>
+        <v>2.46184158325195</v>
       </c>
       <c r="H85" t="n">
         <v>130892</v>
@@ -2863,7 +2863,7 @@
         <v>2.76399993896484</v>
       </c>
       <c r="G86" t="n">
-        <v>2.4888551235199</v>
+        <v>2.48885536193848</v>
       </c>
       <c r="H86" t="n">
         <v>72690</v>
@@ -3008,7 +3008,7 @@
         <v>2.77600002288818</v>
       </c>
       <c r="G91" t="n">
-        <v>2.49966096878052</v>
+        <v>2.49966073036194</v>
       </c>
       <c r="H91" t="n">
         <v>97549</v>
@@ -3095,7 +3095,7 @@
         <v>2.84599995613098</v>
       </c>
       <c r="G94" t="n">
-        <v>2.56269240379333</v>
+        <v>2.56269264221191</v>
       </c>
       <c r="H94" t="n">
         <v>207064</v>
@@ -3269,7 +3269,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G100" t="n">
-        <v>2.62032175064087</v>
+        <v>2.62032198905945</v>
       </c>
       <c r="H100" t="n">
         <v>107418</v>
@@ -3298,7 +3298,7 @@
         <v>2.93799996376038</v>
       </c>
       <c r="G101" t="n">
-        <v>2.64553427696228</v>
+        <v>2.64553451538086</v>
       </c>
       <c r="H101" t="n">
         <v>346899</v>
@@ -3356,7 +3356,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G103" t="n">
-        <v>2.7283763885498</v>
+        <v>2.72837615013123</v>
       </c>
       <c r="H103" t="n">
         <v>552357</v>
@@ -3443,7 +3443,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G106" t="n">
-        <v>2.61131715774536</v>
+        <v>2.61131739616394</v>
       </c>
       <c r="H106" t="n">
         <v>635280</v>
@@ -3501,7 +3501,7 @@
         <v>2.90400004386902</v>
       </c>
       <c r="G108" t="n">
-        <v>2.61491894721985</v>
+        <v>2.61491918563843</v>
       </c>
       <c r="H108" t="n">
         <v>295869</v>
@@ -3530,7 +3530,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G109" t="n">
-        <v>2.69235825538635</v>
+        <v>2.69235801696777</v>
       </c>
       <c r="H109" t="n">
         <v>399236</v>
@@ -3617,7 +3617,7 @@
         <v>3</v>
       </c>
       <c r="G112" t="n">
-        <v>2.7013623714447</v>
+        <v>2.70136260986328</v>
       </c>
       <c r="H112" t="n">
         <v>552276</v>
@@ -3646,7 +3646,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G113" t="n">
-        <v>2.62032175064087</v>
+        <v>2.62032198905945</v>
       </c>
       <c r="H113" t="n">
         <v>3703132</v>
@@ -3733,7 +3733,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G116" t="n">
-        <v>2.6563401222229</v>
+        <v>2.65633988380432</v>
       </c>
       <c r="H116" t="n">
         <v>209509</v>
@@ -3791,7 +3791,7 @@
         <v>2.98799991607666</v>
       </c>
       <c r="G118" t="n">
-        <v>2.69055724143982</v>
+        <v>2.69055700302124</v>
       </c>
       <c r="H118" t="n">
         <v>164670</v>
@@ -3994,7 +3994,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G125" t="n">
-        <v>2.6563401222229</v>
+        <v>2.65633988380432</v>
       </c>
       <c r="H125" t="n">
         <v>301292</v>
@@ -4023,7 +4023,7 @@
         <v>2.99200010299683</v>
       </c>
       <c r="G126" t="n">
-        <v>2.69415903091431</v>
+        <v>2.69415926933289</v>
       </c>
       <c r="H126" t="n">
         <v>265025</v>
@@ -4168,7 +4168,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G131" t="n">
-        <v>2.62032175064087</v>
+        <v>2.62032198905945</v>
       </c>
       <c r="H131" t="n">
         <v>395059</v>
@@ -4197,7 +4197,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G132" t="n">
-        <v>2.59330797195435</v>
+        <v>2.59330821037292</v>
       </c>
       <c r="H132" t="n">
         <v>294667</v>
@@ -4313,7 +4313,7 @@
         <v>2.80599999427795</v>
       </c>
       <c r="G136" t="n">
-        <v>2.52667427062988</v>
+        <v>2.52667450904846</v>
       </c>
       <c r="H136" t="n">
         <v>138883</v>
@@ -4458,7 +4458,7 @@
         <v>2.85800004005432</v>
       </c>
       <c r="G141" t="n">
-        <v>2.57349824905396</v>
+        <v>2.57349801063538</v>
       </c>
       <c r="H141" t="n">
         <v>157341</v>
@@ -4487,7 +4487,7 @@
         <v>2.8659999370575</v>
       </c>
       <c r="G142" t="n">
-        <v>2.58070158958435</v>
+        <v>2.58070182800293</v>
       </c>
       <c r="H142" t="n">
         <v>182319</v>
@@ -4603,7 +4603,7 @@
         <v>2.84599995613098</v>
       </c>
       <c r="G146" t="n">
-        <v>2.56269240379333</v>
+        <v>2.56269264221191</v>
       </c>
       <c r="H146" t="n">
         <v>95512</v>
@@ -4661,7 +4661,7 @@
         <v>2.86800003051758</v>
       </c>
       <c r="G148" t="n">
-        <v>2.58250284194946</v>
+        <v>2.58250260353088</v>
       </c>
       <c r="H148" t="n">
         <v>580188</v>
@@ -4690,7 +4690,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G149" t="n">
-        <v>2.61131715774536</v>
+        <v>2.61131739616394</v>
       </c>
       <c r="H149" t="n">
         <v>610447</v>
@@ -4748,7 +4748,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G151" t="n">
-        <v>2.63833093643188</v>
+        <v>2.63833069801331</v>
       </c>
       <c r="H151" t="n">
         <v>366145</v>
@@ -4777,7 +4777,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G152" t="n">
-        <v>2.6563401222229</v>
+        <v>2.65633988380432</v>
       </c>
       <c r="H152" t="n">
         <v>326136</v>
@@ -4980,7 +4980,7 @@
         <v>3.00799989700317</v>
       </c>
       <c r="G159" t="n">
-        <v>2.70856595039368</v>
+        <v>2.70856618881226</v>
       </c>
       <c r="H159" t="n">
         <v>1219518</v>
@@ -5038,7 +5038,7 @@
         <v>3.12800002098083</v>
       </c>
       <c r="G161" t="n">
-        <v>2.81662082672119</v>
+        <v>2.81662058830261</v>
       </c>
       <c r="H161" t="n">
         <v>1210333</v>
@@ -5125,7 +5125,7 @@
         <v>3.07399988174438</v>
       </c>
       <c r="G164" t="n">
-        <v>2.76799583435059</v>
+        <v>2.76799607276917</v>
       </c>
       <c r="H164" t="n">
         <v>359787</v>
@@ -5241,7 +5241,7 @@
         <v>3.2260000705719</v>
       </c>
       <c r="G168" t="n">
-        <v>2.90486550331116</v>
+        <v>2.90486526489258</v>
       </c>
       <c r="H168" t="n">
         <v>1684867</v>
@@ -5270,7 +5270,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G169" t="n">
-        <v>2.94448494911194</v>
+        <v>2.94448518753052</v>
       </c>
       <c r="H169" t="n">
         <v>1196461</v>
@@ -5299,7 +5299,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G170" t="n">
-        <v>2.98950791358948</v>
+        <v>2.9895076751709</v>
       </c>
       <c r="H170" t="n">
         <v>877610</v>
@@ -5444,7 +5444,7 @@
         <v>3.50600004196167</v>
       </c>
       <c r="G175" t="n">
-        <v>3.15699219703674</v>
+        <v>3.15699243545532</v>
       </c>
       <c r="H175" t="n">
         <v>1959547</v>
@@ -5531,7 +5531,7 @@
         <v>3.31800007820129</v>
       </c>
       <c r="G178" t="n">
-        <v>2.98770689964294</v>
+        <v>2.98770713806152</v>
       </c>
       <c r="H178" t="n">
         <v>742754</v>
@@ -5560,7 +5560,7 @@
         <v>3.29200005531311</v>
       </c>
       <c r="G179" t="n">
-        <v>2.96429538726807</v>
+        <v>2.96429514884949</v>
       </c>
       <c r="H179" t="n">
         <v>510602</v>
@@ -5734,7 +5734,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G185" t="n">
-        <v>2.89045786857605</v>
+        <v>2.89045810699463</v>
       </c>
       <c r="H185" t="n">
         <v>709125</v>
@@ -5763,7 +5763,7 @@
         <v>3.19600009918213</v>
       </c>
       <c r="G186" t="n">
-        <v>2.87785148620605</v>
+        <v>2.87785172462463</v>
       </c>
       <c r="H186" t="n">
         <v>566793</v>
@@ -5879,7 +5879,7 @@
         <v>3.16599988937378</v>
       </c>
       <c r="G190" t="n">
-        <v>2.85083794593811</v>
+        <v>2.85083770751953</v>
       </c>
       <c r="H190" t="n">
         <v>558141</v>
@@ -5937,7 +5937,7 @@
         <v>3.16799998283386</v>
       </c>
       <c r="G192" t="n">
-        <v>2.85263895988464</v>
+        <v>2.85263872146606</v>
       </c>
       <c r="H192" t="n">
         <v>381457</v>
@@ -6024,7 +6024,7 @@
         <v>3.16400003433228</v>
       </c>
       <c r="G195" t="n">
-        <v>2.84903717041016</v>
+        <v>2.84903693199158</v>
       </c>
       <c r="H195" t="n">
         <v>562311</v>
@@ -6082,7 +6082,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G197" t="n">
-        <v>2.84993767738342</v>
+        <v>2.84993743896484</v>
       </c>
       <c r="H197" t="n">
         <v>267637</v>
@@ -6227,7 +6227,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G202" t="n">
-        <v>2.77339887619019</v>
+        <v>2.77339863777161</v>
       </c>
       <c r="H202" t="n">
         <v>272137</v>
@@ -6256,7 +6256,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G203" t="n">
-        <v>2.76439452171326</v>
+        <v>2.7643940448761</v>
       </c>
       <c r="H203" t="n">
         <v>271367</v>
@@ -6314,7 +6314,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G205" t="n">
-        <v>2.67434906959534</v>
+        <v>2.67434883117676</v>
       </c>
       <c r="H205" t="n">
         <v>598555</v>
@@ -6372,7 +6372,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G207" t="n">
-        <v>2.63833093643188</v>
+        <v>2.63833069801331</v>
       </c>
       <c r="H207" t="n">
         <v>256503</v>
@@ -6401,7 +6401,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G208" t="n">
-        <v>2.66534423828125</v>
+        <v>2.66534447669983</v>
       </c>
       <c r="H208" t="n">
         <v>290531</v>
@@ -6430,7 +6430,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G209" t="n">
-        <v>2.63833093643188</v>
+        <v>2.63833069801331</v>
       </c>
       <c r="H209" t="n">
         <v>276036</v>
@@ -6546,7 +6546,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G213" t="n">
-        <v>2.52127194404602</v>
+        <v>2.52127170562744</v>
       </c>
       <c r="H213" t="n">
         <v>657781</v>
@@ -6691,7 +6691,7 @@
         <v>2.875</v>
       </c>
       <c r="G218" t="n">
-        <v>2.58880591392517</v>
+        <v>2.58880567550659</v>
       </c>
       <c r="H218" t="n">
         <v>460755</v>
@@ -6720,7 +6720,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G219" t="n">
-        <v>2.61131715774536</v>
+        <v>2.61131739616394</v>
       </c>
       <c r="H219" t="n">
         <v>259416</v>
@@ -6749,7 +6749,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G220" t="n">
-        <v>2.66534423828125</v>
+        <v>2.66534447669983</v>
       </c>
       <c r="H220" t="n">
         <v>807427</v>
@@ -6807,7 +6807,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G222" t="n">
-        <v>2.70586490631104</v>
+        <v>2.70586514472961</v>
       </c>
       <c r="H222" t="n">
         <v>301429</v>
@@ -6894,7 +6894,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G225" t="n">
-        <v>2.73287844657898</v>
+        <v>2.73287868499756</v>
       </c>
       <c r="H225" t="n">
         <v>325591</v>
@@ -6923,7 +6923,7 @@
         <v>3.04500007629395</v>
       </c>
       <c r="G226" t="n">
-        <v>2.74188303947449</v>
+        <v>2.74188327789307</v>
       </c>
       <c r="H226" t="n">
         <v>320777</v>
@@ -7039,7 +7039,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G230" t="n">
-        <v>2.79140782356262</v>
+        <v>2.7914080619812</v>
       </c>
       <c r="H230" t="n">
         <v>707525</v>
@@ -7126,7 +7126,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G233" t="n">
-        <v>2.76439452171326</v>
+        <v>2.7643940448761</v>
       </c>
       <c r="H233" t="n">
         <v>219195</v>
@@ -7155,7 +7155,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G234" t="n">
-        <v>2.79140782356262</v>
+        <v>2.7914080619812</v>
       </c>
       <c r="H234" t="n">
         <v>307932</v>
@@ -7184,7 +7184,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G235" t="n">
-        <v>2.78690552711487</v>
+        <v>2.78690576553345</v>
       </c>
       <c r="H235" t="n">
         <v>572294</v>
@@ -7358,7 +7358,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G241" t="n">
-        <v>2.73287844657898</v>
+        <v>2.73287868499756</v>
       </c>
       <c r="H241" t="n">
         <v>156956</v>
@@ -7474,7 +7474,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G245" t="n">
-        <v>2.77339887619019</v>
+        <v>2.77339863777161</v>
       </c>
       <c r="H245" t="n">
         <v>803152</v>
@@ -7503,7 +7503,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G246" t="n">
-        <v>2.78690552711487</v>
+        <v>2.78690576553345</v>
       </c>
       <c r="H246" t="n">
         <v>482864</v>
@@ -7590,7 +7590,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G249" t="n">
-        <v>2.669846534729</v>
+        <v>2.66984677314758</v>
       </c>
       <c r="H249" t="n">
         <v>254041</v>
@@ -7619,7 +7619,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G250" t="n">
-        <v>2.6563401222229</v>
+        <v>2.65633988380432</v>
       </c>
       <c r="H250" t="n">
         <v>375208</v>
@@ -7648,7 +7648,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G251" t="n">
-        <v>2.66534423828125</v>
+        <v>2.66534447669983</v>
       </c>
       <c r="H251" t="n">
         <v>193370</v>
@@ -7677,7 +7677,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G252" t="n">
-        <v>2.6563401222229</v>
+        <v>2.65633988380432</v>
       </c>
       <c r="H252" t="n">
         <v>198249</v>
@@ -24996,6 +24996,35 @@
         <v>208216</v>
       </c>
       <c r="I849" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="s">
+        <v>9</v>
+      </c>
+      <c r="B850" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C850" t="n">
+        <v>2.57800006866455</v>
+      </c>
+      <c r="D850" t="n">
+        <v>2.61400008201599</v>
+      </c>
+      <c r="E850" t="n">
+        <v>2.54800009727478</v>
+      </c>
+      <c r="F850" t="n">
+        <v>2.58400011062622</v>
+      </c>
+      <c r="G850" t="n">
+        <v>2.58400011062622</v>
+      </c>
+      <c r="H850" t="n">
+        <v>140127</v>
+      </c>
+      <c r="I850" t="s">
         <v>9</v>
       </c>
     </row>
